--- a/research/traditional_assets/database/data/canada/canada_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_telecom_wireless.xlsx
@@ -650,10 +650,10 @@
         <v>0.1373223801065719</v>
       </c>
       <c r="X2">
-        <v>0.1145694074756904</v>
+        <v>0.1145251948610081</v>
       </c>
       <c r="Y2">
-        <v>0.02275297263088152</v>
+        <v>0.02279718524556384</v>
       </c>
       <c r="Z2">
         <v>0.5045495890210138</v>
@@ -662,10 +662,10 @@
         <v>0.08438607317319718</v>
       </c>
       <c r="AB2">
-        <v>0.06723181193167957</v>
+        <v>0.06721723717237095</v>
       </c>
       <c r="AC2">
-        <v>0.01715426124151762</v>
+        <v>0.01716883600082623</v>
       </c>
       <c r="AD2">
         <v>33987.2</v>
@@ -787,10 +787,10 @@
         <v>0.1373223801065719</v>
       </c>
       <c r="X3">
-        <v>0.1145694074756904</v>
+        <v>0.1145251948610081</v>
       </c>
       <c r="Y3">
-        <v>0.02275297263088152</v>
+        <v>0.02279718524556384</v>
       </c>
       <c r="Z3">
         <v>0.5045495890210138</v>
@@ -799,10 +799,10 @@
         <v>0.08438607317319718</v>
       </c>
       <c r="AB3">
-        <v>0.06723181193167957</v>
+        <v>0.06721723717237095</v>
       </c>
       <c r="AC3">
-        <v>0.01715426124151762</v>
+        <v>0.01716883600082623</v>
       </c>
       <c r="AD3">
         <v>33987.2</v>
@@ -1139,49 +1139,49 @@
         <v>2.09231264072049</v>
       </c>
       <c r="F2">
-        <v>3.0469315136048</v>
+        <v>3.02517721677199</v>
       </c>
       <c r="G2">
         <v>5.09713702964951</v>
       </c>
       <c r="H2">
-        <v>4.1820423221704</v>
+        <v>4.41015372156151</v>
       </c>
       <c r="I2">
         <v>0.670348396869477</v>
       </c>
       <c r="J2">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="K2">
         <v>16713.6</v>
       </c>
       <c r="L2">
-        <v>22540.6711119561</v>
+        <v>22215.5847343778</v>
       </c>
       <c r="M2">
         <v>50107.1</v>
       </c>
       <c r="N2">
-        <v>49832.4111119561</v>
+        <v>51028.3487343778</v>
       </c>
       <c r="O2">
         <v>33987.2</v>
       </c>
       <c r="P2">
-        <v>27885.44</v>
+        <v>29406.464</v>
       </c>
       <c r="Q2">
-        <v>0.0672318119316796</v>
+        <v>0.06721723717237089</v>
       </c>
       <c r="R2">
-        <v>0.0675651965907286</v>
+        <v>0.06612535473807039</v>
       </c>
       <c r="S2">
         <v>0.043953</v>
       </c>
       <c r="T2">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.11456940747569</v>
+        <v>0.114525194861008</v>
       </c>
       <c r="X2">
-        <v>0.09813138131273021</v>
+        <v>0.101311820804929</v>
       </c>
       <c r="Y2">
         <v>1.58718694829118</v>
       </c>
       <c r="Z2">
-        <v>1.20779992811448</v>
+        <v>1.28202819410923</v>
       </c>
       <c r="AA2">
         <v>33987.2</v>
@@ -1236,7 +1236,7 @@
         <v>16713.6</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07336701386096411</v>
+        <v>0.07334929072204936</v>
       </c>
       <c r="C2">
-        <v>46086.0245927835</v>
+        <v>46088.11754527599</v>
       </c>
       <c r="D2">
-        <v>45492.3245927835</v>
+        <v>45494.41754527599</v>
       </c>
       <c r="E2">
         <v>-33987.2</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07336701386096411</v>
+        <v>0.07334929072204936</v>
       </c>
       <c r="T2">
         <v>0.6362422799549506</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.265</v>
       </c>
       <c r="W2">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07321595627423255</v>
+        <v>0.07318799010163592</v>
       </c>
       <c r="C3">
-        <v>45682.40909182026</v>
+        <v>45691.54166724924</v>
       </c>
       <c r="D3">
-        <v>45595.71709182027</v>
+        <v>45604.84966724925</v>
       </c>
       <c r="E3">
         <v>-33480.192</v>
@@ -1539,37 +1539,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M3">
-        <v>26.2123136</v>
+        <v>25.5025024</v>
       </c>
       <c r="N3">
-        <v>4893.262686399999</v>
+        <v>4893.972497599999</v>
       </c>
       <c r="O3">
-        <v>1296.714611896</v>
+        <v>1296.902711864</v>
       </c>
       <c r="P3">
-        <v>3596.548074503999</v>
+        <v>3597.069785735999</v>
       </c>
       <c r="Q3">
-        <v>7011.948074503998</v>
+        <v>7012.469785735999</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07357167805478036</v>
+        <v>0.07355382333498578</v>
       </c>
       <c r="T3">
         <v>0.6409658968818889</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.265</v>
       </c>
       <c r="W3">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>187.6780155720401</v>
+        <v>192.901658152574</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07306489868750102</v>
+        <v>0.07302668948122248</v>
       </c>
       <c r="C4">
-        <v>45279.26463119058</v>
+        <v>45295.50321463588</v>
       </c>
       <c r="D4">
-        <v>45699.58063119059</v>
+        <v>45715.81921463589</v>
       </c>
       <c r="E4">
         <v>-32973.18399999999</v>
@@ -1621,37 +1621,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M4">
-        <v>52.4246272</v>
+        <v>51.00500479999999</v>
       </c>
       <c r="N4">
-        <v>4867.050372799999</v>
+        <v>4868.469995199998</v>
       </c>
       <c r="O4">
-        <v>1289.768348792</v>
+        <v>1290.144548728</v>
       </c>
       <c r="P4">
-        <v>3577.282024007999</v>
+        <v>3578.325446471998</v>
       </c>
       <c r="Q4">
-        <v>6992.682024008</v>
+        <v>6993.725446471999</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07378051906887859</v>
+        <v>0.0737625300828801</v>
       </c>
       <c r="T4">
         <v>0.6457859141542749</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.265</v>
       </c>
       <c r="W4">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.83900778602005</v>
+        <v>96.45082907628702</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07291384110076946</v>
+        <v>0.07286538886080907</v>
       </c>
       <c r="C5">
-        <v>44876.59443722487</v>
+        <v>44900.00612013111</v>
       </c>
       <c r="D5">
-        <v>45803.91843722487</v>
+        <v>45827.33012013111</v>
       </c>
       <c r="E5">
         <v>-32466.176</v>
@@ -1703,37 +1703,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M5">
-        <v>78.6369408</v>
+        <v>76.50750719999999</v>
       </c>
       <c r="N5">
-        <v>4840.838059199998</v>
+        <v>4842.967492799999</v>
       </c>
       <c r="O5">
-        <v>1282.822085688</v>
+        <v>1283.386385592</v>
       </c>
       <c r="P5">
-        <v>3558.015973511999</v>
+        <v>3559.581107207999</v>
       </c>
       <c r="Q5">
-        <v>6973.415973511999</v>
+        <v>6974.981107207999</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07399366608326749</v>
+        <v>0.07397554006268976</v>
       </c>
       <c r="T5">
         <v>0.6507053132260916</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.265</v>
       </c>
       <c r="W5">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.55933852401336</v>
+        <v>64.30055271752468</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07276278351403789</v>
+        <v>0.07270408824039565</v>
       </c>
       <c r="C6">
-        <v>44474.40176578534</v>
+        <v>44505.05435489479</v>
       </c>
       <c r="D6">
-        <v>45908.73376578534</v>
+        <v>45939.38635489479</v>
       </c>
       <c r="E6">
         <v>-31959.168</v>
@@ -1785,37 +1785,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M6">
-        <v>104.8492544</v>
+        <v>102.0100096</v>
       </c>
       <c r="N6">
-        <v>4814.625745599998</v>
+        <v>4817.464990399999</v>
       </c>
       <c r="O6">
-        <v>1275.875822584</v>
+        <v>1276.628222456</v>
       </c>
       <c r="P6">
-        <v>3538.749923015999</v>
+        <v>3540.836767943999</v>
       </c>
       <c r="Q6">
-        <v>6954.149923015999</v>
+        <v>6956.236767943999</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07421125366045614</v>
+        <v>0.07419298775041212</v>
       </c>
       <c r="T6">
         <v>0.655727199778571</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.265</v>
       </c>
       <c r="W6">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.91950389301002</v>
+        <v>48.22541453814351</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07261172592730634</v>
+        <v>0.0725427876199822</v>
       </c>
       <c r="C7">
-        <v>44072.68990260478</v>
+        <v>44110.65192902288</v>
       </c>
       <c r="D7">
-        <v>46014.02990260479</v>
+        <v>46051.99192902288</v>
       </c>
       <c r="E7">
         <v>-31452.16</v>
@@ -1867,37 +1867,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M7">
-        <v>131.061568</v>
+        <v>127.512512</v>
       </c>
       <c r="N7">
-        <v>4788.413431999998</v>
+        <v>4791.962487999998</v>
       </c>
       <c r="O7">
-        <v>1268.92955948</v>
+        <v>1269.87005932</v>
       </c>
       <c r="P7">
-        <v>3519.483872519999</v>
+        <v>3522.092428679999</v>
       </c>
       <c r="Q7">
-        <v>6934.883872519998</v>
+        <v>6937.492428679999</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07443342202874352</v>
+        <v>0.0744150132841918</v>
       </c>
       <c r="T7">
         <v>0.6608548102584711</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.265</v>
       </c>
       <c r="W7">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.53560311440802</v>
+        <v>38.58033163051481</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07246066834057478</v>
+        <v>0.07238148699956877</v>
       </c>
       <c r="C8">
-        <v>43671.46216362988</v>
+        <v>43716.80289202568</v>
       </c>
       <c r="D8">
-        <v>46119.81016362989</v>
+        <v>46165.15089202569</v>
       </c>
       <c r="E8">
         <v>-30945.152</v>
@@ -1949,37 +1949,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M8">
-        <v>157.2738816</v>
+        <v>153.0150144</v>
       </c>
       <c r="N8">
-        <v>4762.201118399998</v>
+        <v>4766.459985599999</v>
       </c>
       <c r="O8">
-        <v>1261.983296376</v>
+        <v>1263.111896184</v>
       </c>
       <c r="P8">
-        <v>3500.217822023999</v>
+        <v>3503.348089415999</v>
       </c>
       <c r="Q8">
-        <v>6915.617822023999</v>
+        <v>6918.748089415999</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07466031738359019</v>
+        <v>0.07464176276549869</v>
       </c>
       <c r="T8">
         <v>0.6660915188336881</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.265</v>
       </c>
       <c r="W8">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.27966926200668</v>
+        <v>32.15027635876234</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07230961075384323</v>
+        <v>0.07222018637915535</v>
       </c>
       <c r="C9">
-        <v>43270.72189536928</v>
+        <v>43323.51133331349</v>
       </c>
       <c r="D9">
-        <v>46226.07789536928</v>
+        <v>46278.86733331349</v>
       </c>
       <c r="E9">
         <v>-30438.144</v>
@@ -2031,37 +2031,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M9">
-        <v>183.4861952</v>
+        <v>178.5175168</v>
       </c>
       <c r="N9">
-        <v>4735.988804799998</v>
+        <v>4740.957483199999</v>
       </c>
       <c r="O9">
-        <v>1255.037033272</v>
+        <v>1256.353733048</v>
       </c>
       <c r="P9">
-        <v>3480.951771527999</v>
+        <v>3484.603750151999</v>
       </c>
       <c r="Q9">
-        <v>6896.351771528</v>
+        <v>6900.003750151999</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0748920922084336</v>
+        <v>0.07487338857973694</v>
       </c>
       <c r="T9">
         <v>0.6714408447976198</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.265</v>
       </c>
       <c r="W9">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.81114508172001</v>
+        <v>27.55737973608201</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07215855316711167</v>
+        <v>0.07205888575874191</v>
       </c>
       <c r="C10">
-        <v>42870.47247524652</v>
+        <v>42930.781382689</v>
       </c>
       <c r="D10">
-        <v>46332.83647524652</v>
+        <v>46393.145382689</v>
       </c>
       <c r="E10">
         <v>-29931.136</v>
@@ -2113,37 +2113,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M10">
-        <v>209.6985088</v>
+        <v>204.0200192</v>
       </c>
       <c r="N10">
-        <v>4709.776491199998</v>
+        <v>4715.454980799998</v>
       </c>
       <c r="O10">
-        <v>1248.090770168</v>
+        <v>1249.595569912</v>
       </c>
       <c r="P10">
-        <v>3461.685721031999</v>
+        <v>3465.859410887999</v>
       </c>
       <c r="Q10">
-        <v>6877.085721031999</v>
+        <v>6881.259410887998</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07512890561642574</v>
+        <v>0.07511004973776295</v>
       </c>
       <c r="T10">
         <v>0.6769064604564192</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.265</v>
       </c>
       <c r="W10">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.45975194650501</v>
+        <v>24.11270726907176</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07200749558038012</v>
+        <v>0.07189758513832847</v>
       </c>
       <c r="C11">
-        <v>42470.71731195783</v>
+        <v>42538.61721084741</v>
       </c>
       <c r="D11">
-        <v>46440.08931195783</v>
+        <v>46507.98921084741</v>
       </c>
       <c r="E11">
         <v>-29424.128</v>
@@ -2195,37 +2195,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M11">
-        <v>235.9108224</v>
+        <v>229.5225215999999</v>
       </c>
       <c r="N11">
-        <v>4683.564177599998</v>
+        <v>4689.952478399999</v>
       </c>
       <c r="O11">
-        <v>1241.144507064</v>
+        <v>1242.837406776</v>
       </c>
       <c r="P11">
-        <v>3442.419670535999</v>
+        <v>3447.115071623999</v>
       </c>
       <c r="Q11">
-        <v>6857.819670535999</v>
+        <v>6862.515071623999</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07537092371470343</v>
+        <v>0.07535191223992141</v>
       </c>
       <c r="T11">
         <v>0.6824921995362913</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.265</v>
       </c>
       <c r="W11">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.85311284133779</v>
+        <v>21.43351757250823</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07185643799364858</v>
+        <v>0.07173628451791506</v>
       </c>
       <c r="C12">
-        <v>42071.45984583496</v>
+        <v>42147.02302988373</v>
       </c>
       <c r="D12">
-        <v>46547.83984583497</v>
+        <v>46623.40302988374</v>
       </c>
       <c r="E12">
         <v>-28917.12</v>
@@ -2277,37 +2277,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M12">
-        <v>262.123136</v>
+        <v>255.025024</v>
       </c>
       <c r="N12">
-        <v>4657.351863999998</v>
+        <v>4664.449975999999</v>
       </c>
       <c r="O12">
-        <v>1234.19824396</v>
+        <v>1236.07924364</v>
       </c>
       <c r="P12">
-        <v>3423.153620039999</v>
+        <v>3428.370732359999</v>
       </c>
       <c r="Q12">
-        <v>6838.553620039998</v>
+        <v>6843.770732359999</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07561831999294286</v>
+        <v>0.07559914946435006</v>
       </c>
       <c r="T12">
         <v>0.6882020661512716</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.265</v>
       </c>
       <c r="W12">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.76780155720401</v>
+        <v>19.29016581525741</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07170538040691703</v>
+        <v>0.07157498389750162</v>
       </c>
       <c r="C13">
-        <v>41672.70354921301</v>
+        <v>41756.00309380784</v>
       </c>
       <c r="D13">
-        <v>46656.09154921302</v>
+        <v>46739.39109380784</v>
       </c>
       <c r="E13">
         <v>-28410.112</v>
@@ -2359,37 +2359,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M13">
-        <v>288.3354496</v>
+        <v>280.5275264</v>
       </c>
       <c r="N13">
-        <v>4631.139550399998</v>
+        <v>4638.947473599998</v>
       </c>
       <c r="O13">
-        <v>1227.251980856</v>
+        <v>1229.321080504</v>
       </c>
       <c r="P13">
-        <v>3403.887569543999</v>
+        <v>3409.626393095999</v>
       </c>
       <c r="Q13">
-        <v>6819.287569543999</v>
+        <v>6825.026393095999</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07587127573810901</v>
+        <v>0.07585194258146249</v>
       </c>
       <c r="T13">
         <v>0.6940402443755773</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.265</v>
       </c>
       <c r="W13">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.06163777927637</v>
+        <v>17.53651437750673</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07155432282018546</v>
+        <v>0.07141368327708819</v>
       </c>
       <c r="C14">
-        <v>41274.45192680344</v>
+        <v>41365.56169906703</v>
       </c>
       <c r="D14">
-        <v>46764.84792680344</v>
+        <v>46855.95769906703</v>
       </c>
       <c r="E14">
         <v>-27903.104</v>
@@ -2441,37 +2441,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M14">
-        <v>314.5477632</v>
+        <v>306.0300288</v>
       </c>
       <c r="N14">
-        <v>4604.927236799998</v>
+        <v>4613.444971199999</v>
       </c>
       <c r="O14">
-        <v>1220.305717752</v>
+        <v>1222.562917368</v>
       </c>
       <c r="P14">
-        <v>3384.621519047999</v>
+        <v>3390.882053831999</v>
       </c>
       <c r="Q14">
-        <v>6800.021519047999</v>
+        <v>6806.282053831999</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07612998047748348</v>
+        <v>0.07611048099669113</v>
       </c>
       <c r="T14">
         <v>0.7000111084686172</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.265</v>
       </c>
       <c r="W14">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.63983463100334</v>
+        <v>16.07513817938117</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07140326523345392</v>
+        <v>0.07125238265667476</v>
       </c>
       <c r="C15">
-        <v>40876.70851607226</v>
+        <v>40975.70318507661</v>
       </c>
       <c r="D15">
-        <v>46874.11251607227</v>
+        <v>46973.10718507661</v>
       </c>
       <c r="E15">
         <v>-27396.096</v>
@@ -2523,37 +2523,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M15">
-        <v>340.7600768</v>
+        <v>331.5325311999999</v>
       </c>
       <c r="N15">
-        <v>4578.714923199998</v>
+        <v>4587.942468799999</v>
       </c>
       <c r="O15">
-        <v>1213.359454648</v>
+        <v>1215.804754232</v>
       </c>
       <c r="P15">
-        <v>3365.355468551998</v>
+        <v>3372.137714567999</v>
       </c>
       <c r="Q15">
-        <v>6780.755468551999</v>
+        <v>6787.537714568</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07639463245224587</v>
+        <v>0.07637496282376409</v>
       </c>
       <c r="T15">
         <v>0.7061192338051754</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.265</v>
       </c>
       <c r="W15">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.43677042861847</v>
+        <v>14.83858908865954</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07125220764672235</v>
+        <v>0.07109108203626133</v>
       </c>
       <c r="C16">
-        <v>40479.47688762369</v>
+        <v>40586.43193475838</v>
       </c>
       <c r="D16">
-        <v>46983.8888876237</v>
+        <v>47090.84393475838</v>
       </c>
       <c r="E16">
         <v>-26889.088</v>
@@ -2605,37 +2605,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M16">
-        <v>366.9723904000001</v>
+        <v>357.0350336</v>
       </c>
       <c r="N16">
-        <v>4552.502609599998</v>
+        <v>4562.439966399998</v>
       </c>
       <c r="O16">
-        <v>1206.413191544</v>
+        <v>1209.046591096</v>
       </c>
       <c r="P16">
-        <v>3346.089418055999</v>
+        <v>3353.393375303999</v>
       </c>
       <c r="Q16">
-        <v>6761.489418055999</v>
+        <v>6768.793375303999</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07666543912409576</v>
+        <v>0.07664559539100155</v>
       </c>
       <c r="T16">
         <v>0.7123694085681651</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.265</v>
       </c>
       <c r="W16">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.40557254086001</v>
+        <v>13.778689868041</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07110115005999078</v>
+        <v>0.0709297814158479</v>
       </c>
       <c r="C17">
-        <v>40082.76064558899</v>
+        <v>40197.75237508721</v>
       </c>
       <c r="D17">
-        <v>47094.180645589</v>
+        <v>47209.1723750872</v>
       </c>
       <c r="E17">
         <v>-26382.08</v>
@@ -2687,37 +2687,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M17">
-        <v>393.184704</v>
+        <v>382.5375359999999</v>
       </c>
       <c r="N17">
-        <v>4526.290295999998</v>
+        <v>4536.937463999999</v>
       </c>
       <c r="O17">
-        <v>1199.46692844</v>
+        <v>1202.28842796</v>
       </c>
       <c r="P17">
-        <v>3326.823367559999</v>
+        <v>3334.649036039999</v>
       </c>
       <c r="Q17">
-        <v>6742.223367559998</v>
+        <v>6750.049036039999</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07694261771763622</v>
+        <v>0.07692259578335046</v>
       </c>
       <c r="T17">
         <v>0.7187666462667545</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.51186770480267</v>
+        <v>12.86011054350494</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07095009247325924</v>
+        <v>0.07076848079543448</v>
       </c>
       <c r="C18">
-        <v>39686.56342802091</v>
+        <v>39809.66897764592</v>
       </c>
       <c r="D18">
-        <v>47204.99142802091</v>
+        <v>47328.09697764592</v>
       </c>
       <c r="E18">
         <v>-25875.072</v>
@@ -2769,37 +2769,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M18">
-        <v>419.3970176</v>
+        <v>408.0400384</v>
       </c>
       <c r="N18">
-        <v>4500.077982399998</v>
+        <v>4511.434961599998</v>
       </c>
       <c r="O18">
-        <v>1192.520665336</v>
+        <v>1195.530264823999</v>
       </c>
       <c r="P18">
-        <v>3307.557317063999</v>
+        <v>3315.904696775999</v>
       </c>
       <c r="Q18">
-        <v>6722.957317063999</v>
+        <v>6731.304696775998</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07722639580149909</v>
+        <v>0.07720619142313628</v>
       </c>
       <c r="T18">
         <v>0.7253161991486438</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.265</v>
       </c>
       <c r="W18">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.72987597325251</v>
+        <v>12.05635363453588</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07079903488652768</v>
+        <v>0.07060718017502104</v>
       </c>
       <c r="C19">
-        <v>39290.88890729384</v>
+        <v>39422.18625918864</v>
       </c>
       <c r="D19">
-        <v>47316.32490729384</v>
+        <v>47447.62225918864</v>
       </c>
       <c r="E19">
         <v>-25368.064</v>
@@ -2851,37 +2851,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M19">
-        <v>445.6093312</v>
+        <v>433.5425408</v>
       </c>
       <c r="N19">
-        <v>4473.865668799998</v>
+        <v>4485.932459199998</v>
       </c>
       <c r="O19">
-        <v>1185.574402232</v>
+        <v>1188.772101688</v>
       </c>
       <c r="P19">
-        <v>3288.291266567999</v>
+        <v>3297.160357511999</v>
       </c>
       <c r="Q19">
-        <v>6703.691266567999</v>
+        <v>6712.560357511999</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07751701191147914</v>
+        <v>0.07749662069279643</v>
       </c>
       <c r="T19">
         <v>0.7320235725819038</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.265</v>
       </c>
       <c r="W19">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.03988326894353</v>
+        <v>11.34715636191612</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07064797729979613</v>
+        <v>0.07044587955460761</v>
       </c>
       <c r="C20">
-        <v>38895.74079050931</v>
+        <v>39035.30878221249</v>
       </c>
       <c r="D20">
-        <v>47428.18479050932</v>
+        <v>47567.75278221249</v>
       </c>
       <c r="E20">
         <v>-24861.056</v>
@@ -2933,37 +2933,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M20">
-        <v>471.8216447999999</v>
+        <v>459.0450431999999</v>
       </c>
       <c r="N20">
-        <v>4447.653355199998</v>
+        <v>4460.429956799999</v>
       </c>
       <c r="O20">
-        <v>1178.628139128</v>
+        <v>1182.013938552</v>
       </c>
       <c r="P20">
-        <v>3269.025216071998</v>
+        <v>3278.416018247999</v>
       </c>
       <c r="Q20">
-        <v>6684.425216071999</v>
+        <v>6693.816018247999</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07781471621926357</v>
+        <v>0.07779413360318001</v>
       </c>
       <c r="T20">
         <v>0.7388945404891457</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.265</v>
       </c>
       <c r="W20">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.42655642066889</v>
+        <v>10.71675878625411</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07049691971306458</v>
+        <v>0.07028457893419418</v>
       </c>
       <c r="C21">
-        <v>38501.12281990764</v>
+        <v>38649.04115553825</v>
       </c>
       <c r="D21">
-        <v>47540.57481990764</v>
+        <v>47688.49315553825</v>
       </c>
       <c r="E21">
         <v>-24354.048</v>
@@ -3015,37 +3015,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M21">
-        <v>498.0339584</v>
+        <v>484.5475456</v>
       </c>
       <c r="N21">
-        <v>4421.441041599998</v>
+        <v>4434.927454399998</v>
       </c>
       <c r="O21">
-        <v>1171.681876024</v>
+        <v>1175.255775416</v>
       </c>
       <c r="P21">
-        <v>3249.759165575999</v>
+        <v>3259.671678983998</v>
       </c>
       <c r="Q21">
-        <v>6665.159165575998</v>
+        <v>6675.071678983999</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07811977125069701</v>
+        <v>0.07809899251135083</v>
       </c>
       <c r="T21">
         <v>0.7459351619249616</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.877790293265267</v>
+        <v>10.15271885013548</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07034586212633304</v>
+        <v>0.07012327831378076</v>
       </c>
       <c r="C22">
-        <v>38107.03877328514</v>
+        <v>38263.3880348997</v>
       </c>
       <c r="D22">
-        <v>47653.49877328514</v>
+        <v>47809.84803489971</v>
       </c>
       <c r="E22">
         <v>-23847.04</v>
@@ -3097,37 +3097,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M22">
-        <v>524.246272</v>
+        <v>510.0500479999999</v>
       </c>
       <c r="N22">
-        <v>4395.228727999998</v>
+        <v>4409.424951999998</v>
       </c>
       <c r="O22">
-        <v>1164.73561292</v>
+        <v>1168.49761228</v>
       </c>
       <c r="P22">
-        <v>3230.493115079998</v>
+        <v>3240.927339719999</v>
       </c>
       <c r="Q22">
-        <v>6645.893115079998</v>
+        <v>6656.327339719999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07843245265791628</v>
+        <v>0.07841147289222594</v>
       </c>
       <c r="T22">
         <v>0.7531517988966728</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.265</v>
       </c>
       <c r="W22">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.383900778602005</v>
+        <v>9.645082907628701</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07019480453960146</v>
+        <v>0.06996197769336732</v>
       </c>
       <c r="C23">
-        <v>37713.49246441746</v>
+        <v>37878.35412354216</v>
       </c>
       <c r="D23">
-        <v>47766.96046441746</v>
+        <v>47931.82212354216</v>
       </c>
       <c r="E23">
         <v>-23340.032</v>
@@ -3179,37 +3179,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M23">
-        <v>550.4585855999999</v>
+        <v>535.5525503999999</v>
       </c>
       <c r="N23">
-        <v>4369.016414399999</v>
+        <v>4383.922449599999</v>
       </c>
       <c r="O23">
-        <v>1157.789349816</v>
+        <v>1161.739449144</v>
       </c>
       <c r="P23">
-        <v>3211.227064583999</v>
+        <v>3222.183000455999</v>
       </c>
       <c r="Q23">
-        <v>6626.627064584</v>
+        <v>6637.583000455999</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07875305005012843</v>
+        <v>0.07873186416881939</v>
       </c>
       <c r="T23">
         <v>0.7605511355385539</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.265</v>
       </c>
       <c r="W23">
-        <v>0.0379995</v>
+        <v>0.0369705</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.937048360573341</v>
+        <v>9.185793245360671</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07022161695286991</v>
+        <v>0.06980067707295388</v>
       </c>
       <c r="C24">
-        <v>37186.3058227872</v>
+        <v>37493.94417282989</v>
       </c>
       <c r="D24">
-        <v>47746.7818227872</v>
+        <v>48054.42017282989</v>
       </c>
       <c r="E24">
         <v>-22833.024</v>
@@ -3261,45 +3261,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M24">
-        <v>588.9404928</v>
+        <v>561.0550528</v>
       </c>
       <c r="N24">
-        <v>4330.534507199998</v>
+        <v>4358.419947199998</v>
       </c>
       <c r="O24">
-        <v>1147.591644408</v>
+        <v>1154.981286008</v>
       </c>
       <c r="P24">
-        <v>3182.942862791999</v>
+        <v>3203.438661191999</v>
       </c>
       <c r="Q24">
-        <v>6598.342862791998</v>
+        <v>6618.838661191999</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07908186788829476</v>
+        <v>0.07906047060635113</v>
       </c>
       <c r="T24">
         <v>0.7681401987609962</v>
       </c>
       <c r="U24">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.265</v>
       </c>
       <c r="W24">
-        <v>0.038808</v>
+        <v>0.0369705</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.353093496104057</v>
+        <v>8.768257188753363</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07007864436613837</v>
+        <v>0.06989295145254046</v>
       </c>
       <c r="C25">
-        <v>36787.09432878907</v>
+        <v>36916.72551183125</v>
       </c>
       <c r="D25">
-        <v>47854.57832878907</v>
+        <v>47984.20951183125</v>
       </c>
       <c r="E25">
         <v>-22326.016</v>
@@ -3343,37 +3343,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M25">
-        <v>615.7105151999999</v>
+        <v>604.0493312</v>
       </c>
       <c r="N25">
-        <v>4303.764484799998</v>
+        <v>4315.425668799999</v>
       </c>
       <c r="O25">
-        <v>1140.497588472</v>
+        <v>1143.587802232</v>
       </c>
       <c r="P25">
-        <v>3163.266896327998</v>
+        <v>3171.837866567999</v>
       </c>
       <c r="Q25">
-        <v>6578.666896327999</v>
+        <v>6587.237866567999</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07941922644953034</v>
+        <v>0.07939761227602657</v>
       </c>
       <c r="T25">
         <v>0.7759263805086966</v>
       </c>
       <c r="U25">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.265</v>
       </c>
       <c r="W25">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.989915518012577</v>
+        <v>8.144160991333283</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06993567177940679</v>
+        <v>0.06974267583212702</v>
       </c>
       <c r="C26">
-        <v>36388.37067417834</v>
+        <v>36524.16600402581</v>
       </c>
       <c r="D26">
-        <v>47962.86267417834</v>
+        <v>48098.65800402581</v>
       </c>
       <c r="E26">
         <v>-21819.008</v>
@@ -3425,37 +3425,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M26">
-        <v>642.4805375999999</v>
+        <v>630.3123456</v>
       </c>
       <c r="N26">
-        <v>4276.994462399998</v>
+        <v>4289.162654399998</v>
       </c>
       <c r="O26">
-        <v>1133.403532536</v>
+        <v>1136.628103416</v>
       </c>
       <c r="P26">
-        <v>3143.590929863999</v>
+        <v>3152.534550983999</v>
       </c>
       <c r="Q26">
-        <v>6558.990929863999</v>
+        <v>6567.934550983999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07976546286764052</v>
+        <v>0.07974362609490399</v>
       </c>
       <c r="T26">
         <v>0.7839174617760735</v>
       </c>
       <c r="U26">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.265</v>
       </c>
       <c r="W26">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.657002371428719</v>
+        <v>7.80482095002773</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06979269919267525</v>
+        <v>0.06959240021171359</v>
       </c>
       <c r="C27">
-        <v>35990.13817808392</v>
+        <v>36132.15375014798</v>
       </c>
       <c r="D27">
-        <v>48071.63817808392</v>
+        <v>48213.65375014798</v>
       </c>
       <c r="E27">
         <v>-21312</v>
@@ -3507,37 +3507,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M27">
-        <v>669.25056</v>
+        <v>656.5753599999999</v>
       </c>
       <c r="N27">
-        <v>4250.224439999998</v>
+        <v>4262.899639999999</v>
       </c>
       <c r="O27">
-        <v>1126.309476599999</v>
+        <v>1129.6684046</v>
       </c>
       <c r="P27">
-        <v>3123.914963399999</v>
+        <v>3133.231235399999</v>
       </c>
       <c r="Q27">
-        <v>6539.314963399998</v>
+        <v>6548.631235399998</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08012093225690034</v>
+        <v>0.08009886694895146</v>
       </c>
       <c r="T27">
         <v>0.7921216385439136</v>
       </c>
       <c r="U27">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.265</v>
       </c>
       <c r="W27">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.35072227657157</v>
+        <v>7.492628112026622</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06964972660594368</v>
+        <v>0.06944212459130016</v>
       </c>
       <c r="C28">
-        <v>35592.40018981318</v>
+        <v>35740.69268477906</v>
       </c>
       <c r="D28">
-        <v>48180.90818981318</v>
+        <v>48329.20068477906</v>
       </c>
       <c r="E28">
         <v>-20804.992</v>
@@ -3589,37 +3589,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M28">
-        <v>696.0205824</v>
+        <v>682.8383743999999</v>
       </c>
       <c r="N28">
-        <v>4223.454417599998</v>
+        <v>4236.636625599998</v>
       </c>
       <c r="O28">
-        <v>1119.215420664</v>
+        <v>1122.708705784</v>
       </c>
       <c r="P28">
-        <v>3104.238996935998</v>
+        <v>3113.927919815998</v>
       </c>
       <c r="Q28">
-        <v>6519.638996935999</v>
+        <v>6529.327919815998</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08048600892695093</v>
+        <v>0.08046370890716238</v>
       </c>
       <c r="T28">
         <v>0.8005475498189927</v>
       </c>
       <c r="U28">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.265</v>
       </c>
       <c r="W28">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.068002189011126</v>
+        <v>7.204450107717904</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06950675401921214</v>
+        <v>0.06929184897088672</v>
       </c>
       <c r="C29">
-        <v>35195.16008919557</v>
+        <v>35349.78678030883</v>
       </c>
       <c r="D29">
-        <v>48290.67608919557</v>
+        <v>48445.30278030883</v>
       </c>
       <c r="E29">
         <v>-20297.984</v>
@@ -3671,37 +3671,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M29">
-        <v>722.7906048</v>
+        <v>709.1013888</v>
       </c>
       <c r="N29">
-        <v>4196.684395199998</v>
+        <v>4210.373611199999</v>
       </c>
       <c r="O29">
-        <v>1112.121364728</v>
+        <v>1115.749006968</v>
       </c>
       <c r="P29">
-        <v>3084.563030471998</v>
+        <v>3094.624604231999</v>
       </c>
       <c r="Q29">
-        <v>6499.963030471999</v>
+        <v>6510.024604232</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08086108769755088</v>
+        <v>0.08083854653546127</v>
       </c>
       <c r="T29">
         <v>0.8092043079783204</v>
       </c>
       <c r="U29">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.265</v>
       </c>
       <c r="W29">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.806224330158861</v>
+        <v>6.937618622246871</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06981654143248059</v>
+        <v>0.06949143335047331</v>
       </c>
       <c r="C30">
-        <v>34450.94040972335</v>
+        <v>34688.70217633218</v>
       </c>
       <c r="D30">
-        <v>48053.46440972335</v>
+        <v>48291.22617633219</v>
       </c>
       <c r="E30">
         <v>-19790.976</v>
@@ -3753,37 +3753,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M30">
-        <v>780.79232</v>
+        <v>759.497984</v>
       </c>
       <c r="N30">
-        <v>4138.682679999998</v>
+        <v>4159.977015999999</v>
       </c>
       <c r="O30">
-        <v>1096.750910199999</v>
+        <v>1102.39390924</v>
       </c>
       <c r="P30">
-        <v>3041.931769799999</v>
+        <v>3057.583106759999</v>
       </c>
       <c r="Q30">
-        <v>6457.331769799999</v>
+        <v>6472.983106759999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.0812465853228897</v>
+        <v>0.08122379632010181</v>
       </c>
       <c r="T30">
         <v>0.8181015316420741</v>
       </c>
       <c r="U30">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.265</v>
       </c>
       <c r="W30">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.300619094204203</v>
+        <v>6.477271966004322</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06968973884574903</v>
+        <v>0.06935365273005986</v>
       </c>
       <c r="C31">
-        <v>34040.74591072738</v>
+        <v>34287.95407910941</v>
       </c>
       <c r="D31">
-        <v>48150.27791072738</v>
+        <v>48397.48607910941</v>
       </c>
       <c r="E31">
         <v>-19283.968</v>
@@ -3835,37 +3835,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M31">
-        <v>808.6777599999999</v>
+        <v>786.6229119999999</v>
       </c>
       <c r="N31">
-        <v>4110.797239999999</v>
+        <v>4132.852087999999</v>
       </c>
       <c r="O31">
-        <v>1089.3612686</v>
+        <v>1095.20580332</v>
       </c>
       <c r="P31">
-        <v>3021.435971399999</v>
+        <v>3037.646284679999</v>
       </c>
       <c r="Q31">
-        <v>6436.8359714</v>
+        <v>6453.046284679999</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08164294203626624</v>
+        <v>0.08161989821135193</v>
       </c>
       <c r="T31">
         <v>0.827249381324525</v>
       </c>
       <c r="U31">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.265</v>
       </c>
       <c r="W31">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.083356366817853</v>
+        <v>6.253917760280035</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06956293625901747</v>
+        <v>0.06921587210964644</v>
       </c>
       <c r="C32">
-        <v>33630.94230032763</v>
+        <v>33887.67464121385</v>
       </c>
       <c r="D32">
-        <v>48247.48230032763</v>
+        <v>48504.21464121385</v>
       </c>
       <c r="E32">
         <v>-18776.96</v>
@@ -3917,37 +3917,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M32">
-        <v>836.5631999999999</v>
+        <v>813.7478399999999</v>
       </c>
       <c r="N32">
-        <v>4082.911799999998</v>
+        <v>4105.727159999999</v>
       </c>
       <c r="O32">
-        <v>1081.971627</v>
+        <v>1088.0176974</v>
       </c>
       <c r="P32">
-        <v>3000.940172999999</v>
+        <v>3017.709462599999</v>
       </c>
       <c r="Q32">
-        <v>6416.340172999999</v>
+        <v>6433.109462599999</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08205062322716782</v>
+        <v>0.08202731729949492</v>
       </c>
       <c r="T32">
         <v>0.83665859814076</v>
       </c>
       <c r="U32">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.265</v>
       </c>
       <c r="W32">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.880577821257257</v>
+        <v>6.045453834937367</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0694361336722859</v>
+        <v>0.069078091489233</v>
       </c>
       <c r="C33">
-        <v>33221.5319506567</v>
+        <v>33487.86697003122</v>
       </c>
       <c r="D33">
-        <v>48345.07995065671</v>
+        <v>48611.41497003122</v>
       </c>
       <c r="E33">
         <v>-18269.952</v>
@@ -3999,37 +3999,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M33">
-        <v>864.4486399999998</v>
+        <v>840.8727679999998</v>
       </c>
       <c r="N33">
-        <v>4055.026359999999</v>
+        <v>4078.602231999999</v>
       </c>
       <c r="O33">
-        <v>1074.5819854</v>
+        <v>1080.82959148</v>
       </c>
       <c r="P33">
-        <v>2980.444374599999</v>
+        <v>2997.772640519999</v>
       </c>
       <c r="Q33">
-        <v>6395.844374599999</v>
+        <v>6413.172640519999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08247012126418249</v>
+        <v>0.08244654563656957</v>
       </c>
       <c r="T33">
         <v>0.8463405458792049</v>
       </c>
       <c r="U33">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.265</v>
       </c>
       <c r="W33">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.690881762507024</v>
+        <v>5.850439195100678</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06966213108555436</v>
+        <v>0.06894031086881958</v>
       </c>
       <c r="C34">
-        <v>32540.85211153364</v>
+        <v>33088.53420047883</v>
       </c>
       <c r="D34">
-        <v>48171.40811153364</v>
+        <v>48719.09020047884</v>
       </c>
       <c r="E34">
         <v>-17762.944</v>
@@ -4081,45 +4081,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M34">
-        <v>916.670464</v>
+        <v>867.9976959999999</v>
       </c>
       <c r="N34">
-        <v>4002.804535999999</v>
+        <v>4051.477303999999</v>
       </c>
       <c r="O34">
-        <v>1060.74320204</v>
+        <v>1073.64148556</v>
       </c>
       <c r="P34">
-        <v>2942.061333959999</v>
+        <v>2977.835818439999</v>
       </c>
       <c r="Q34">
-        <v>6357.461333959999</v>
+        <v>6393.235818439999</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08290195747875642</v>
+        <v>0.08287810421885232</v>
       </c>
       <c r="T34">
         <v>0.8563072567864277</v>
       </c>
       <c r="U34">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.265</v>
       </c>
       <c r="W34">
-        <v>0.0415275</v>
+        <v>0.0393225</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.366677768293403</v>
+        <v>5.667612970253781</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06954635349882281</v>
+        <v>0.06899657024840614</v>
       </c>
       <c r="C35">
-        <v>32122.65934722044</v>
+        <v>32537.50205859626</v>
       </c>
       <c r="D35">
-        <v>48260.22334722044</v>
+        <v>48675.06605859626</v>
       </c>
       <c r="E35">
         <v>-17255.936</v>
@@ -4163,37 +4163,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M35">
-        <v>945.316416</v>
+        <v>908.5076352</v>
       </c>
       <c r="N35">
-        <v>3974.158583999998</v>
+        <v>4010.967364799998</v>
       </c>
       <c r="O35">
-        <v>1053.15202476</v>
+        <v>1062.906351672</v>
       </c>
       <c r="P35">
-        <v>2921.006559239999</v>
+        <v>2948.061013127999</v>
       </c>
       <c r="Q35">
-        <v>6336.406559239998</v>
+        <v>6363.461013127999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08334668432660121</v>
+        <v>0.08332254514687484</v>
       </c>
       <c r="T35">
         <v>0.866571481452075</v>
       </c>
       <c r="U35">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.265</v>
       </c>
       <c r="W35">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.20405116925421</v>
+        <v>5.414896704656774</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06943057591209124</v>
+        <v>0.0688646696279927</v>
       </c>
       <c r="C36">
-        <v>31704.79469109018</v>
+        <v>32133.83472082702</v>
       </c>
       <c r="D36">
-        <v>48349.36669109019</v>
+        <v>48778.40672082702</v>
       </c>
       <c r="E36">
         <v>-16748.928</v>
@@ -4245,37 +4245,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M36">
-        <v>973.9623680000001</v>
+        <v>936.0381696000001</v>
       </c>
       <c r="N36">
-        <v>3945.512631999999</v>
+        <v>3983.436830399999</v>
       </c>
       <c r="O36">
-        <v>1045.56084748</v>
+        <v>1055.610760056</v>
       </c>
       <c r="P36">
-        <v>2899.951784519999</v>
+        <v>2927.826070343999</v>
       </c>
       <c r="Q36">
-        <v>6315.351784519999</v>
+        <v>6343.226070343999</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.0838048877455928</v>
+        <v>0.08378045398180714</v>
       </c>
       <c r="T36">
         <v>0.8771467432288024</v>
       </c>
       <c r="U36">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.265</v>
       </c>
       <c r="W36">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.050990840746732</v>
+        <v>5.255635036872751</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06931479832535969</v>
+        <v>0.06873276900757928</v>
       </c>
       <c r="C37">
-        <v>31287.25996469186</v>
+        <v>31730.60711594282</v>
       </c>
       <c r="D37">
-        <v>48438.83996469186</v>
+        <v>48882.18711594282</v>
       </c>
       <c r="E37">
         <v>-16241.92</v>
@@ -4327,37 +4327,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M37">
-        <v>1002.60832</v>
+        <v>963.5687039999999</v>
       </c>
       <c r="N37">
-        <v>3916.866679999999</v>
+        <v>3955.906295999999</v>
       </c>
       <c r="O37">
-        <v>1037.9696702</v>
+        <v>1048.31516844</v>
       </c>
       <c r="P37">
-        <v>2878.897009799999</v>
+        <v>2907.591127559999</v>
       </c>
       <c r="Q37">
-        <v>6294.297009799999</v>
+        <v>6322.991127559999</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08427718973132262</v>
+        <v>0.08425245231935274</v>
       </c>
       <c r="T37">
         <v>0.8880473976755831</v>
       </c>
       <c r="U37">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.265</v>
       </c>
       <c r="W37">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.906676816725398</v>
+        <v>5.105474035819245</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06919902073862814</v>
+        <v>0.06860086838716585</v>
       </c>
       <c r="C38">
-        <v>30870.05700308298</v>
+        <v>31327.82205664031</v>
       </c>
       <c r="D38">
-        <v>48528.64500308298</v>
+        <v>48986.41005664031</v>
       </c>
       <c r="E38">
         <v>-15734.912</v>
@@ -4409,37 +4409,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M38">
-        <v>1031.254272</v>
+        <v>991.0992383999999</v>
       </c>
       <c r="N38">
-        <v>3888.220727999998</v>
+        <v>3928.375761599998</v>
       </c>
       <c r="O38">
-        <v>1030.37849292</v>
+        <v>1041.019576824</v>
       </c>
       <c r="P38">
-        <v>2857.842235079999</v>
+        <v>2887.356184775999</v>
       </c>
       <c r="Q38">
-        <v>6273.242235079999</v>
+        <v>6302.756184775999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08476425115410648</v>
+        <v>0.08473920060494665</v>
       </c>
       <c r="T38">
         <v>0.8992886975738257</v>
       </c>
       <c r="U38">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.265</v>
       </c>
       <c r="W38">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.770380238483026</v>
+        <v>4.963655312602043</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0690832431518966</v>
+        <v>0.06846896776675242</v>
       </c>
       <c r="C39">
-        <v>30453.18765495502</v>
+        <v>30925.48237965547</v>
       </c>
       <c r="D39">
-        <v>48618.78365495502</v>
+        <v>49091.07837965548</v>
       </c>
       <c r="E39">
         <v>-15227.904</v>
@@ -4491,37 +4491,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M39">
-        <v>1059.900224</v>
+        <v>1018.6297728</v>
       </c>
       <c r="N39">
-        <v>3859.574775999999</v>
+        <v>3900.845227199999</v>
       </c>
       <c r="O39">
-        <v>1022.78731564</v>
+        <v>1033.723985208</v>
       </c>
       <c r="P39">
-        <v>2836.787460359999</v>
+        <v>2867.121241991999</v>
       </c>
       <c r="Q39">
-        <v>6252.187460359999</v>
+        <v>6282.521241991999</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.0852667748442803</v>
+        <v>0.08524140121706733</v>
       </c>
       <c r="T39">
         <v>0.9108868641355043</v>
       </c>
       <c r="U39">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.265</v>
       </c>
       <c r="W39">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.641451042848349</v>
+        <v>4.829502466315502</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06896746556516503</v>
+        <v>0.068337067146339</v>
       </c>
       <c r="C40">
-        <v>30036.65378276029</v>
+        <v>30523.59094602098</v>
       </c>
       <c r="D40">
-        <v>48709.25778276029</v>
+        <v>49196.19494602098</v>
       </c>
       <c r="E40">
         <v>-14720.896</v>
@@ -4573,37 +4573,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M40">
-        <v>1088.546176</v>
+        <v>1046.1603072</v>
       </c>
       <c r="N40">
-        <v>3830.928823999999</v>
+        <v>3873.314692799999</v>
       </c>
       <c r="O40">
-        <v>1015.19613836</v>
+        <v>1026.428393592</v>
       </c>
       <c r="P40">
-        <v>2815.732685639999</v>
+        <v>2846.886299207999</v>
       </c>
       <c r="Q40">
-        <v>6231.132685639999</v>
+        <v>6262.286299207999</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08578550897607262</v>
+        <v>0.08575980184893386</v>
       </c>
       <c r="T40">
         <v>0.9228591651023985</v>
       </c>
       <c r="U40">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.265</v>
       </c>
       <c r="W40">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.519307594352339</v>
+        <v>4.702410296149304</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06885168797843348</v>
+        <v>0.06820516652592556</v>
       </c>
       <c r="C41">
-        <v>29620.45726284022</v>
+        <v>30122.15064132692</v>
       </c>
       <c r="D41">
-        <v>48800.06926284022</v>
+        <v>49301.76264132692</v>
       </c>
       <c r="E41">
         <v>-14213.888</v>
@@ -4655,37 +4655,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M41">
-        <v>1117.192128</v>
+        <v>1073.6908416</v>
       </c>
       <c r="N41">
-        <v>3802.282871999999</v>
+        <v>3845.784158399999</v>
       </c>
       <c r="O41">
-        <v>1007.60496108</v>
+        <v>1019.132801976</v>
       </c>
       <c r="P41">
-        <v>2794.677910919999</v>
+        <v>2826.651356423999</v>
       </c>
       <c r="Q41">
-        <v>6210.077910919999</v>
+        <v>6242.051356423999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08632125078431718</v>
+        <v>0.08629519922282879</v>
       </c>
       <c r="T41">
         <v>0.9352240005272238</v>
       </c>
       <c r="U41">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.265</v>
       </c>
       <c r="W41">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.403427912445871</v>
+        <v>4.581835673171117</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06873591039170193</v>
+        <v>0.06807326590551213</v>
       </c>
       <c r="C42">
-        <v>29204.59998555505</v>
+        <v>29721.16437598482</v>
       </c>
       <c r="D42">
-        <v>48891.21998555505</v>
+        <v>49407.78437598483</v>
       </c>
       <c r="E42">
         <v>-13706.88</v>
@@ -4737,37 +4737,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M42">
-        <v>1145.83808</v>
+        <v>1101.221376</v>
       </c>
       <c r="N42">
-        <v>3773.636919999999</v>
+        <v>3818.253623999999</v>
       </c>
       <c r="O42">
-        <v>1000.0137838</v>
+        <v>1011.83721036</v>
       </c>
       <c r="P42">
-        <v>2773.623136199999</v>
+        <v>2806.416413639999</v>
       </c>
       <c r="Q42">
-        <v>6189.023136199999</v>
+        <v>6221.816413639999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08687485065283654</v>
+        <v>0.08684844317585355</v>
       </c>
       <c r="T42">
         <v>0.9480009971328764</v>
       </c>
       <c r="U42">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.265</v>
       </c>
       <c r="W42">
-        <v>0.0415275</v>
+        <v>0.0399105</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.293342214634723</v>
+        <v>4.467289781341838</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06904202280497036</v>
+        <v>0.0679413652850987</v>
       </c>
       <c r="C43">
-        <v>28457.32864519994</v>
+        <v>29320.63508549514</v>
       </c>
       <c r="D43">
-        <v>48650.95664519995</v>
+        <v>49514.26308549514</v>
       </c>
       <c r="E43">
         <v>-13199.872</v>
@@ -4819,45 +4819,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M43">
-        <v>1203.5862912</v>
+        <v>1128.7519104</v>
       </c>
       <c r="N43">
-        <v>3715.888708799998</v>
+        <v>3790.723089599998</v>
       </c>
       <c r="O43">
-        <v>984.7105078319996</v>
+        <v>1004.541618744</v>
       </c>
       <c r="P43">
-        <v>2731.178200967999</v>
+        <v>2786.181470855999</v>
       </c>
       <c r="Q43">
-        <v>6146.578200967999</v>
+        <v>6201.581470855999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08744721661859384</v>
+        <v>0.08742044116118423</v>
       </c>
       <c r="T43">
         <v>0.9612111122675343</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.265</v>
       </c>
       <c r="W43">
-        <v>0.0425565</v>
+        <v>0.0399105</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.087347152396678</v>
+        <v>4.358331493992037</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06893653521823881</v>
+        <v>0.06780946466468527</v>
       </c>
       <c r="C44">
-        <v>28032.84925394662</v>
+        <v>28920.56573071814</v>
       </c>
       <c r="D44">
-        <v>48733.48525394662</v>
+        <v>49621.20173071814</v>
       </c>
       <c r="E44">
         <v>-12692.864</v>
@@ -4901,45 +4901,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M44">
-        <v>1232.9420544</v>
+        <v>1156.2824448</v>
       </c>
       <c r="N44">
-        <v>3686.532945599999</v>
+        <v>3763.192555199998</v>
       </c>
       <c r="O44">
-        <v>976.9312305839998</v>
+        <v>997.2460271279996</v>
       </c>
       <c r="P44">
-        <v>2709.601715015999</v>
+        <v>2765.946528071999</v>
       </c>
       <c r="Q44">
-        <v>6125.001715015999</v>
+        <v>6181.346528071999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08803931934179106</v>
+        <v>0.0880121632149746</v>
       </c>
       <c r="T44">
         <v>0.9748767486137322</v>
       </c>
       <c r="U44">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.265</v>
       </c>
       <c r="W44">
-        <v>0.0425565</v>
+        <v>0.0399105</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.990029363053901</v>
+        <v>4.254561696516037</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06883104763150727</v>
+        <v>0.06799361404427184</v>
       </c>
       <c r="C45">
-        <v>27608.65033177729</v>
+        <v>28264.38566358005</v>
       </c>
       <c r="D45">
-        <v>48816.2943317773</v>
+        <v>49472.02966358005</v>
       </c>
       <c r="E45">
         <v>-12185.856</v>
@@ -4983,37 +4983,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M45">
-        <v>1262.2978176</v>
+        <v>1205.6143232</v>
       </c>
       <c r="N45">
-        <v>3657.177182399999</v>
+        <v>3713.860676799999</v>
       </c>
       <c r="O45">
-        <v>969.1519533359998</v>
+        <v>984.1730793519997</v>
       </c>
       <c r="P45">
-        <v>2688.025229063999</v>
+        <v>2729.687597447999</v>
       </c>
       <c r="Q45">
-        <v>6103.425229064</v>
+        <v>6145.087597447999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08865219759913553</v>
+        <v>0.08862464744609094</v>
       </c>
       <c r="T45">
         <v>0.9890218809720772</v>
       </c>
       <c r="U45">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.265</v>
       </c>
       <c r="W45">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.897237982517763</v>
+        <v>4.080471594715704</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06872556004477572</v>
+        <v>0.06786906342385841</v>
       </c>
       <c r="C46">
-        <v>27184.73331086446</v>
+        <v>27858.17278959253</v>
       </c>
       <c r="D46">
-        <v>48899.38531086446</v>
+        <v>49572.82478959253</v>
       </c>
       <c r="E46">
         <v>-11678.848</v>
@@ -5065,37 +5065,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M46">
-        <v>1291.6535808</v>
+        <v>1233.6518656</v>
       </c>
       <c r="N46">
-        <v>3627.821419199999</v>
+        <v>3685.823134399999</v>
       </c>
       <c r="O46">
-        <v>961.3726760879997</v>
+        <v>976.7431306159997</v>
       </c>
       <c r="P46">
-        <v>2666.448743111999</v>
+        <v>2709.080003783999</v>
       </c>
       <c r="Q46">
-        <v>6081.848743111999</v>
+        <v>6124.480003784</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08928696436567091</v>
+        <v>0.08925900611403287</v>
       </c>
       <c r="T46">
         <v>1.003672196628935</v>
       </c>
       <c r="U46">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.265</v>
       </c>
       <c r="W46">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.808664392005995</v>
+        <v>3.987733603926711</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06862007245804416</v>
+        <v>0.06774451280344498</v>
       </c>
       <c r="C47">
-        <v>26761.09963314807</v>
+        <v>27452.37147741922</v>
       </c>
       <c r="D47">
-        <v>48982.75963314807</v>
+        <v>49674.03147741922</v>
       </c>
       <c r="E47">
         <v>-11171.84</v>
@@ -5147,37 +5147,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M47">
-        <v>1321.009344</v>
+        <v>1261.689408</v>
       </c>
       <c r="N47">
-        <v>3598.465655999998</v>
+        <v>3657.785591999998</v>
       </c>
       <c r="O47">
-        <v>953.5933988399996</v>
+        <v>969.3131818799997</v>
       </c>
       <c r="P47">
-        <v>2644.872257159999</v>
+        <v>2688.472410119999</v>
       </c>
       <c r="Q47">
-        <v>6060.272257159999</v>
+        <v>6103.872410119999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08994481356008027</v>
+        <v>0.08991643236989995</v>
       </c>
       <c r="T47">
         <v>1.01885525103695</v>
       </c>
       <c r="U47">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.265</v>
       </c>
       <c r="W47">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.724027405516973</v>
+        <v>3.899117301617228</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06851458487131259</v>
+        <v>0.06761996218303154</v>
       </c>
       <c r="C48">
-        <v>26337.75075041906</v>
+        <v>27046.98425292098</v>
       </c>
       <c r="D48">
-        <v>49066.41875041906</v>
+        <v>49775.65225292098</v>
       </c>
       <c r="E48">
         <v>-10664.832</v>
@@ -5229,37 +5229,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M48">
-        <v>1350.3651072</v>
+        <v>1289.7269504</v>
       </c>
       <c r="N48">
-        <v>3569.109892799998</v>
+        <v>3629.748049599998</v>
       </c>
       <c r="O48">
-        <v>945.8141215919997</v>
+        <v>961.8832331439996</v>
       </c>
       <c r="P48">
-        <v>2623.295771207999</v>
+        <v>2667.864816455999</v>
       </c>
       <c r="Q48">
-        <v>6038.695771207998</v>
+        <v>6083.264816456</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09062702753946777</v>
+        <v>0.09059820774635471</v>
       </c>
       <c r="T48">
         <v>1.034600640793411</v>
       </c>
       <c r="U48">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.265</v>
       </c>
       <c r="W48">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.643070288005734</v>
+        <v>3.814353882016854</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06840909728458104</v>
+        <v>0.06749541156261812</v>
       </c>
       <c r="C49">
-        <v>25914.6881244035</v>
+        <v>26642.01366267018</v>
       </c>
       <c r="D49">
-        <v>49150.3641244035</v>
+        <v>49877.68966267018</v>
       </c>
       <c r="E49">
         <v>-10157.824</v>
@@ -5311,37 +5311,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M49">
-        <v>1379.7208704</v>
+        <v>1317.7644928</v>
       </c>
       <c r="N49">
-        <v>3539.754129599999</v>
+        <v>3601.710507199999</v>
       </c>
       <c r="O49">
-        <v>938.0348443439997</v>
+        <v>954.4532844079997</v>
       </c>
       <c r="P49">
-        <v>2601.719285255999</v>
+        <v>2647.257222791999</v>
       </c>
       <c r="Q49">
-        <v>6017.119285255999</v>
+        <v>6062.657222791999</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09133498544260574</v>
+        <v>0.09130571049550587</v>
       </c>
       <c r="T49">
         <v>1.05094019620106</v>
       </c>
       <c r="U49">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.265</v>
       </c>
       <c r="W49">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.565558154218379</v>
+        <v>3.733197416442028</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06830360969784947</v>
+        <v>0.06737086094220468</v>
       </c>
       <c r="C50">
-        <v>25491.91322684785</v>
+        <v>26237.46227416347</v>
       </c>
       <c r="D50">
-        <v>49234.59722684785</v>
+        <v>49980.14627416347</v>
       </c>
       <c r="E50">
         <v>-9650.815999999999</v>
@@ -5393,37 +5393,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M50">
-        <v>1409.0766336</v>
+        <v>1345.8020352</v>
       </c>
       <c r="N50">
-        <v>3510.398366399999</v>
+        <v>3573.672964799999</v>
       </c>
       <c r="O50">
-        <v>930.2555670959997</v>
+        <v>947.0233356719997</v>
       </c>
       <c r="P50">
-        <v>2580.142799303999</v>
+        <v>2626.649629127999</v>
       </c>
       <c r="Q50">
-        <v>5995.542799303999</v>
+        <v>6042.049629128</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09207017249586438</v>
+        <v>0.09204042488885517</v>
       </c>
       <c r="T50">
         <v>1.067908196047463</v>
       </c>
       <c r="U50">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.265</v>
       </c>
       <c r="W50">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.491275692672163</v>
+        <v>3.655422470266152</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06819812211111792</v>
+        <v>0.06724631032179125</v>
       </c>
       <c r="C51">
-        <v>25069.42753960488</v>
+        <v>25833.33267603704</v>
       </c>
       <c r="D51">
-        <v>49319.11953960488</v>
+        <v>50083.02467603704</v>
       </c>
       <c r="E51">
         <v>-9143.808000000001</v>
@@ -5475,37 +5475,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M51">
-        <v>1438.4323968</v>
+        <v>1373.8395776</v>
       </c>
       <c r="N51">
-        <v>3481.042603199999</v>
+        <v>3545.635422399999</v>
       </c>
       <c r="O51">
-        <v>922.4762898479997</v>
+        <v>939.5933869359998</v>
       </c>
       <c r="P51">
-        <v>2558.566313351999</v>
+        <v>2606.042035463999</v>
       </c>
       <c r="Q51">
-        <v>5973.966313351999</v>
+        <v>6021.442035463999</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09283419041395671</v>
+        <v>0.09280395161135539</v>
       </c>
       <c r="T51">
         <v>1.085541607652549</v>
       </c>
       <c r="U51">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.265</v>
       </c>
       <c r="W51">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.420025168331915</v>
+        <v>3.580822011689292</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06809263452438637</v>
+        <v>0.06712175970137782</v>
       </c>
       <c r="C52">
-        <v>24647.23255472059</v>
+        <v>25429.62747828471</v>
       </c>
       <c r="D52">
-        <v>49403.93255472059</v>
+        <v>50186.32747828471</v>
       </c>
       <c r="E52">
         <v>-8636.799999999999</v>
@@ -5557,37 +5557,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M52">
-        <v>1467.78816</v>
+        <v>1401.87712</v>
       </c>
       <c r="N52">
-        <v>3451.686839999998</v>
+        <v>3517.597879999998</v>
       </c>
       <c r="O52">
-        <v>914.6970125999997</v>
+        <v>932.1634381999996</v>
       </c>
       <c r="P52">
-        <v>2536.989827399999</v>
+        <v>2585.434441799999</v>
       </c>
       <c r="Q52">
-        <v>5952.389827399998</v>
+        <v>6000.834441799999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09362876904877274</v>
+        <v>0.09359801940275564</v>
       </c>
       <c r="T52">
         <v>1.103880355721839</v>
       </c>
       <c r="U52">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.265</v>
       </c>
       <c r="W52">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.351624664965276</v>
+        <v>3.509205571455506</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06798714693765483</v>
+        <v>0.0669972090809644</v>
       </c>
       <c r="C53">
-        <v>24225.32977452204</v>
+        <v>25026.34931247859</v>
       </c>
       <c r="D53">
-        <v>49489.03777452205</v>
+        <v>50290.0573124786</v>
       </c>
       <c r="E53">
         <v>-8129.791999999998</v>
@@ -5639,37 +5639,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M53">
-        <v>1497.1439232</v>
+        <v>1429.9146624</v>
       </c>
       <c r="N53">
-        <v>3422.331076799998</v>
+        <v>3489.560337599999</v>
       </c>
       <c r="O53">
-        <v>906.9177353519996</v>
+        <v>924.7334894639997</v>
       </c>
       <c r="P53">
-        <v>2515.413341447999</v>
+        <v>2564.826848135999</v>
       </c>
       <c r="Q53">
-        <v>5930.813341447999</v>
+        <v>5980.226848135999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09445577946460168</v>
+        <v>0.09442449812441714</v>
       </c>
       <c r="T53">
         <v>1.122967624120488</v>
       </c>
       <c r="U53">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.265</v>
       </c>
       <c r="W53">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.285906534279682</v>
+        <v>3.440397619074025</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06788165935092326</v>
+        <v>0.06687265846055096</v>
       </c>
       <c r="C54">
-        <v>23803.72071170607</v>
+        <v>24623.50083199269</v>
       </c>
       <c r="D54">
-        <v>49574.43671170607</v>
+        <v>50394.21683199269</v>
       </c>
       <c r="E54">
         <v>-7622.784</v>
@@ -5721,37 +5721,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M54">
-        <v>1526.4996864</v>
+        <v>1457.9522048</v>
       </c>
       <c r="N54">
-        <v>3392.975313599999</v>
+        <v>3461.522795199999</v>
       </c>
       <c r="O54">
-        <v>899.1384581039998</v>
+        <v>917.3035407279997</v>
       </c>
       <c r="P54">
-        <v>2493.836855495999</v>
+        <v>2544.219254471999</v>
       </c>
       <c r="Q54">
-        <v>5909.236855495999</v>
+        <v>5959.619254472</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.0953172486477568</v>
+        <v>0.09528541345948116</v>
       </c>
       <c r="T54">
         <v>1.14285019536908</v>
       </c>
       <c r="U54">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.265</v>
       </c>
       <c r="W54">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.222716024005074</v>
+        <v>3.374236126399525</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06777617176419171</v>
+        <v>0.06674810784013753</v>
       </c>
       <c r="C55">
-        <v>23382.40688942878</v>
+        <v>24221.08471222891</v>
       </c>
       <c r="D55">
-        <v>49660.13088942878</v>
+        <v>50498.80871222891</v>
       </c>
       <c r="E55">
         <v>-7115.775999999998</v>
@@ -5803,37 +5803,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M55">
-        <v>1555.8554496</v>
+        <v>1485.9897472</v>
       </c>
       <c r="N55">
-        <v>3363.619550399999</v>
+        <v>3433.485252799998</v>
       </c>
       <c r="O55">
-        <v>891.3591808559997</v>
+        <v>909.8735919919995</v>
       </c>
       <c r="P55">
-        <v>2472.260369543999</v>
+        <v>2523.611660807999</v>
       </c>
       <c r="Q55">
-        <v>5887.660369543999</v>
+        <v>5939.011660807999</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09621537609402492</v>
+        <v>0.09618296348965433</v>
       </c>
       <c r="T55">
         <v>1.163578833479315</v>
       </c>
       <c r="U55">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.265</v>
       </c>
       <c r="W55">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.161910061287996</v>
+        <v>3.310571293825948</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.06767068417746015</v>
+        <v>0.0666235572197241</v>
       </c>
       <c r="C56">
-        <v>22961.38984139628</v>
+        <v>23819.10365084631</v>
       </c>
       <c r="D56">
-        <v>49746.12184139629</v>
+        <v>50603.83565084632</v>
       </c>
       <c r="E56">
         <v>-6608.767999999996</v>
@@ -5885,37 +5885,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M56">
-        <v>1585.2112128</v>
+        <v>1514.0272896</v>
       </c>
       <c r="N56">
-        <v>3334.263787199999</v>
+        <v>3405.447710399998</v>
       </c>
       <c r="O56">
-        <v>883.5799036079997</v>
+        <v>902.4436432559996</v>
       </c>
       <c r="P56">
-        <v>2450.683883591999</v>
+        <v>2503.004067143999</v>
       </c>
       <c r="Q56">
-        <v>5866.083883591999</v>
+        <v>5918.404067143999</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09715255255969599</v>
+        <v>0.09711953743418283</v>
       </c>
       <c r="T56">
         <v>1.185208716724777</v>
       </c>
       <c r="U56">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.265</v>
       </c>
       <c r="W56">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.103356171264144</v>
+        <v>3.249264418014357</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0675651965907286</v>
+        <v>0.06649900659931067</v>
       </c>
       <c r="C57">
-        <v>22540.67111195609</v>
+        <v>23417.56036799305</v>
       </c>
       <c r="D57">
-        <v>49832.41111195609</v>
+        <v>50709.30036799305</v>
       </c>
       <c r="E57">
         <v>-6101.759999999998</v>
@@ -5967,37 +5967,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M57">
-        <v>1614.566976</v>
+        <v>1542.064832</v>
       </c>
       <c r="N57">
-        <v>3304.908023999998</v>
+        <v>3377.410167999999</v>
       </c>
       <c r="O57">
-        <v>875.8006263599997</v>
+        <v>895.0136945199996</v>
       </c>
       <c r="P57">
-        <v>2429.107397639999</v>
+        <v>2482.396473479999</v>
       </c>
       <c r="Q57">
-        <v>5844.507397639999</v>
+        <v>5897.796473479999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09813138131273022</v>
+        <v>0.09809773688735704</v>
       </c>
       <c r="T57">
         <v>1.207799928114481</v>
       </c>
       <c r="U57">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V57">
         <v>0.265</v>
       </c>
       <c r="W57">
-        <v>0.0425565</v>
+        <v>0.0406455</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.046931513604796</v>
+        <v>3.190186883141369</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06852986900399705</v>
+        <v>0.06637445597889723</v>
       </c>
       <c r="C58">
-        <v>21255.53165364835</v>
+        <v>23016.45760654103</v>
       </c>
       <c r="D58">
-        <v>49054.27965364835</v>
+        <v>50815.20560654104</v>
       </c>
       <c r="E58">
         <v>-5594.751999999997</v>
@@ -6049,45 +6049,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M58">
-        <v>1717.743104</v>
+        <v>1570.1023744</v>
       </c>
       <c r="N58">
-        <v>3201.731895999998</v>
+        <v>3349.372625599998</v>
       </c>
       <c r="O58">
-        <v>848.4589524399996</v>
+        <v>887.5837457839996</v>
       </c>
       <c r="P58">
-        <v>2353.272943559999</v>
+        <v>2461.788879815998</v>
       </c>
       <c r="Q58">
-        <v>5768.672943559999</v>
+        <v>5877.188879815998</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09915470228181147</v>
+        <v>0.09912039995203917</v>
       </c>
       <c r="T58">
         <v>1.231418012749173</v>
       </c>
       <c r="U58">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.265</v>
       </c>
       <c r="W58">
-        <v>0.0444675</v>
+        <v>0.0406455</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.86391777009282</v>
+        <v>3.13321926022813</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0684434914172655</v>
+        <v>0.06624990535848381</v>
       </c>
       <c r="C59">
-        <v>20817.20626958846</v>
+        <v>22615.79813232393</v>
       </c>
       <c r="D59">
-        <v>49122.96226958846</v>
+        <v>50921.55413232393</v>
       </c>
       <c r="E59">
         <v>-5087.743999999995</v>
@@ -6131,45 +6131,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M59">
-        <v>1748.417088</v>
+        <v>1598.1399168</v>
       </c>
       <c r="N59">
-        <v>3171.057911999998</v>
+        <v>3321.335083199998</v>
       </c>
       <c r="O59">
-        <v>840.3303466799996</v>
+        <v>880.1537970479995</v>
       </c>
       <c r="P59">
-        <v>2330.727565319999</v>
+        <v>2441.181286151999</v>
       </c>
       <c r="Q59">
-        <v>5746.127565319999</v>
+        <v>5856.581286151999</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.100225619575036</v>
+        <v>0.10019062874066</v>
       </c>
       <c r="T59">
         <v>1.256134612948268</v>
       </c>
       <c r="U59">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.265</v>
       </c>
       <c r="W59">
-        <v>0.0444675</v>
+        <v>0.0406455</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.813673598687682</v>
+        <v>3.078250501276759</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.06835711383053394</v>
+        <v>0.06612535473807038</v>
       </c>
       <c r="C60">
-        <v>20379.07348506875</v>
+        <v>22215.58473437781</v>
       </c>
       <c r="D60">
-        <v>49191.83748506875</v>
+        <v>51028.34873437781</v>
       </c>
       <c r="E60">
         <v>-4580.736000000001</v>
@@ -6213,45 +6213,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M60">
-        <v>1779.091072</v>
+        <v>1626.1774592</v>
       </c>
       <c r="N60">
-        <v>3140.383927999999</v>
+        <v>3293.297540799998</v>
       </c>
       <c r="O60">
-        <v>832.2017409199997</v>
+        <v>872.7238483119996</v>
       </c>
       <c r="P60">
-        <v>2308.182187079999</v>
+        <v>2420.573692487999</v>
       </c>
       <c r="Q60">
-        <v>5723.582187079999</v>
+        <v>5835.973692487999</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1013475329298427</v>
+        <v>0.1013118208049295</v>
       </c>
       <c r="T60">
         <v>1.282028194109225</v>
       </c>
       <c r="U60">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.265</v>
       </c>
       <c r="W60">
-        <v>0.0444675</v>
+        <v>0.0406455</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.765161984917206</v>
+        <v>3.025177216771988</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.06827073624380238</v>
+        <v>0.06708492911765694</v>
       </c>
       <c r="C61">
-        <v>19941.13411135709</v>
+        <v>20897.18460740894</v>
       </c>
       <c r="D61">
-        <v>49260.90611135709</v>
+        <v>50216.95660740894</v>
       </c>
       <c r="E61">
         <v>-4073.728000000003</v>
@@ -6295,37 +6295,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M61">
-        <v>1809.765056</v>
+        <v>1728.9986816</v>
       </c>
       <c r="N61">
-        <v>3109.709943999999</v>
+        <v>3190.476318399998</v>
       </c>
       <c r="O61">
-        <v>824.0731351599999</v>
+        <v>845.4762243759997</v>
       </c>
       <c r="P61">
-        <v>2285.63680884</v>
+        <v>2345.000094023999</v>
       </c>
       <c r="Q61">
-        <v>5701.036808839999</v>
+        <v>5760.400094023998</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1025241737653717</v>
+        <v>0.1024877051650169</v>
       </c>
       <c r="T61">
         <v>1.309184876790229</v>
       </c>
       <c r="U61">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.265</v>
       </c>
       <c r="W61">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.718294832630474</v>
+        <v>2.845274003012865</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.06818435865707083</v>
+        <v>0.06697875349724353</v>
       </c>
       <c r="C62">
-        <v>19503.38896428403</v>
+        <v>20478.68421444348</v>
       </c>
       <c r="D62">
-        <v>49330.16896428403</v>
+        <v>50305.46421444348</v>
       </c>
       <c r="E62">
         <v>-3566.720000000001</v>
@@ -6377,37 +6377,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M62">
-        <v>1840.43904</v>
+        <v>1758.303744</v>
       </c>
       <c r="N62">
-        <v>3079.035959999999</v>
+        <v>3161.171255999999</v>
       </c>
       <c r="O62">
-        <v>815.9445293999997</v>
+        <v>837.7103828399997</v>
       </c>
       <c r="P62">
-        <v>2263.091430599999</v>
+        <v>2323.460873159999</v>
       </c>
       <c r="Q62">
-        <v>5678.491430599999</v>
+        <v>5738.86087316</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1037596466426771</v>
+        <v>0.1037223837431088</v>
       </c>
       <c r="T62">
         <v>1.337699393605284</v>
       </c>
       <c r="U62">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V62">
         <v>0.265</v>
       </c>
       <c r="W62">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.672989918753299</v>
+        <v>2.797852769629318</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.06809798107033926</v>
+        <v>0.06687257787683008</v>
       </c>
       <c r="C63">
-        <v>19065.83886427499</v>
+        <v>20060.49636242671</v>
       </c>
       <c r="D63">
-        <v>49399.62686427499</v>
+        <v>50394.28436242671</v>
       </c>
       <c r="E63">
         <v>-3059.712</v>
@@ -6459,37 +6459,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M63">
-        <v>1871.113024</v>
+        <v>1787.6088064</v>
       </c>
       <c r="N63">
-        <v>3048.361975999999</v>
+        <v>3131.866193599998</v>
       </c>
       <c r="O63">
-        <v>807.8159236399997</v>
+        <v>829.9445413039997</v>
       </c>
       <c r="P63">
-        <v>2240.546052359999</v>
+        <v>2301.921652295999</v>
       </c>
       <c r="Q63">
-        <v>5655.946052359999</v>
+        <v>5717.321652295999</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.105058477103434</v>
+        <v>0.1050203791713592</v>
       </c>
       <c r="T63">
         <v>1.367676193333931</v>
       </c>
       <c r="U63">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.265</v>
       </c>
       <c r="W63">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.629170411888491</v>
+        <v>2.751986330782935</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.06801160348360771</v>
+        <v>0.06676640225641665</v>
       </c>
       <c r="C64">
-        <v>18628.48463638255</v>
+        <v>19642.62270976892</v>
       </c>
       <c r="D64">
-        <v>49469.28063638255</v>
+        <v>50483.41870976891</v>
       </c>
       <c r="E64">
         <v>-2552.704000000002</v>
@@ -6541,37 +6541,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M64">
-        <v>1901.787008</v>
+        <v>1816.9138688</v>
       </c>
       <c r="N64">
-        <v>3017.687991999999</v>
+        <v>3102.561131199999</v>
       </c>
       <c r="O64">
-        <v>799.6873178799997</v>
+        <v>822.1786997679997</v>
       </c>
       <c r="P64">
-        <v>2218.000674119999</v>
+        <v>2280.382431431999</v>
       </c>
       <c r="Q64">
-        <v>5633.400674119999</v>
+        <v>5695.782431431999</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1064256670621256</v>
+        <v>0.1063866901484649</v>
       </c>
       <c r="T64">
         <v>1.399230719364085</v>
       </c>
       <c r="U64">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.265</v>
       </c>
       <c r="W64">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.586764437503192</v>
+        <v>2.707599454479985</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.06792522589687616</v>
+        <v>0.06666022663600323</v>
       </c>
       <c r="C65">
-        <v>18191.32711031923</v>
+        <v>19225.06492663437</v>
       </c>
       <c r="D65">
-        <v>49539.13111031923</v>
+        <v>50572.86892663437</v>
       </c>
       <c r="E65">
         <v>-2045.696</v>
@@ -6623,37 +6623,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M65">
-        <v>1932.460992</v>
+        <v>1846.2189312</v>
       </c>
       <c r="N65">
-        <v>2987.014007999999</v>
+        <v>3073.256068799999</v>
       </c>
       <c r="O65">
-        <v>791.5587121199997</v>
+        <v>814.4128582319996</v>
       </c>
       <c r="P65">
-        <v>2195.455295879999</v>
+        <v>2258.843210567999</v>
       </c>
       <c r="Q65">
-        <v>5610.855295879999</v>
+        <v>5674.243210567999</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1078667591807464</v>
+        <v>0.1078268557729817</v>
       </c>
       <c r="T65">
         <v>1.432490895449923</v>
       </c>
       <c r="U65">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.265</v>
       </c>
       <c r="W65">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.545704684526951</v>
+        <v>2.664621685361255</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.0678388483101446</v>
+        <v>0.0665540510155898</v>
       </c>
       <c r="C66">
-        <v>17754.36712049038</v>
+        <v>18807.82469504563</v>
       </c>
       <c r="D66">
-        <v>49609.17912049039</v>
+        <v>50662.63669504564</v>
       </c>
       <c r="E66">
         <v>-1538.687999999998</v>
@@ -6705,37 +6705,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M66">
-        <v>1963.134976</v>
+        <v>1875.5239936</v>
       </c>
       <c r="N66">
-        <v>2956.340023999999</v>
+        <v>3043.951006399999</v>
       </c>
       <c r="O66">
-        <v>783.4301063599997</v>
+        <v>806.6470166959997</v>
       </c>
       <c r="P66">
-        <v>2172.909917639999</v>
+        <v>2237.303989703999</v>
       </c>
       <c r="Q66">
-        <v>5588.309917639999</v>
+        <v>5652.703989703999</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1093879119726239</v>
+        <v>0.1093470305988605</v>
       </c>
       <c r="T66">
         <v>1.467598859096086</v>
       </c>
       <c r="U66">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.265</v>
       </c>
       <c r="W66">
-        <v>0.0444675</v>
+        <v>0.042483</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.505928048831217</v>
+        <v>2.622986971527485</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.06904239572341304</v>
+        <v>0.06644787539517637</v>
       </c>
       <c r="C67">
-        <v>16288.84538687902</v>
+        <v>18390.903708989</v>
       </c>
       <c r="D67">
-        <v>48650.66538687902</v>
+        <v>50752.723708989</v>
       </c>
       <c r="E67">
         <v>-1031.68</v>
@@ -6787,45 +6787,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M67">
-        <v>2082.788864</v>
+        <v>1904.829056</v>
       </c>
       <c r="N67">
-        <v>2836.686135999998</v>
+        <v>3014.645943999999</v>
       </c>
       <c r="O67">
-        <v>751.7218260399997</v>
+        <v>798.8811751599997</v>
       </c>
       <c r="P67">
-        <v>2084.964309959999</v>
+        <v>2215.764768839999</v>
       </c>
       <c r="Q67">
-        <v>5500.364309959999</v>
+        <v>5631.164768839999</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1109959877811801</v>
+        <v>0.1109540725576467</v>
       </c>
       <c r="T67">
         <v>1.504712992093458</v>
       </c>
       <c r="U67">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.265</v>
       </c>
       <c r="W67">
-        <v>0.046452</v>
+        <v>0.042483</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.361965288479667</v>
+        <v>2.582633325811678</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.0689758631366815</v>
+        <v>0.06634169977476292</v>
       </c>
       <c r="C68">
-        <v>15833.85619551357</v>
+        <v>17974.30367452102</v>
       </c>
       <c r="D68">
-        <v>48702.68419551357</v>
+        <v>50843.13167452102</v>
       </c>
       <c r="E68">
         <v>-524.6719999999987</v>
@@ -6869,45 +6869,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M68">
-        <v>2114.8317696</v>
+        <v>1934.1341184</v>
       </c>
       <c r="N68">
-        <v>2804.643230399999</v>
+        <v>2985.340881599998</v>
       </c>
       <c r="O68">
-        <v>743.2304560559996</v>
+        <v>791.1153336239996</v>
       </c>
       <c r="P68">
-        <v>2061.412774343999</v>
+        <v>2194.225547975999</v>
       </c>
       <c r="Q68">
-        <v>5476.812774343999</v>
+        <v>5609.625547975998</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1126986562843573</v>
+        <v>0.1126556463963616</v>
       </c>
       <c r="T68">
         <v>1.544010309384793</v>
       </c>
       <c r="U68">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.265</v>
       </c>
       <c r="W68">
-        <v>0.046452</v>
+        <v>0.042483</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.326177935623915</v>
+        <v>2.543502517844834</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.06890933054994995</v>
+        <v>0.0662355241543495</v>
       </c>
       <c r="C69">
-        <v>15378.97836348185</v>
+        <v>17558.02630987622</v>
       </c>
       <c r="D69">
-        <v>48754.81436348186</v>
+        <v>50933.86230987623</v>
       </c>
       <c r="E69">
         <v>-17.66399999999703</v>
@@ -6951,45 +6951,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M69">
-        <v>2146.8746752</v>
+        <v>1963.4391808</v>
       </c>
       <c r="N69">
-        <v>2772.600324799998</v>
+        <v>2956.035819199999</v>
       </c>
       <c r="O69">
-        <v>734.7390860719996</v>
+        <v>783.3494920879997</v>
       </c>
       <c r="P69">
-        <v>2037.861238727999</v>
+        <v>2172.686327111999</v>
       </c>
       <c r="Q69">
-        <v>5453.261238727999</v>
+        <v>5588.086327111999</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1145045168180301</v>
+        <v>0.1144603459222712</v>
       </c>
       <c r="T69">
         <v>1.585689282269543</v>
       </c>
       <c r="U69">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V69">
         <v>0.265</v>
       </c>
       <c r="W69">
-        <v>0.046452</v>
+        <v>0.042483</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.291458861957886</v>
+        <v>2.505539793697896</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.06884279796321838</v>
+        <v>0.06787864853393608</v>
       </c>
       <c r="C70">
-        <v>14924.21224875602</v>
+        <v>15682.20925846937</v>
       </c>
       <c r="D70">
-        <v>48807.05624875602</v>
+        <v>49565.05325846937</v>
       </c>
       <c r="E70">
         <v>489.3440000000046</v>
@@ -7033,37 +7033,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M70">
-        <v>2178.9175808</v>
+        <v>2113.4121472</v>
       </c>
       <c r="N70">
-        <v>2740.557419199998</v>
+        <v>2806.062852799998</v>
       </c>
       <c r="O70">
-        <v>726.2477160879995</v>
+        <v>743.6066559919996</v>
       </c>
       <c r="P70">
-        <v>2014.309703111999</v>
+        <v>2062.456196807999</v>
       </c>
       <c r="Q70">
-        <v>5429.709703111999</v>
+        <v>5477.856196807999</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1164232436350575</v>
+        <v>0.1163778391685502</v>
       </c>
       <c r="T70">
         <v>1.62997319095959</v>
       </c>
       <c r="U70">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.265</v>
       </c>
       <c r="W70">
-        <v>0.046452</v>
+        <v>0.0450555</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.257760937517329</v>
+        <v>2.327740477179367</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07115987037648683</v>
+        <v>0.06779819791352264</v>
       </c>
       <c r="C71">
-        <v>12661.39368488772</v>
+        <v>15240.5056852517</v>
       </c>
       <c r="D71">
-        <v>47051.24568488773</v>
+        <v>49630.35768525171</v>
       </c>
       <c r="E71">
         <v>996.3520000000062</v>
@@ -7115,45 +7115,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M71">
-        <v>2375.3831808</v>
+        <v>2144.4917376</v>
       </c>
       <c r="N71">
-        <v>2544.091819199998</v>
+        <v>2774.983262399998</v>
       </c>
       <c r="O71">
-        <v>674.1843320879996</v>
+        <v>735.3705645359996</v>
       </c>
       <c r="P71">
-        <v>1869.907487111999</v>
+        <v>2039.612697863999</v>
       </c>
       <c r="Q71">
-        <v>5285.307487111999</v>
+        <v>5455.012697863998</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1184657592789898</v>
+        <v>0.1184190416565246</v>
       </c>
       <c r="T71">
         <v>1.677114126016736</v>
       </c>
       <c r="U71">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.265</v>
       </c>
       <c r="W71">
-        <v>0.0499065</v>
+        <v>0.0450555</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.071023757246264</v>
+        <v>2.294005107944883</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07112788278975526</v>
+        <v>0.0677177472931092</v>
       </c>
       <c r="C72">
-        <v>12177.76456900079</v>
+        <v>14798.97442273291</v>
       </c>
       <c r="D72">
-        <v>47074.62456900079</v>
+        <v>49695.83442273291</v>
       </c>
       <c r="E72">
         <v>1503.360000000001</v>
@@ -7197,45 +7197,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M72">
-        <v>2409.809024</v>
+        <v>2175.571328</v>
       </c>
       <c r="N72">
-        <v>2509.665975999998</v>
+        <v>2743.903671999999</v>
       </c>
       <c r="O72">
-        <v>665.0614836399997</v>
+        <v>727.1344730799997</v>
       </c>
       <c r="P72">
-        <v>1844.604492359999</v>
+        <v>2016.769198919999</v>
       </c>
       <c r="Q72">
-        <v>5260.004492359999</v>
+        <v>5432.169198919999</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1206444426325176</v>
+        <v>0.120596324310364</v>
       </c>
       <c r="T72">
         <v>1.727397790077691</v>
       </c>
       <c r="U72">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.265</v>
       </c>
       <c r="W72">
-        <v>0.0499065</v>
+        <v>0.0450555</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.041437703571318</v>
+        <v>2.261233606402814</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07109589520302372</v>
+        <v>0.06909847667269578</v>
       </c>
       <c r="C73">
-        <v>11694.15869772431</v>
+        <v>13191.65640273778</v>
       </c>
       <c r="D73">
-        <v>47098.02669772431</v>
+        <v>48595.52440273778</v>
       </c>
       <c r="E73">
         <v>2010.367999999995</v>
@@ -7279,37 +7279,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M73">
-        <v>2444.234867199999</v>
+        <v>2307.4441088</v>
       </c>
       <c r="N73">
-        <v>2475.240132799999</v>
+        <v>2612.030891199999</v>
       </c>
       <c r="O73">
-        <v>655.9386351919998</v>
+        <v>692.1881861679997</v>
       </c>
       <c r="P73">
-        <v>1819.301497607999</v>
+        <v>1919.842705031999</v>
       </c>
       <c r="Q73">
-        <v>5234.701497607999</v>
+        <v>5335.242705031999</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1229733800104266</v>
+        <v>0.1229237643886061</v>
       </c>
       <c r="T73">
         <v>1.781149293039402</v>
       </c>
       <c r="U73">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.265</v>
       </c>
       <c r="W73">
-        <v>0.0499065</v>
+        <v>0.0471135</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.012685059859046</v>
+        <v>2.132001802877211</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07847270761629216</v>
+        <v>0.06903860605228235</v>
       </c>
       <c r="C74">
-        <v>6342.953264207616</v>
+        <v>12731.34806043953</v>
       </c>
       <c r="D74">
-        <v>42253.82926420761</v>
+        <v>48642.22406043953</v>
       </c>
       <c r="E74">
         <v>2517.375999999997</v>
@@ -7361,45 +7361,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M74">
-        <v>2989.7247744</v>
+        <v>2339.9433216</v>
       </c>
       <c r="N74">
-        <v>1929.750225599999</v>
+        <v>2579.531678399999</v>
       </c>
       <c r="O74">
-        <v>511.3838097839997</v>
+        <v>683.5758947759997</v>
       </c>
       <c r="P74">
-        <v>1418.366415815999</v>
+        <v>1895.955783623999</v>
       </c>
       <c r="Q74">
-        <v>4833.766415815999</v>
+        <v>5311.355783624</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1254686700581863</v>
+        <v>0.1254174501867227</v>
       </c>
       <c r="T74">
         <v>1.838740189069807</v>
       </c>
       <c r="U74">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.265</v>
       </c>
       <c r="W74">
-        <v>0.0601965</v>
+        <v>0.0471135</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.645460827071373</v>
+        <v>2.102390666726139</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07854362002956061</v>
+        <v>0.06897873543186891</v>
       </c>
       <c r="C75">
-        <v>5794.209387615949</v>
+        <v>12271.12955998773</v>
       </c>
       <c r="D75">
-        <v>42212.09338761595</v>
+        <v>48689.01355998773</v>
       </c>
       <c r="E75">
         <v>3024.383999999998</v>
@@ -7443,45 +7443,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M75">
-        <v>3031.248729599999</v>
+        <v>2372.4425344</v>
       </c>
       <c r="N75">
-        <v>1888.226270399999</v>
+        <v>2547.032465599999</v>
       </c>
       <c r="O75">
-        <v>500.3799616559998</v>
+        <v>674.9636033839997</v>
       </c>
       <c r="P75">
-        <v>1387.846308743999</v>
+        <v>1872.068862215999</v>
       </c>
       <c r="Q75">
-        <v>4803.246308743999</v>
+        <v>5287.468862215999</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.12814879640578</v>
+        <v>0.1280958534513663</v>
       </c>
       <c r="T75">
         <v>1.900597077398761</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.265</v>
       </c>
       <c r="W75">
-        <v>0.0601965</v>
+        <v>0.0471135</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.622920267796423</v>
+        <v>2.073590794579205</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07861453244282907</v>
+        <v>0.06891886481145548</v>
       </c>
       <c r="C76">
-        <v>5245.547878212848</v>
+        <v>11811.00116089167</v>
       </c>
       <c r="D76">
-        <v>42170.43987821285</v>
+        <v>48735.89316089167</v>
       </c>
       <c r="E76">
         <v>3531.392</v>
@@ -7525,45 +7525,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M76">
-        <v>3072.7726848</v>
+        <v>2404.9417472</v>
       </c>
       <c r="N76">
-        <v>1846.702315199999</v>
+        <v>2514.533252799999</v>
       </c>
       <c r="O76">
-        <v>489.3761135279997</v>
+        <v>666.3513119919996</v>
       </c>
       <c r="P76">
-        <v>1357.326201671999</v>
+        <v>1848.181940807999</v>
       </c>
       <c r="Q76">
-        <v>4772.726201672</v>
+        <v>5263.581940807999</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1310350863185733</v>
+        <v>0.1309802877363672</v>
       </c>
       <c r="T76">
         <v>1.967212187906865</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.265</v>
       </c>
       <c r="W76">
-        <v>0.0601965</v>
+        <v>0.0471135</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.600988912826201</v>
+        <v>2.045569297355161</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07868544485609751</v>
+        <v>0.06885899419104205</v>
       </c>
       <c r="C77">
-        <v>4696.968492406981</v>
+        <v>11350.96312366101</v>
       </c>
       <c r="D77">
-        <v>42128.86849240698</v>
+        <v>48782.86312366101</v>
       </c>
       <c r="E77">
         <v>4038.400000000001</v>
@@ -7607,45 +7607,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M77">
-        <v>3114.29664</v>
+        <v>2437.44096</v>
       </c>
       <c r="N77">
-        <v>1805.178359999999</v>
+        <v>2482.034039999999</v>
       </c>
       <c r="O77">
-        <v>478.3722653999996</v>
+        <v>657.7390205999997</v>
       </c>
       <c r="P77">
-        <v>1326.806094599999</v>
+        <v>1824.295019399999</v>
       </c>
       <c r="Q77">
-        <v>4742.206094599999</v>
+        <v>5239.695019399999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.13415227942439</v>
+        <v>0.1340954767641682</v>
       </c>
       <c r="T77">
         <v>2.039156507255617</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.265</v>
       </c>
       <c r="W77">
-        <v>0.0601965</v>
+        <v>0.0471135</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.579642393988518</v>
+        <v>2.018295040057093</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07875635726936595</v>
+        <v>0.07315620357062863</v>
       </c>
       <c r="C78">
-        <v>4148.470987566558</v>
+        <v>7687.767118248048</v>
       </c>
       <c r="D78">
-        <v>42087.37898756656</v>
+        <v>45626.67511824805</v>
       </c>
       <c r="E78">
         <v>4545.408000000003</v>
@@ -7689,45 +7689,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M78">
-        <v>3155.8205952</v>
+        <v>2770.4945152</v>
       </c>
       <c r="N78">
-        <v>1763.654404799999</v>
+        <v>2148.980484799999</v>
       </c>
       <c r="O78">
-        <v>467.3684172719997</v>
+        <v>569.4798284719997</v>
       </c>
       <c r="P78">
-        <v>1296.285987527999</v>
+        <v>1579.500656327999</v>
       </c>
       <c r="Q78">
-        <v>4711.685987527999</v>
+        <v>4994.900656327999</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1375292386223581</v>
+        <v>0.1374702648776192</v>
       </c>
       <c r="T78">
         <v>2.117096186550098</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.265</v>
       </c>
       <c r="W78">
-        <v>0.0601965</v>
+        <v>0.0528465</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.558857625646564</v>
+        <v>1.775666752996573</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.0788272696826344</v>
+        <v>0.07315366295021519</v>
       </c>
       <c r="C79">
-        <v>3600.055122014659</v>
+        <v>7182.504475288901</v>
       </c>
       <c r="D79">
-        <v>42045.97112201466</v>
+        <v>45628.4204752889</v>
       </c>
       <c r="E79">
         <v>5052.415999999997</v>
@@ -7771,45 +7771,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M79">
-        <v>3197.3445504</v>
+        <v>2806.9483904</v>
       </c>
       <c r="N79">
-        <v>1722.130449599999</v>
+        <v>2112.526609599999</v>
       </c>
       <c r="O79">
-        <v>456.3645691439997</v>
+        <v>559.8195515439996</v>
       </c>
       <c r="P79">
-        <v>1265.765880455999</v>
+        <v>1552.707058055999</v>
       </c>
       <c r="Q79">
-        <v>4681.165880455999</v>
+        <v>4968.107058055999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1411998464462365</v>
+        <v>0.1411385128270226</v>
       </c>
       <c r="T79">
         <v>2.201813229261491</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.265</v>
       </c>
       <c r="W79">
-        <v>0.0601965</v>
+        <v>0.0528465</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.538612721417388</v>
+        <v>1.752606145814799</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.07889818209590282</v>
+        <v>0.07538699232980176</v>
       </c>
       <c r="C80">
-        <v>3051.720655024546</v>
+        <v>5191.09847644619</v>
       </c>
       <c r="D80">
-        <v>42004.64465502455</v>
+        <v>44144.02247644619</v>
       </c>
       <c r="E80">
         <v>5559.423999999999</v>
@@ -7853,37 +7853,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M80">
-        <v>3238.8685056</v>
+        <v>2997.6340992</v>
       </c>
       <c r="N80">
-        <v>1680.606494399999</v>
+        <v>1921.840900799999</v>
       </c>
       <c r="O80">
-        <v>445.3607210159997</v>
+        <v>509.2878387119997</v>
       </c>
       <c r="P80">
-        <v>1235.245773383999</v>
+        <v>1412.553062087999</v>
       </c>
       <c r="Q80">
-        <v>4650.645773383999</v>
+        <v>4827.953062087999</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1452041458904674</v>
+        <v>0.1451402378627352</v>
       </c>
       <c r="T80">
         <v>2.294231821310283</v>
       </c>
       <c r="U80">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.265</v>
       </c>
       <c r="W80">
-        <v>0.0601965</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.518886917296652</v>
+        <v>1.64111924177567</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08843368950917128</v>
+        <v>0.07541311670938833</v>
       </c>
       <c r="C81">
-        <v>-2358.852797309439</v>
+        <v>4667.297998068039</v>
       </c>
       <c r="D81">
-        <v>37101.07920269056</v>
+        <v>44127.22999806804</v>
       </c>
       <c r="E81">
         <v>6066.432000000001</v>
@@ -7935,45 +7935,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M81">
-        <v>3933.2666624</v>
+        <v>3036.0653056</v>
       </c>
       <c r="N81">
-        <v>986.2083375999982</v>
+        <v>1883.409694399998</v>
       </c>
       <c r="O81">
-        <v>261.3452094639995</v>
+        <v>499.1035690159996</v>
       </c>
       <c r="P81">
-        <v>724.8631281359987</v>
+        <v>1384.306125383999</v>
       </c>
       <c r="Q81">
-        <v>4140.263128135999</v>
+        <v>4799.706125383998</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1495898071865299</v>
+        <v>0.1495230795685159</v>
       </c>
       <c r="T81">
         <v>2.39545218403039</v>
       </c>
       <c r="U81">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.265</v>
       </c>
       <c r="W81">
-        <v>0.07217700000000001</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.250735183308989</v>
+        <v>1.620345580487371</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1103191694217304</v>
+        <v>0.0754392410889749</v>
       </c>
       <c r="C82">
-        <v>-10705.87795069126</v>
+        <v>4143.510290619524</v>
       </c>
       <c r="D82">
-        <v>29261.06204930874</v>
+        <v>44110.45029061953</v>
       </c>
       <c r="E82">
         <v>6573.440000000002</v>
@@ -8017,45 +8017,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M82">
-        <v>5309.387776</v>
+        <v>3074.496512</v>
       </c>
       <c r="N82">
-        <v>-389.912776000001</v>
+        <v>1844.978487999998</v>
       </c>
       <c r="O82">
-        <v>-103.3268856400003</v>
+        <v>488.9192993199996</v>
       </c>
       <c r="P82">
-        <v>-286.5858903600007</v>
+        <v>1356.059188679999</v>
       </c>
       <c r="Q82">
-        <v>3128.81410964</v>
+        <v>4771.459188679999</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1565599797258886</v>
+        <v>0.1543442054448745</v>
       </c>
       <c r="T82">
-        <v>2.556322653733338</v>
+        <v>2.506794583022506</v>
       </c>
       <c r="U82">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
-        <v>0.2455388323476638</v>
+        <v>0.265</v>
       </c>
       <c r="W82">
-        <v>0.0987589668456908</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9265616315006182</v>
+        <v>1.600091260731278</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1111701694217304</v>
+        <v>0.07546536546856147</v>
       </c>
       <c r="C83">
-        <v>-11451.35943712722</v>
+        <v>3619.735339537445</v>
       </c>
       <c r="D83">
-        <v>29022.58856287278</v>
+        <v>44093.68333953745</v>
       </c>
       <c r="E83">
         <v>7080.448000000004</v>
@@ -8099,45 +8099,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M83">
-        <v>5375.7551232</v>
+        <v>3112.9277184</v>
       </c>
       <c r="N83">
-        <v>-456.2801232000011</v>
+        <v>1806.547281599998</v>
       </c>
       <c r="O83">
-        <v>-120.9142326480003</v>
+        <v>478.7350296239996</v>
       </c>
       <c r="P83">
-        <v>-335.3658905520008</v>
+        <v>1327.812251975999</v>
       </c>
       <c r="Q83">
-        <v>3080.034109447999</v>
+        <v>4743.212251975999</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1623894523430407</v>
+        <v>0.1596728182555867</v>
       </c>
       <c r="T83">
-        <v>2.69086595129825</v>
+        <v>2.629857234540108</v>
       </c>
       <c r="U83">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
-        <v>0.2425074887384334</v>
+        <v>0.265</v>
       </c>
       <c r="W83">
-        <v>0.09915576972413906</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9151225990129562</v>
+        <v>1.58033704763583</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1120211694217304</v>
+        <v>0.07549148984814805</v>
       </c>
       <c r="C84">
-        <v>-12192.98529650329</v>
+        <v>3095.97313028077</v>
       </c>
       <c r="D84">
-        <v>28787.97070349671</v>
+        <v>44076.92913028078</v>
       </c>
       <c r="E84">
         <v>7587.456000000006</v>
@@ -8181,45 +8181,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M84">
-        <v>5442.1224704</v>
+        <v>3151.3589248</v>
       </c>
       <c r="N84">
-        <v>-522.6474704000011</v>
+        <v>1768.116075199998</v>
       </c>
       <c r="O84">
-        <v>-138.5015796560003</v>
+        <v>468.5507599279995</v>
       </c>
       <c r="P84">
-        <v>-384.1458907440008</v>
+        <v>1299.565315271999</v>
       </c>
       <c r="Q84">
-        <v>3031.254109256</v>
+        <v>4714.965315271998</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1688666441398763</v>
+        <v>0.165593499156378</v>
       </c>
       <c r="T84">
-        <v>2.840358504148153</v>
+        <v>2.766593514004111</v>
       </c>
       <c r="U84">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
-        <v>0.2395500803391842</v>
+        <v>0.265</v>
       </c>
       <c r="W84">
-        <v>0.09954289448360078</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.9039625673176763</v>
+        <v>1.561064644615881</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1128721694217304</v>
+        <v>0.07551761422773461</v>
       </c>
       <c r="C85">
-        <v>-12930.84828534798</v>
+        <v>2572.223648330539</v>
       </c>
       <c r="D85">
-        <v>28557.11571465201</v>
+        <v>44060.18764833054</v>
       </c>
       <c r="E85">
         <v>8094.464</v>
@@ -8263,45 +8263,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M85">
-        <v>5508.489817599999</v>
+        <v>3189.7901312</v>
       </c>
       <c r="N85">
-        <v>-589.0148176000002</v>
+        <v>1729.684868799999</v>
       </c>
       <c r="O85">
-        <v>-156.0889266640001</v>
+        <v>458.3664902319996</v>
       </c>
       <c r="P85">
-        <v>-432.9258909360002</v>
+        <v>1271.318378567999</v>
       </c>
       <c r="Q85">
-        <v>2982.474109064</v>
+        <v>4686.718378567999</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1761058585010455</v>
+        <v>0.17221073075138</v>
       </c>
       <c r="T85">
-        <v>3.007438416156868</v>
+        <v>2.919416414581526</v>
       </c>
       <c r="U85">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
-        <v>0.236663934792929</v>
+        <v>0.265</v>
       </c>
       <c r="W85">
-        <v>0.09992069093560559</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8930714520487888</v>
+        <v>1.542256636849425</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1137231694217304</v>
+        <v>0.07554373860732118</v>
       </c>
       <c r="C86">
-        <v>-13665.0382085463</v>
+        <v>2048.486879189826</v>
       </c>
       <c r="D86">
-        <v>28329.9337914537</v>
+        <v>44043.45887918982</v>
       </c>
       <c r="E86">
         <v>8601.471999999994</v>
@@ -8345,45 +8345,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M86">
-        <v>5574.857164799999</v>
+        <v>3228.2213376</v>
       </c>
       <c r="N86">
-        <v>-655.3821648000003</v>
+        <v>1691.253662399999</v>
       </c>
       <c r="O86">
-        <v>-173.6762736720001</v>
+        <v>448.1822205359998</v>
       </c>
       <c r="P86">
-        <v>-481.7058911280002</v>
+        <v>1243.071441863999</v>
       </c>
       <c r="Q86">
-        <v>2933.694108872</v>
+        <v>4658.471441864</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1842499746573608</v>
+        <v>0.1796551162957573</v>
       </c>
       <c r="T86">
-        <v>3.195403317166671</v>
+        <v>3.091342177731116</v>
       </c>
       <c r="U86">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
-        <v>0.2338465069977751</v>
+        <v>0.265</v>
       </c>
       <c r="W86">
-        <v>0.1002894922339912</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8824396490482079</v>
+        <v>1.523896438791694</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1145741694217304</v>
+        <v>0.07556986298690775</v>
       </c>
       <c r="C87">
-        <v>-14395.64203581985</v>
+        <v>1524.762808383733</v>
       </c>
       <c r="D87">
-        <v>28106.33796418014</v>
+        <v>44026.74280838373</v>
       </c>
       <c r="E87">
         <v>9108.479999999996</v>
@@ -8427,45 +8427,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M87">
-        <v>5641.224511999999</v>
+        <v>3266.652544</v>
       </c>
       <c r="N87">
-        <v>-721.7495120000003</v>
+        <v>1652.822455999999</v>
       </c>
       <c r="O87">
-        <v>-191.2636206800001</v>
+        <v>437.9979508399998</v>
       </c>
       <c r="P87">
-        <v>-530.4858913200003</v>
+        <v>1214.824505159999</v>
       </c>
       <c r="Q87">
-        <v>2884.91410868</v>
+        <v>4630.224505159999</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1934799729678515</v>
+        <v>0.1880920865793849</v>
       </c>
       <c r="T87">
-        <v>3.408430204977783</v>
+        <v>3.28619137596732</v>
       </c>
       <c r="U87">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
-        <v>0.2310953716213307</v>
+        <v>0.265</v>
       </c>
       <c r="W87">
-        <v>0.1006496158547678</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.872058006118229</v>
+        <v>1.505968245394145</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1154251694217304</v>
+        <v>0.08457180736649432</v>
       </c>
       <c r="C88">
-        <v>-15122.74401273433</v>
+        <v>-4074.16264564501</v>
       </c>
       <c r="D88">
-        <v>27886.24398726567</v>
+        <v>38934.82535435499</v>
       </c>
       <c r="E88">
         <v>9615.487999999998</v>
@@ -8509,45 +8509,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M88">
-        <v>5707.591859199999</v>
+        <v>3924.241919999999</v>
       </c>
       <c r="N88">
-        <v>-788.1168592000004</v>
+        <v>995.2330799999991</v>
       </c>
       <c r="O88">
-        <v>-208.8509676880001</v>
+        <v>263.7367661999997</v>
       </c>
       <c r="P88">
-        <v>-579.2658915120003</v>
+        <v>731.4963137999994</v>
       </c>
       <c r="Q88">
-        <v>2836.134108488</v>
+        <v>4146.8963138</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2040285424655552</v>
+        <v>0.1977343383321022</v>
       </c>
       <c r="T88">
-        <v>3.651889505333338</v>
+        <v>3.508876173951553</v>
       </c>
       <c r="U88">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V88">
-        <v>0.2284082161373617</v>
+        <v>0.265</v>
       </c>
       <c r="W88">
-        <v>0.1010013645076193</v>
+        <v>0.06615</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8619177967447612</v>
+        <v>1.253611551043214</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1162761694217304</v>
+        <v>0.1049996974770162</v>
       </c>
       <c r="C89">
-        <v>-15846.42576653177</v>
+        <v>-12675.38880656925</v>
       </c>
       <c r="D89">
-        <v>27669.57023346823</v>
+        <v>30840.60719343074</v>
       </c>
       <c r="E89">
         <v>10122.496</v>
@@ -8591,37 +8591,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M89">
-        <v>5773.959206399999</v>
+        <v>5231.4099456</v>
       </c>
       <c r="N89">
-        <v>-854.4842064000004</v>
+        <v>-311.9349456000018</v>
       </c>
       <c r="O89">
-        <v>-226.4383146960001</v>
+        <v>-82.66276058400048</v>
       </c>
       <c r="P89">
-        <v>-628.0458917040003</v>
+        <v>-229.2721850160013</v>
       </c>
       <c r="Q89">
-        <v>2787.354108296</v>
+        <v>3186.127814983999</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2161999688090594</v>
+        <v>0.2117732615420276</v>
       </c>
       <c r="T89">
-        <v>3.932804082666672</v>
+        <v>3.833100728453293</v>
       </c>
       <c r="U89">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.2257828343426794</v>
+        <v>0.2491987606699556</v>
       </c>
       <c r="W89">
-        <v>0.1013450269845433</v>
+        <v>0.08904502698454328</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8520106956327524</v>
+        <v>0.9403726817734172</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1171271694217304</v>
+        <v>0.1057276974770162</v>
       </c>
       <c r="C90">
-        <v>-16566.76640706708</v>
+        <v>-13409.2065697776</v>
       </c>
       <c r="D90">
-        <v>27456.23759293292</v>
+        <v>30613.7974302224</v>
       </c>
       <c r="E90">
         <v>10629.504</v>
@@ -8673,37 +8673,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M90">
-        <v>5840.326553599999</v>
+        <v>5291.5410944</v>
       </c>
       <c r="N90">
-        <v>-920.8515536000004</v>
+        <v>-372.0660944000019</v>
       </c>
       <c r="O90">
-        <v>-244.0256617040001</v>
+        <v>-98.59751501600051</v>
       </c>
       <c r="P90">
-        <v>-676.8258918960003</v>
+        <v>-273.4685793840014</v>
       </c>
       <c r="Q90">
-        <v>2738.574108104</v>
+        <v>3141.931420615999</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2303999662098144</v>
+        <v>0.2256043666705299</v>
       </c>
       <c r="T90">
-        <v>4.260537756222229</v>
+        <v>4.152525789157735</v>
       </c>
       <c r="U90">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.2232171203160581</v>
+        <v>0.2463669565714333</v>
       </c>
       <c r="W90">
-        <v>0.101680878950628</v>
+        <v>0.08938087895062802</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8423287559096531</v>
+        <v>0.9296866285714465</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1179781694217304</v>
+        <v>0.1064556974770162</v>
       </c>
       <c r="C91">
-        <v>-17283.8426231109</v>
+        <v>-14139.71265317952</v>
       </c>
       <c r="D91">
-        <v>27246.1693768891</v>
+        <v>30390.29934682048</v>
       </c>
       <c r="E91">
         <v>11136.512</v>
@@ -8755,37 +8755,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M91">
-        <v>5906.693900799999</v>
+        <v>5351.672243200001</v>
       </c>
       <c r="N91">
-        <v>-987.2189008000005</v>
+        <v>-432.197243200002</v>
       </c>
       <c r="O91">
-        <v>-261.6130087120001</v>
+        <v>-114.5322694480005</v>
       </c>
       <c r="P91">
-        <v>-725.6058920880004</v>
+        <v>-317.6649737520015</v>
       </c>
       <c r="Q91">
-        <v>2689.794107912</v>
+        <v>3097.735026247999</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2471817813197975</v>
+        <v>0.2419502181860326</v>
       </c>
       <c r="T91">
-        <v>4.64785937042425</v>
+        <v>4.53002813362662</v>
       </c>
       <c r="U91">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.220709062784417</v>
+        <v>0.2435987885200689</v>
       </c>
       <c r="W91">
-        <v>0.1020091836815198</v>
+        <v>0.08970918368151984</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8328643878657243</v>
+        <v>0.9192407113964863</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1188291694217304</v>
+        <v>0.1071836974770162</v>
       </c>
       <c r="C92">
-        <v>-17997.72877426521</v>
+        <v>-14866.97906251454</v>
       </c>
       <c r="D92">
-        <v>27039.29122573479</v>
+        <v>30170.04093748546</v>
       </c>
       <c r="E92">
         <v>11643.52</v>
@@ -8837,37 +8837,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M92">
-        <v>5973.061247999999</v>
+        <v>5411.803392</v>
       </c>
       <c r="N92">
-        <v>-1053.586248000001</v>
+        <v>-492.3283920000013</v>
       </c>
       <c r="O92">
-        <v>-279.2003557200002</v>
+        <v>-130.4670238800003</v>
       </c>
       <c r="P92">
-        <v>-774.3858922800003</v>
+        <v>-361.8613681200009</v>
       </c>
       <c r="Q92">
-        <v>2641.01410772</v>
+        <v>3053.538631879999</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2673199594517773</v>
+        <v>0.2615652400046359</v>
       </c>
       <c r="T92">
-        <v>5.112645307466676</v>
+        <v>4.983030946989282</v>
       </c>
       <c r="U92">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.2182567398645901</v>
+        <v>0.2408921353142904</v>
       </c>
       <c r="W92">
-        <v>0.1023301927517252</v>
+        <v>0.09003019275172516</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8236103391116607</v>
+        <v>0.9090269257143033</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1196801694217303</v>
+        <v>0.1079116974770162</v>
       </c>
       <c r="C93">
-        <v>-18708.49697872298</v>
+        <v>-15591.07573105169</v>
       </c>
       <c r="D93">
-        <v>26835.53102127702</v>
+        <v>29952.95226894831</v>
       </c>
       <c r="E93">
         <v>12150.528</v>
@@ -8919,37 +8919,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M93">
-        <v>6039.428595199999</v>
+        <v>5471.9345408</v>
       </c>
       <c r="N93">
-        <v>-1119.953595200001</v>
+        <v>-552.4595408000014</v>
       </c>
       <c r="O93">
-        <v>-296.7877027280002</v>
+        <v>-146.4017783120004</v>
       </c>
       <c r="P93">
-        <v>-823.1658924720005</v>
+        <v>-406.057762488001</v>
       </c>
       <c r="Q93">
-        <v>2592.234107528</v>
+        <v>3009.342237511999</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2919332882797525</v>
+        <v>0.2855391555607066</v>
       </c>
       <c r="T93">
-        <v>5.680717008296305</v>
+        <v>5.536701052210314</v>
       </c>
       <c r="U93">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.2158583141517924</v>
+        <v>0.2382449689921553</v>
       </c>
       <c r="W93">
-        <v>0.1026441466775304</v>
+        <v>0.09034414667753039</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8145596760444995</v>
+        <v>0.899037618838322</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1205311694217304</v>
+        <v>0.1086396974770162</v>
       </c>
       <c r="C94">
-        <v>-19416.21719708954</v>
+        <v>-16312.07059361911</v>
       </c>
       <c r="D94">
-        <v>26634.81880291045</v>
+        <v>29738.96540638088</v>
       </c>
       <c r="E94">
         <v>12657.536</v>
@@ -9001,37 +9001,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M94">
-        <v>6105.795942399999</v>
+        <v>5532.0656896</v>
       </c>
       <c r="N94">
-        <v>-1186.320942400001</v>
+        <v>-612.5906896000015</v>
       </c>
       <c r="O94">
-        <v>-314.3750497360002</v>
+        <v>-162.3365327440004</v>
       </c>
       <c r="P94">
-        <v>-871.9458926640004</v>
+        <v>-450.2541568560011</v>
       </c>
       <c r="Q94">
-        <v>2543.454107336</v>
+        <v>2965.145843143999</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3226999493147217</v>
+        <v>0.315506550005795</v>
       </c>
       <c r="T94">
-        <v>6.390806634333346</v>
+        <v>6.228788683736605</v>
       </c>
       <c r="U94">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.2135120281284034</v>
+        <v>0.2356553497639797</v>
       </c>
       <c r="W94">
-        <v>0.102951275517992</v>
+        <v>0.09065127551799201</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8057057665222768</v>
+        <v>0.8892654708074705</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2024695448668197</v>
+        <v>0.1093676974770162</v>
       </c>
       <c r="C95">
-        <v>-31074.01131771501</v>
+        <v>-17030.02965748308</v>
       </c>
       <c r="D95">
-        <v>15484.03268228498</v>
+        <v>29528.01434251692</v>
       </c>
       <c r="E95">
         <v>13164.544</v>
@@ -9083,45 +9083,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M95">
-        <v>10175.3463552</v>
+        <v>5592.1968384</v>
       </c>
       <c r="N95">
-        <v>-5255.871355200003</v>
+        <v>-672.7218384000016</v>
       </c>
       <c r="O95">
-        <v>-1392.805909128001</v>
+        <v>-178.2712871760004</v>
       </c>
       <c r="P95">
-        <v>-3863.065446072002</v>
+        <v>-494.4505512240012</v>
       </c>
       <c r="Q95">
-        <v>-447.6654460720015</v>
+        <v>2920.949448775999</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3926910198609573</v>
+        <v>0.3540360571494801</v>
       </c>
       <c r="T95">
-        <v>8.00618937130373</v>
+        <v>7.118615638556121</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1281195577518379</v>
+        <v>0.2331214212718939</v>
       </c>
       <c r="W95">
-        <v>0.1881517994371534</v>
+        <v>0.09095179943715338</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4834700292522184</v>
+        <v>0.8797034764977129</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2041695448668197</v>
+        <v>0.1100956974770163</v>
       </c>
       <c r="C96">
-        <v>-31714.35470273139</v>
+        <v>-17745.01707023145</v>
       </c>
       <c r="D96">
-        <v>15350.69729726861</v>
+        <v>29320.03492976855</v>
       </c>
       <c r="E96">
         <v>13671.552</v>
@@ -9165,45 +9165,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M96">
-        <v>10284.7586816</v>
+        <v>5652.3279872</v>
       </c>
       <c r="N96">
-        <v>-5365.283681600002</v>
+        <v>-732.8529872000017</v>
       </c>
       <c r="O96">
-        <v>-1421.800175624001</v>
+        <v>-194.2060416080005</v>
       </c>
       <c r="P96">
-        <v>-3943.483505976001</v>
+        <v>-538.6469455920012</v>
       </c>
       <c r="Q96">
-        <v>-528.0835059760011</v>
+        <v>2876.753054407999</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4505061898377836</v>
+        <v>0.4054087333410601</v>
       </c>
       <c r="T96">
-        <v>9.340554266521021</v>
+        <v>8.305051578315476</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.1267565837332013</v>
+        <v>0.2306414061519801</v>
       </c>
       <c r="W96">
-        <v>0.1884459292303752</v>
+        <v>0.09124592923037517</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.4783267310686842</v>
+        <v>0.8703449288753967</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2058695448668197</v>
+        <v>0.1108236974770162</v>
       </c>
       <c r="C97">
-        <v>-32352.42135010275</v>
+        <v>-18457.09518480851</v>
       </c>
       <c r="D97">
-        <v>15219.63864989725</v>
+        <v>29114.96481519149</v>
       </c>
       <c r="E97">
         <v>14178.56</v>
@@ -9247,45 +9247,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M97">
-        <v>10394.171008</v>
+        <v>5712.459136</v>
       </c>
       <c r="N97">
-        <v>-5474.696008000003</v>
+        <v>-792.9841360000019</v>
       </c>
       <c r="O97">
-        <v>-1450.794442120001</v>
+        <v>-210.1407960400005</v>
       </c>
       <c r="P97">
-        <v>-4023.901565880002</v>
+        <v>-582.8433399600013</v>
       </c>
       <c r="Q97">
-        <v>-608.5015658800016</v>
+        <v>2832.556660039999</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5314474278053406</v>
+        <v>0.4773304800092724</v>
       </c>
       <c r="T97">
-        <v>11.20866511982523</v>
+        <v>9.966061893978576</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.1254223039044308</v>
+        <v>0.2282136018766961</v>
       </c>
       <c r="W97">
-        <v>0.1887338668174239</v>
+        <v>0.09153386681742384</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4732917128469085</v>
+        <v>0.8611834033082872</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2075695448668197</v>
+        <v>0.1115516974770162</v>
       </c>
       <c r="C98">
-        <v>-32988.2690800448</v>
+        <v>-19166.32462183949</v>
       </c>
       <c r="D98">
-        <v>15090.79891995519</v>
+        <v>28912.74337816051</v>
       </c>
       <c r="E98">
         <v>14685.568</v>
@@ -9329,45 +9329,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M98">
-        <v>10503.5833344</v>
+        <v>5772.590284800001</v>
       </c>
       <c r="N98">
-        <v>-5584.108334400002</v>
+        <v>-853.115284800002</v>
       </c>
       <c r="O98">
-        <v>-1479.788708616001</v>
+        <v>-226.0755504720005</v>
       </c>
       <c r="P98">
-        <v>-4104.319625784001</v>
+        <v>-627.0397343280015</v>
       </c>
       <c r="Q98">
-        <v>-688.9196257840008</v>
+        <v>2788.360265671999</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6528592847566743</v>
+        <v>0.5852131000115892</v>
       </c>
       <c r="T98">
-        <v>14.01083139978151</v>
+        <v>12.45757736747319</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.124115821572093</v>
+        <v>0.2258363768571472</v>
       </c>
       <c r="W98">
-        <v>0.1890158057047424</v>
+        <v>0.09181580570474235</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4683615908380866</v>
+        <v>0.8522127428571593</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2092695448668196</v>
+        <v>0.1122796974770162</v>
       </c>
       <c r="C99">
-        <v>-33621.95377133238</v>
+        <v>-19872.76432937577</v>
       </c>
       <c r="D99">
-        <v>14964.12222866761</v>
+        <v>28713.31167062423</v>
       </c>
       <c r="E99">
         <v>15192.576</v>
@@ -9411,45 +9411,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M99">
-        <v>10612.9956608</v>
+        <v>5832.721433600001</v>
       </c>
       <c r="N99">
-        <v>-5693.520660800003</v>
+        <v>-913.2464336000021</v>
       </c>
       <c r="O99">
-        <v>-1508.782975112001</v>
+        <v>-242.0103049040006</v>
       </c>
       <c r="P99">
-        <v>-4184.737685688002</v>
+        <v>-671.2361286960015</v>
       </c>
       <c r="Q99">
-        <v>-769.3376856880018</v>
+        <v>2744.163871303998</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8552123796755658</v>
+        <v>0.7650174666821191</v>
       </c>
       <c r="T99">
-        <v>18.68110853304201</v>
+        <v>16.61010315663093</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.1228362770198033</v>
+        <v>0.223508166786455</v>
       </c>
       <c r="W99">
-        <v>0.1892919314191265</v>
+        <v>0.09209193141912646</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4635331208294465</v>
+        <v>0.8434270444771885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2109695448668197</v>
+        <v>0.1130076974770162</v>
       </c>
       <c r="C100">
-        <v>-34253.52944210624</v>
+        <v>-20576.4716401843</v>
       </c>
       <c r="D100">
-        <v>14839.55455789375</v>
+        <v>28516.6123598157</v>
       </c>
       <c r="E100">
         <v>15699.584</v>
@@ -9493,45 +9493,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M100">
-        <v>10722.4079872</v>
+        <v>5892.8525824</v>
       </c>
       <c r="N100">
-        <v>-5802.932987200002</v>
+        <v>-973.3775824000013</v>
       </c>
       <c r="O100">
-        <v>-1537.777241608001</v>
+        <v>-257.9450593360004</v>
       </c>
       <c r="P100">
-        <v>-4265.155745592001</v>
+        <v>-715.4325230640009</v>
       </c>
       <c r="Q100">
-        <v>-849.7557455920009</v>
+        <v>2699.967476935999</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.259918569513349</v>
+        <v>1.124626200023179</v>
       </c>
       <c r="T100">
-        <v>28.02166279956301</v>
+        <v>24.91515473494639</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.1215828456216421</v>
+        <v>0.2212274712070014</v>
       </c>
       <c r="W100">
-        <v>0.1895624219148496</v>
+        <v>0.09236242191484964</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4588031910250645</v>
+        <v>0.8348206460641561</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2126695448668197</v>
+        <v>0.1137356974770162</v>
       </c>
       <c r="C101">
-        <v>-34883.04832667726</v>
+        <v>-21277.5023266984</v>
       </c>
       <c r="D101">
-        <v>14717.04367332273</v>
+        <v>28322.5896733016</v>
       </c>
       <c r="E101">
         <v>16206.592</v>
@@ -9575,45 +9575,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M101">
-        <v>10831.8203136</v>
+        <v>5952.9837312</v>
       </c>
       <c r="N101">
-        <v>-5912.345313600001</v>
+        <v>-1033.508731200001</v>
       </c>
       <c r="O101">
-        <v>-1566.771508104</v>
+        <v>-273.8798137680004</v>
       </c>
       <c r="P101">
-        <v>-4345.573805496</v>
+        <v>-759.628917432001</v>
       </c>
       <c r="Q101">
-        <v>-930.1738054960001</v>
+        <v>2655.771082567999</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.474037139026698</v>
+        <v>2.203452400046356</v>
       </c>
       <c r="T101">
-        <v>56.04332559912604</v>
+        <v>49.83030946989276</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V101">
-        <v>0.1203547360699083</v>
+        <v>0.2189928502857185</v>
       </c>
       <c r="W101">
-        <v>0.1898274479561138</v>
+        <v>0.09262744795611379</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4541688153581447</v>
+        <v>0.8263881142857302</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/canada/canada_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07334929072204936</v>
+        <v>0.07318799010163592</v>
       </c>
       <c r="C2">
-        <v>46088.11754527599</v>
+        <v>45691.54166724924</v>
       </c>
       <c r="D2">
-        <v>45494.41754527599</v>
+        <v>45604.84966724925</v>
       </c>
       <c r="E2">
-        <v>-33987.2</v>
+        <v>-33480.192</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>507.008</v>
       </c>
       <c r="G2">
         <v>593.7</v>
@@ -1457,28 +1457,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>25.5025024</v>
       </c>
       <c r="N2">
-        <v>4919.474999999999</v>
+        <v>4893.972497599999</v>
       </c>
       <c r="O2">
-        <v>1303.660875</v>
+        <v>1296.902711864</v>
       </c>
       <c r="P2">
-        <v>3615.814124999999</v>
+        <v>3597.069785735999</v>
       </c>
       <c r="Q2">
-        <v>7031.214124999999</v>
+        <v>7012.469785735999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07334929072204936</v>
+        <v>0.07355382333498578</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6409658968818889</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>192.901658152574</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07318799010163592</v>
+        <v>0.07302668948122248</v>
       </c>
       <c r="C3">
-        <v>45691.54166724924</v>
+        <v>45295.50321463588</v>
       </c>
       <c r="D3">
-        <v>45604.84966724925</v>
+        <v>45715.81921463589</v>
       </c>
       <c r="E3">
-        <v>-33480.192</v>
+        <v>-32973.18399999999</v>
       </c>
       <c r="F3">
-        <v>507.008</v>
+        <v>1014.016</v>
       </c>
       <c r="G3">
         <v>593.7</v>
@@ -1539,28 +1539,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M3">
-        <v>25.5025024</v>
+        <v>51.00500479999999</v>
       </c>
       <c r="N3">
-        <v>4893.972497599999</v>
+        <v>4868.469995199998</v>
       </c>
       <c r="O3">
-        <v>1296.902711864</v>
+        <v>1290.144548728</v>
       </c>
       <c r="P3">
-        <v>3597.069785735999</v>
+        <v>3578.325446471998</v>
       </c>
       <c r="Q3">
-        <v>7012.469785735999</v>
+        <v>6993.725446471999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07355382333498578</v>
+        <v>0.0737625300828801</v>
       </c>
       <c r="T3">
-        <v>0.6409658968818889</v>
+        <v>0.6457859141542749</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.901658152574</v>
+        <v>96.45082907628702</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07302668948122248</v>
+        <v>0.07286538886080907</v>
       </c>
       <c r="C4">
-        <v>45295.50321463588</v>
+        <v>44900.00612013111</v>
       </c>
       <c r="D4">
-        <v>45715.81921463589</v>
+        <v>45827.33012013111</v>
       </c>
       <c r="E4">
-        <v>-32973.18399999999</v>
+        <v>-32466.176</v>
       </c>
       <c r="F4">
-        <v>1014.016</v>
+        <v>1521.024</v>
       </c>
       <c r="G4">
         <v>593.7</v>
@@ -1621,28 +1621,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M4">
-        <v>51.00500479999999</v>
+        <v>76.50750719999999</v>
       </c>
       <c r="N4">
-        <v>4868.469995199998</v>
+        <v>4842.967492799999</v>
       </c>
       <c r="O4">
-        <v>1290.144548728</v>
+        <v>1283.386385592</v>
       </c>
       <c r="P4">
-        <v>3578.325446471998</v>
+        <v>3559.581107207999</v>
       </c>
       <c r="Q4">
-        <v>6993.725446471999</v>
+        <v>6974.981107207999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0737625300828801</v>
+        <v>0.07397554006268976</v>
       </c>
       <c r="T4">
-        <v>0.6457859141542749</v>
+        <v>0.6507053132260916</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.45082907628702</v>
+        <v>64.30055271752468</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07286538886080907</v>
+        <v>0.07270408824039565</v>
       </c>
       <c r="C5">
-        <v>44900.00612013111</v>
+        <v>44505.05435489479</v>
       </c>
       <c r="D5">
-        <v>45827.33012013111</v>
+        <v>45939.38635489479</v>
       </c>
       <c r="E5">
-        <v>-32466.176</v>
+        <v>-31959.168</v>
       </c>
       <c r="F5">
-        <v>1521.024</v>
+        <v>2028.032</v>
       </c>
       <c r="G5">
         <v>593.7</v>
@@ -1703,28 +1703,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M5">
-        <v>76.50750719999999</v>
+        <v>102.0100096</v>
       </c>
       <c r="N5">
-        <v>4842.967492799999</v>
+        <v>4817.464990399999</v>
       </c>
       <c r="O5">
-        <v>1283.386385592</v>
+        <v>1276.628222456</v>
       </c>
       <c r="P5">
-        <v>3559.581107207999</v>
+        <v>3540.836767943999</v>
       </c>
       <c r="Q5">
-        <v>6974.981107207999</v>
+        <v>6956.236767943999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07397554006268976</v>
+        <v>0.07419298775041212</v>
       </c>
       <c r="T5">
-        <v>0.6507053132260916</v>
+        <v>0.655727199778571</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.30055271752468</v>
+        <v>48.22541453814351</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07270408824039565</v>
+        <v>0.0725427876199822</v>
       </c>
       <c r="C6">
-        <v>44505.05435489479</v>
+        <v>44110.65192902288</v>
       </c>
       <c r="D6">
-        <v>45939.38635489479</v>
+        <v>46051.99192902288</v>
       </c>
       <c r="E6">
-        <v>-31959.168</v>
+        <v>-31452.16</v>
       </c>
       <c r="F6">
-        <v>2028.032</v>
+        <v>2535.04</v>
       </c>
       <c r="G6">
         <v>593.7</v>
@@ -1785,28 +1785,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M6">
-        <v>102.0100096</v>
+        <v>127.512512</v>
       </c>
       <c r="N6">
-        <v>4817.464990399999</v>
+        <v>4791.962487999998</v>
       </c>
       <c r="O6">
-        <v>1276.628222456</v>
+        <v>1269.87005932</v>
       </c>
       <c r="P6">
-        <v>3540.836767943999</v>
+        <v>3522.092428679999</v>
       </c>
       <c r="Q6">
-        <v>6956.236767943999</v>
+        <v>6937.492428679999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07419298775041212</v>
+        <v>0.0744150132841918</v>
       </c>
       <c r="T6">
-        <v>0.655727199778571</v>
+        <v>0.6608548102584711</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.22541453814351</v>
+        <v>38.58033163051481</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0725427876199822</v>
+        <v>0.07238148699956878</v>
       </c>
       <c r="C7">
-        <v>44110.65192902288</v>
+        <v>43716.80289202568</v>
       </c>
       <c r="D7">
-        <v>46051.99192902288</v>
+        <v>46165.15089202569</v>
       </c>
       <c r="E7">
-        <v>-31452.16</v>
+        <v>-30945.152</v>
       </c>
       <c r="F7">
-        <v>2535.04</v>
+        <v>3042.048</v>
       </c>
       <c r="G7">
         <v>593.7</v>
@@ -1867,28 +1867,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M7">
-        <v>127.512512</v>
+        <v>153.0150144</v>
       </c>
       <c r="N7">
-        <v>4791.962487999998</v>
+        <v>4766.459985599999</v>
       </c>
       <c r="O7">
-        <v>1269.87005932</v>
+        <v>1263.111896184</v>
       </c>
       <c r="P7">
-        <v>3522.092428679999</v>
+        <v>3503.348089415999</v>
       </c>
       <c r="Q7">
-        <v>6937.492428679999</v>
+        <v>6918.748089415999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0744150132841918</v>
+        <v>0.07464176276549871</v>
       </c>
       <c r="T7">
-        <v>0.6608548102584711</v>
+        <v>0.6660915188336883</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.58033163051481</v>
+        <v>32.15027635876234</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07238148699956877</v>
+        <v>0.07222018637915535</v>
       </c>
       <c r="C8">
-        <v>43716.80289202568</v>
+        <v>43323.51133331349</v>
       </c>
       <c r="D8">
-        <v>46165.15089202569</v>
+        <v>46278.86733331349</v>
       </c>
       <c r="E8">
-        <v>-30945.152</v>
+        <v>-30438.144</v>
       </c>
       <c r="F8">
-        <v>3042.048</v>
+        <v>3549.055999999999</v>
       </c>
       <c r="G8">
         <v>593.7</v>
@@ -1949,28 +1949,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M8">
-        <v>153.0150144</v>
+        <v>178.5175168</v>
       </c>
       <c r="N8">
-        <v>4766.459985599999</v>
+        <v>4740.957483199999</v>
       </c>
       <c r="O8">
-        <v>1263.111896184</v>
+        <v>1256.353733048</v>
       </c>
       <c r="P8">
-        <v>3503.348089415999</v>
+        <v>3484.603750151999</v>
       </c>
       <c r="Q8">
-        <v>6918.748089415999</v>
+        <v>6900.003750151999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07464176276549869</v>
+        <v>0.07487338857973694</v>
       </c>
       <c r="T8">
-        <v>0.6660915188336881</v>
+        <v>0.6714408447976198</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.15027635876234</v>
+        <v>27.55737973608201</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07222018637915535</v>
+        <v>0.07205888575874191</v>
       </c>
       <c r="C9">
-        <v>43323.51133331349</v>
+        <v>42930.781382689</v>
       </c>
       <c r="D9">
-        <v>46278.86733331349</v>
+        <v>46393.145382689</v>
       </c>
       <c r="E9">
-        <v>-30438.144</v>
+        <v>-29931.136</v>
       </c>
       <c r="F9">
-        <v>3549.056</v>
+        <v>4056.064</v>
       </c>
       <c r="G9">
         <v>593.7</v>
@@ -2031,28 +2031,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M9">
-        <v>178.5175168</v>
+        <v>204.0200192</v>
       </c>
       <c r="N9">
-        <v>4740.957483199999</v>
+        <v>4715.454980799998</v>
       </c>
       <c r="O9">
-        <v>1256.353733048</v>
+        <v>1249.595569912</v>
       </c>
       <c r="P9">
-        <v>3484.603750151999</v>
+        <v>3465.859410887999</v>
       </c>
       <c r="Q9">
-        <v>6900.003750151999</v>
+        <v>6881.259410887998</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07487338857973694</v>
+        <v>0.07511004973776295</v>
       </c>
       <c r="T9">
-        <v>0.6714408447976198</v>
+        <v>0.6769064604564192</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.55737973608201</v>
+        <v>24.11270726907176</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07205888575874191</v>
+        <v>0.07189758513832847</v>
       </c>
       <c r="C10">
-        <v>42930.781382689</v>
+        <v>42538.61721084741</v>
       </c>
       <c r="D10">
-        <v>46393.145382689</v>
+        <v>46507.98921084741</v>
       </c>
       <c r="E10">
-        <v>-29931.136</v>
+        <v>-29424.128</v>
       </c>
       <c r="F10">
-        <v>4056.064</v>
+        <v>4563.071999999999</v>
       </c>
       <c r="G10">
         <v>593.7</v>
@@ -2113,28 +2113,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M10">
-        <v>204.0200192</v>
+        <v>229.5225215999999</v>
       </c>
       <c r="N10">
-        <v>4715.454980799998</v>
+        <v>4689.952478399999</v>
       </c>
       <c r="O10">
-        <v>1249.595569912</v>
+        <v>1242.837406776</v>
       </c>
       <c r="P10">
-        <v>3465.859410887999</v>
+        <v>3447.115071623999</v>
       </c>
       <c r="Q10">
-        <v>6881.259410887998</v>
+        <v>6862.515071623999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07511004973776295</v>
+        <v>0.07535191223992141</v>
       </c>
       <c r="T10">
-        <v>0.6769064604564192</v>
+        <v>0.6824921995362913</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.11270726907176</v>
+        <v>21.43351757250823</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07189758513832847</v>
+        <v>0.07173628451791506</v>
       </c>
       <c r="C11">
-        <v>42538.61721084741</v>
+        <v>42147.02302988373</v>
       </c>
       <c r="D11">
-        <v>46507.98921084741</v>
+        <v>46623.40302988374</v>
       </c>
       <c r="E11">
-        <v>-29424.128</v>
+        <v>-28917.12</v>
       </c>
       <c r="F11">
-        <v>4563.071999999999</v>
+        <v>5070.079999999999</v>
       </c>
       <c r="G11">
         <v>593.7</v>
@@ -2195,28 +2195,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M11">
-        <v>229.5225215999999</v>
+        <v>255.0250239999999</v>
       </c>
       <c r="N11">
-        <v>4689.952478399999</v>
+        <v>4664.449975999999</v>
       </c>
       <c r="O11">
-        <v>1242.837406776</v>
+        <v>1236.07924364</v>
       </c>
       <c r="P11">
-        <v>3447.115071623999</v>
+        <v>3428.370732359999</v>
       </c>
       <c r="Q11">
-        <v>6862.515071623999</v>
+        <v>6843.770732359999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07535191223992141</v>
+        <v>0.07559914946435006</v>
       </c>
       <c r="T11">
-        <v>0.6824921995362913</v>
+        <v>0.6882020661512716</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.43351757250823</v>
+        <v>19.29016581525741</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07173628451791506</v>
+        <v>0.07157498389750162</v>
       </c>
       <c r="C12">
-        <v>42147.02302988373</v>
+        <v>41756.00309380784</v>
       </c>
       <c r="D12">
-        <v>46623.40302988374</v>
+        <v>46739.39109380784</v>
       </c>
       <c r="E12">
-        <v>-28917.12</v>
+        <v>-28410.112</v>
       </c>
       <c r="F12">
-        <v>5070.08</v>
+        <v>5577.088</v>
       </c>
       <c r="G12">
         <v>593.7</v>
@@ -2277,28 +2277,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M12">
-        <v>255.025024</v>
+        <v>280.5275264</v>
       </c>
       <c r="N12">
-        <v>4664.449975999999</v>
+        <v>4638.947473599998</v>
       </c>
       <c r="O12">
-        <v>1236.07924364</v>
+        <v>1229.321080504</v>
       </c>
       <c r="P12">
-        <v>3428.370732359999</v>
+        <v>3409.626393095999</v>
       </c>
       <c r="Q12">
-        <v>6843.770732359999</v>
+        <v>6825.026393095999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07559914946435006</v>
+        <v>0.07585194258146249</v>
       </c>
       <c r="T12">
-        <v>0.6882020661512716</v>
+        <v>0.6940402443755773</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.29016581525741</v>
+        <v>17.53651437750673</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07157498389750162</v>
+        <v>0.07141368327708819</v>
       </c>
       <c r="C13">
-        <v>41756.00309380784</v>
+        <v>41365.56169906703</v>
       </c>
       <c r="D13">
-        <v>46739.39109380784</v>
+        <v>46855.95769906703</v>
       </c>
       <c r="E13">
-        <v>-28410.112</v>
+        <v>-27903.104</v>
       </c>
       <c r="F13">
-        <v>5577.088</v>
+        <v>6084.096</v>
       </c>
       <c r="G13">
         <v>593.7</v>
@@ -2359,28 +2359,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M13">
-        <v>280.5275264</v>
+        <v>306.0300288</v>
       </c>
       <c r="N13">
-        <v>4638.947473599998</v>
+        <v>4613.444971199999</v>
       </c>
       <c r="O13">
-        <v>1229.321080504</v>
+        <v>1222.562917368</v>
       </c>
       <c r="P13">
-        <v>3409.626393095999</v>
+        <v>3390.882053831999</v>
       </c>
       <c r="Q13">
-        <v>6825.026393095999</v>
+        <v>6806.282053831999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07585194258146249</v>
+        <v>0.07611048099669113</v>
       </c>
       <c r="T13">
-        <v>0.6940402443755773</v>
+        <v>0.7000111084686172</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.53651437750673</v>
+        <v>16.07513817938117</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07141368327708819</v>
+        <v>0.07125238265667476</v>
       </c>
       <c r="C14">
-        <v>41365.56169906703</v>
+        <v>40975.70318507661</v>
       </c>
       <c r="D14">
-        <v>46855.95769906703</v>
+        <v>46973.10718507661</v>
       </c>
       <c r="E14">
-        <v>-27903.104</v>
+        <v>-27396.096</v>
       </c>
       <c r="F14">
-        <v>6084.096</v>
+        <v>6591.103999999999</v>
       </c>
       <c r="G14">
         <v>593.7</v>
@@ -2441,28 +2441,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M14">
-        <v>306.0300288</v>
+        <v>331.5325311999999</v>
       </c>
       <c r="N14">
-        <v>4613.444971199999</v>
+        <v>4587.942468799999</v>
       </c>
       <c r="O14">
-        <v>1222.562917368</v>
+        <v>1215.804754232</v>
       </c>
       <c r="P14">
-        <v>3390.882053831999</v>
+        <v>3372.137714567999</v>
       </c>
       <c r="Q14">
-        <v>6806.282053831999</v>
+        <v>6787.537714568</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07611048099669113</v>
+        <v>0.07637496282376409</v>
       </c>
       <c r="T14">
-        <v>0.7000111084686172</v>
+        <v>0.7061192338051754</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.07513817938117</v>
+        <v>14.83858908865954</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07125238265667476</v>
+        <v>0.07109108203626133</v>
       </c>
       <c r="C15">
-        <v>40975.70318507661</v>
+        <v>40586.43193475838</v>
       </c>
       <c r="D15">
-        <v>46973.10718507661</v>
+        <v>47090.84393475838</v>
       </c>
       <c r="E15">
-        <v>-27396.096</v>
+        <v>-26889.088</v>
       </c>
       <c r="F15">
-        <v>6591.103999999999</v>
+        <v>7098.112</v>
       </c>
       <c r="G15">
         <v>593.7</v>
@@ -2523,28 +2523,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M15">
-        <v>331.5325311999999</v>
+        <v>357.0350336</v>
       </c>
       <c r="N15">
-        <v>4587.942468799999</v>
+        <v>4562.439966399998</v>
       </c>
       <c r="O15">
-        <v>1215.804754232</v>
+        <v>1209.046591096</v>
       </c>
       <c r="P15">
-        <v>3372.137714567999</v>
+        <v>3353.393375303999</v>
       </c>
       <c r="Q15">
-        <v>6787.537714568</v>
+        <v>6768.793375303999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07637496282376409</v>
+        <v>0.07664559539100155</v>
       </c>
       <c r="T15">
-        <v>0.7061192338051754</v>
+        <v>0.7123694085681651</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.83858908865954</v>
+        <v>13.778689868041</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07109108203626133</v>
+        <v>0.0709297814158479</v>
       </c>
       <c r="C16">
-        <v>40586.43193475838</v>
+        <v>40197.7523750872</v>
       </c>
       <c r="D16">
-        <v>47090.84393475838</v>
+        <v>47209.1723750872</v>
       </c>
       <c r="E16">
-        <v>-26889.088</v>
+        <v>-26382.07999999999</v>
       </c>
       <c r="F16">
-        <v>7098.112</v>
+        <v>7605.120000000001</v>
       </c>
       <c r="G16">
         <v>593.7</v>
@@ -2605,28 +2605,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M16">
-        <v>357.0350336</v>
+        <v>382.537536</v>
       </c>
       <c r="N16">
-        <v>4562.439966399998</v>
+        <v>4536.937463999999</v>
       </c>
       <c r="O16">
-        <v>1209.046591096</v>
+        <v>1202.28842796</v>
       </c>
       <c r="P16">
-        <v>3353.393375303999</v>
+        <v>3334.649036039999</v>
       </c>
       <c r="Q16">
-        <v>6768.793375303999</v>
+        <v>6750.049036039999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07664559539100155</v>
+        <v>0.07692259578335046</v>
       </c>
       <c r="T16">
-        <v>0.7123694085681651</v>
+        <v>0.7187666462667545</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.778689868041</v>
+        <v>12.86011054350493</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0709297814158479</v>
+        <v>0.07076848079543448</v>
       </c>
       <c r="C17">
-        <v>40197.75237508721</v>
+        <v>39809.66897764592</v>
       </c>
       <c r="D17">
-        <v>47209.1723750872</v>
+        <v>47328.09697764592</v>
       </c>
       <c r="E17">
-        <v>-26382.08</v>
+        <v>-25875.072</v>
       </c>
       <c r="F17">
-        <v>7605.119999999999</v>
+        <v>8112.128</v>
       </c>
       <c r="G17">
         <v>593.7</v>
@@ -2687,28 +2687,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M17">
-        <v>382.5375359999999</v>
+        <v>408.0400384</v>
       </c>
       <c r="N17">
-        <v>4536.937463999999</v>
+        <v>4511.434961599998</v>
       </c>
       <c r="O17">
-        <v>1202.28842796</v>
+        <v>1195.530264823999</v>
       </c>
       <c r="P17">
-        <v>3334.649036039999</v>
+        <v>3315.904696775999</v>
       </c>
       <c r="Q17">
-        <v>6750.049036039999</v>
+        <v>6731.304696775998</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07692259578335046</v>
+        <v>0.07720619142313628</v>
       </c>
       <c r="T17">
-        <v>0.7187666462667545</v>
+        <v>0.7253161991486438</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.86011054350494</v>
+        <v>12.05635363453588</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07076848079543448</v>
+        <v>0.07060718017502104</v>
       </c>
       <c r="C18">
-        <v>39809.66897764592</v>
+        <v>39422.18625918864</v>
       </c>
       <c r="D18">
-        <v>47328.09697764592</v>
+        <v>47447.62225918864</v>
       </c>
       <c r="E18">
-        <v>-25875.072</v>
+        <v>-25368.064</v>
       </c>
       <c r="F18">
-        <v>8112.128</v>
+        <v>8619.136</v>
       </c>
       <c r="G18">
         <v>593.7</v>
@@ -2769,28 +2769,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M18">
-        <v>408.0400384</v>
+        <v>433.5425408</v>
       </c>
       <c r="N18">
-        <v>4511.434961599998</v>
+        <v>4485.932459199998</v>
       </c>
       <c r="O18">
-        <v>1195.530264823999</v>
+        <v>1188.772101688</v>
       </c>
       <c r="P18">
-        <v>3315.904696775999</v>
+        <v>3297.160357511999</v>
       </c>
       <c r="Q18">
-        <v>6731.304696775998</v>
+        <v>6712.560357511999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07720619142313628</v>
+        <v>0.07749662069279643</v>
       </c>
       <c r="T18">
-        <v>0.7253161991486438</v>
+        <v>0.7320235725819038</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.05635363453588</v>
+        <v>11.34715636191612</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07060718017502104</v>
+        <v>0.07044587955460761</v>
       </c>
       <c r="C19">
-        <v>39422.18625918864</v>
+        <v>39035.30878221249</v>
       </c>
       <c r="D19">
-        <v>47447.62225918864</v>
+        <v>47567.75278221249</v>
       </c>
       <c r="E19">
-        <v>-25368.064</v>
+        <v>-24861.056</v>
       </c>
       <c r="F19">
-        <v>8619.136</v>
+        <v>9126.144</v>
       </c>
       <c r="G19">
         <v>593.7</v>
@@ -2851,28 +2851,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M19">
-        <v>433.5425408</v>
+        <v>459.0450432</v>
       </c>
       <c r="N19">
-        <v>4485.932459199998</v>
+        <v>4460.429956799999</v>
       </c>
       <c r="O19">
-        <v>1188.772101688</v>
+        <v>1182.013938552</v>
       </c>
       <c r="P19">
-        <v>3297.160357511999</v>
+        <v>3278.416018247999</v>
       </c>
       <c r="Q19">
-        <v>6712.560357511999</v>
+        <v>6693.816018247999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07749662069279643</v>
+        <v>0.07779413360318001</v>
       </c>
       <c r="T19">
-        <v>0.7320235725819038</v>
+        <v>0.7388945404891457</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.34715636191612</v>
+        <v>10.71675878625411</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07044587955460761</v>
+        <v>0.07028457893419418</v>
       </c>
       <c r="C20">
-        <v>39035.30878221249</v>
+        <v>38649.04115553825</v>
       </c>
       <c r="D20">
-        <v>47567.75278221249</v>
+        <v>47688.49315553825</v>
       </c>
       <c r="E20">
-        <v>-24861.056</v>
+        <v>-24354.048</v>
       </c>
       <c r="F20">
-        <v>9126.143999999998</v>
+        <v>9633.152</v>
       </c>
       <c r="G20">
         <v>593.7</v>
@@ -2933,28 +2933,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M20">
-        <v>459.0450431999999</v>
+        <v>484.5475456</v>
       </c>
       <c r="N20">
-        <v>4460.429956799999</v>
+        <v>4434.927454399998</v>
       </c>
       <c r="O20">
-        <v>1182.013938552</v>
+        <v>1175.255775416</v>
       </c>
       <c r="P20">
-        <v>3278.416018247999</v>
+        <v>3259.671678983998</v>
       </c>
       <c r="Q20">
-        <v>6693.816018247999</v>
+        <v>6675.071678983999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07779413360318001</v>
+        <v>0.07809899251135083</v>
       </c>
       <c r="T20">
-        <v>0.7388945404891457</v>
+        <v>0.7459351619249616</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.71675878625411</v>
+        <v>10.15271885013548</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07028457893419418</v>
+        <v>0.07012327831378076</v>
       </c>
       <c r="C21">
-        <v>38649.04115553825</v>
+        <v>38263.3880348997</v>
       </c>
       <c r="D21">
-        <v>47688.49315553825</v>
+        <v>47809.84803489971</v>
       </c>
       <c r="E21">
-        <v>-24354.048</v>
+        <v>-23847.04</v>
       </c>
       <c r="F21">
-        <v>9633.152</v>
+        <v>10140.16</v>
       </c>
       <c r="G21">
         <v>593.7</v>
@@ -3015,28 +3015,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M21">
-        <v>484.5475456</v>
+        <v>510.0500479999999</v>
       </c>
       <c r="N21">
-        <v>4434.927454399998</v>
+        <v>4409.424951999998</v>
       </c>
       <c r="O21">
-        <v>1175.255775416</v>
+        <v>1168.49761228</v>
       </c>
       <c r="P21">
-        <v>3259.671678983998</v>
+        <v>3240.927339719999</v>
       </c>
       <c r="Q21">
-        <v>6675.071678983999</v>
+        <v>6656.327339719999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07809899251135083</v>
+        <v>0.07841147289222594</v>
       </c>
       <c r="T21">
-        <v>0.7459351619249616</v>
+        <v>0.7531517988966728</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.15271885013548</v>
+        <v>9.645082907628701</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07012327831378076</v>
+        <v>0.06996197769336732</v>
       </c>
       <c r="C22">
-        <v>38263.3880348997</v>
+        <v>37878.35412354216</v>
       </c>
       <c r="D22">
-        <v>47809.84803489971</v>
+        <v>47931.82212354216</v>
       </c>
       <c r="E22">
-        <v>-23847.04</v>
+        <v>-23340.032</v>
       </c>
       <c r="F22">
-        <v>10140.16</v>
+        <v>10647.168</v>
       </c>
       <c r="G22">
         <v>593.7</v>
@@ -3097,28 +3097,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M22">
-        <v>510.0500479999999</v>
+        <v>535.5525504</v>
       </c>
       <c r="N22">
-        <v>4409.424951999998</v>
+        <v>4383.922449599999</v>
       </c>
       <c r="O22">
-        <v>1168.49761228</v>
+        <v>1161.739449144</v>
       </c>
       <c r="P22">
-        <v>3240.927339719999</v>
+        <v>3222.183000455999</v>
       </c>
       <c r="Q22">
-        <v>6656.327339719999</v>
+        <v>6637.583000455999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07841147289222594</v>
+        <v>0.07873186416881939</v>
       </c>
       <c r="T22">
-        <v>0.7531517988966728</v>
+        <v>0.7605511355385539</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.645082907628701</v>
+        <v>9.185793245360669</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06996197769336732</v>
+        <v>0.06980067707295388</v>
       </c>
       <c r="C23">
-        <v>37878.35412354216</v>
+        <v>37493.94417282989</v>
       </c>
       <c r="D23">
-        <v>47931.82212354216</v>
+        <v>48054.42017282989</v>
       </c>
       <c r="E23">
-        <v>-23340.032</v>
+        <v>-22833.024</v>
       </c>
       <c r="F23">
-        <v>10647.168</v>
+        <v>11154.176</v>
       </c>
       <c r="G23">
         <v>593.7</v>
@@ -3179,28 +3179,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M23">
-        <v>535.5525503999999</v>
+        <v>561.0550528</v>
       </c>
       <c r="N23">
-        <v>4383.922449599999</v>
+        <v>4358.419947199998</v>
       </c>
       <c r="O23">
-        <v>1161.739449144</v>
+        <v>1154.981286008</v>
       </c>
       <c r="P23">
-        <v>3222.183000455999</v>
+        <v>3203.438661191999</v>
       </c>
       <c r="Q23">
-        <v>6637.583000455999</v>
+        <v>6618.838661191999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07873186416881939</v>
+        <v>0.07906047060635113</v>
       </c>
       <c r="T23">
-        <v>0.7605511355385539</v>
+        <v>0.7681401987609962</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.185793245360671</v>
+        <v>8.768257188753363</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06980067707295388</v>
+        <v>0.06989295145254046</v>
       </c>
       <c r="C24">
-        <v>37493.94417282989</v>
+        <v>36916.72551183125</v>
       </c>
       <c r="D24">
-        <v>48054.42017282989</v>
+        <v>47984.20951183125</v>
       </c>
       <c r="E24">
-        <v>-22833.024</v>
+        <v>-22326.016</v>
       </c>
       <c r="F24">
-        <v>11154.176</v>
+        <v>11661.184</v>
       </c>
       <c r="G24">
         <v>593.7</v>
@@ -3261,45 +3261,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M24">
-        <v>561.0550528</v>
+        <v>604.0493312</v>
       </c>
       <c r="N24">
-        <v>4358.419947199998</v>
+        <v>4315.425668799999</v>
       </c>
       <c r="O24">
-        <v>1154.981286008</v>
+        <v>1143.587802232</v>
       </c>
       <c r="P24">
-        <v>3203.438661191999</v>
+        <v>3171.837866567999</v>
       </c>
       <c r="Q24">
-        <v>6618.838661191999</v>
+        <v>6587.237866567999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07906047060635113</v>
+        <v>0.07939761227602657</v>
       </c>
       <c r="T24">
-        <v>0.7681401987609962</v>
+        <v>0.7759263805086966</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.265</v>
       </c>
       <c r="W24">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.768257188753363</v>
+        <v>8.144160991333283</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06989295145254046</v>
+        <v>0.06974267583212702</v>
       </c>
       <c r="C25">
-        <v>36916.72551183125</v>
+        <v>36524.16600402581</v>
       </c>
       <c r="D25">
-        <v>47984.20951183125</v>
+        <v>48098.65800402581</v>
       </c>
       <c r="E25">
-        <v>-22326.016</v>
+        <v>-21819.008</v>
       </c>
       <c r="F25">
-        <v>11661.184</v>
+        <v>12168.192</v>
       </c>
       <c r="G25">
         <v>593.7</v>
@@ -3343,28 +3343,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M25">
-        <v>604.0493312</v>
+        <v>630.3123456</v>
       </c>
       <c r="N25">
-        <v>4315.425668799999</v>
+        <v>4289.162654399998</v>
       </c>
       <c r="O25">
-        <v>1143.587802232</v>
+        <v>1136.628103416</v>
       </c>
       <c r="P25">
-        <v>3171.837866567999</v>
+        <v>3152.534550983999</v>
       </c>
       <c r="Q25">
-        <v>6587.237866567999</v>
+        <v>6567.934550983999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07939761227602657</v>
+        <v>0.07974362609490399</v>
       </c>
       <c r="T25">
-        <v>0.7759263805086966</v>
+        <v>0.7839174617760735</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.144160991333283</v>
+        <v>7.80482095002773</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06974267583212702</v>
+        <v>0.06959240021171359</v>
       </c>
       <c r="C26">
-        <v>36524.16600402581</v>
+        <v>36132.15375014798</v>
       </c>
       <c r="D26">
-        <v>48098.65800402581</v>
+        <v>48213.65375014798</v>
       </c>
       <c r="E26">
-        <v>-21819.008</v>
+        <v>-21312</v>
       </c>
       <c r="F26">
-        <v>12168.192</v>
+        <v>12675.2</v>
       </c>
       <c r="G26">
         <v>593.7</v>
@@ -3425,28 +3425,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M26">
-        <v>630.3123456</v>
+        <v>656.5753599999999</v>
       </c>
       <c r="N26">
-        <v>4289.162654399998</v>
+        <v>4262.899639999999</v>
       </c>
       <c r="O26">
-        <v>1136.628103416</v>
+        <v>1129.6684046</v>
       </c>
       <c r="P26">
-        <v>3152.534550983999</v>
+        <v>3133.231235399999</v>
       </c>
       <c r="Q26">
-        <v>6567.934550983999</v>
+        <v>6548.631235399998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07974362609490399</v>
+        <v>0.08009886694895146</v>
       </c>
       <c r="T26">
-        <v>0.7839174617760735</v>
+        <v>0.7921216385439136</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.80482095002773</v>
+        <v>7.492628112026622</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06959240021171359</v>
+        <v>0.06944212459130016</v>
       </c>
       <c r="C27">
-        <v>36132.15375014798</v>
+        <v>35740.69268477906</v>
       </c>
       <c r="D27">
-        <v>48213.65375014798</v>
+        <v>48329.20068477906</v>
       </c>
       <c r="E27">
-        <v>-21312</v>
+        <v>-20804.992</v>
       </c>
       <c r="F27">
-        <v>12675.2</v>
+        <v>13182.208</v>
       </c>
       <c r="G27">
         <v>593.7</v>
@@ -3507,28 +3507,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M27">
-        <v>656.5753599999999</v>
+        <v>682.8383743999999</v>
       </c>
       <c r="N27">
-        <v>4262.899639999999</v>
+        <v>4236.636625599998</v>
       </c>
       <c r="O27">
-        <v>1129.6684046</v>
+        <v>1122.708705784</v>
       </c>
       <c r="P27">
-        <v>3133.231235399999</v>
+        <v>3113.927919815998</v>
       </c>
       <c r="Q27">
-        <v>6548.631235399998</v>
+        <v>6529.327919815998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08009886694895146</v>
+        <v>0.08046370890716238</v>
       </c>
       <c r="T27">
-        <v>0.7921216385439136</v>
+        <v>0.8005475498189927</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.492628112026622</v>
+        <v>7.204450107717904</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06944212459130016</v>
+        <v>0.06929184897088672</v>
       </c>
       <c r="C28">
-        <v>35740.69268477906</v>
+        <v>35349.78678030883</v>
       </c>
       <c r="D28">
-        <v>48329.20068477906</v>
+        <v>48445.30278030883</v>
       </c>
       <c r="E28">
-        <v>-20804.992</v>
+        <v>-20297.984</v>
       </c>
       <c r="F28">
-        <v>13182.208</v>
+        <v>13689.216</v>
       </c>
       <c r="G28">
         <v>593.7</v>
@@ -3589,28 +3589,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M28">
-        <v>682.8383743999999</v>
+        <v>709.1013888</v>
       </c>
       <c r="N28">
-        <v>4236.636625599998</v>
+        <v>4210.373611199999</v>
       </c>
       <c r="O28">
-        <v>1122.708705784</v>
+        <v>1115.749006968</v>
       </c>
       <c r="P28">
-        <v>3113.927919815998</v>
+        <v>3094.624604231999</v>
       </c>
       <c r="Q28">
-        <v>6529.327919815998</v>
+        <v>6510.024604232</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08046370890716238</v>
+        <v>0.08083854653546127</v>
       </c>
       <c r="T28">
-        <v>0.8005475498189927</v>
+        <v>0.8092043079783204</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.204450107717904</v>
+        <v>6.937618622246871</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06929184897088672</v>
+        <v>0.06949143335047331</v>
       </c>
       <c r="C29">
-        <v>35349.78678030883</v>
+        <v>34688.70217633218</v>
       </c>
       <c r="D29">
-        <v>48445.30278030883</v>
+        <v>48291.22617633219</v>
       </c>
       <c r="E29">
-        <v>-20297.984</v>
+        <v>-19790.976</v>
       </c>
       <c r="F29">
-        <v>13689.216</v>
+        <v>14196.224</v>
       </c>
       <c r="G29">
         <v>593.7</v>
@@ -3671,45 +3671,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M29">
-        <v>709.1013888</v>
+        <v>759.497984</v>
       </c>
       <c r="N29">
-        <v>4210.373611199999</v>
+        <v>4159.977015999999</v>
       </c>
       <c r="O29">
-        <v>1115.749006968</v>
+        <v>1102.39390924</v>
       </c>
       <c r="P29">
-        <v>3094.624604231999</v>
+        <v>3057.583106759999</v>
       </c>
       <c r="Q29">
-        <v>6510.024604232</v>
+        <v>6472.983106759999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08083854653546127</v>
+        <v>0.08122379632010181</v>
       </c>
       <c r="T29">
-        <v>0.8092043079783204</v>
+        <v>0.8181015316420741</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.265</v>
       </c>
       <c r="W29">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.937618622246871</v>
+        <v>6.477271966004322</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06949143335047331</v>
+        <v>0.06935365273005988</v>
       </c>
       <c r="C30">
-        <v>34688.70217633218</v>
+        <v>34287.9540791094</v>
       </c>
       <c r="D30">
-        <v>48291.22617633219</v>
+        <v>48397.4860791094</v>
       </c>
       <c r="E30">
-        <v>-19790.976</v>
+        <v>-19283.968</v>
       </c>
       <c r="F30">
-        <v>14196.224</v>
+        <v>14703.232</v>
       </c>
       <c r="G30">
         <v>593.7</v>
@@ -3753,28 +3753,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M30">
-        <v>759.497984</v>
+        <v>786.6229119999999</v>
       </c>
       <c r="N30">
-        <v>4159.977015999999</v>
+        <v>4132.852087999999</v>
       </c>
       <c r="O30">
-        <v>1102.39390924</v>
+        <v>1095.20580332</v>
       </c>
       <c r="P30">
-        <v>3057.583106759999</v>
+        <v>3037.646284679999</v>
       </c>
       <c r="Q30">
-        <v>6472.983106759999</v>
+        <v>6453.046284679999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08122379632010181</v>
+        <v>0.08161989821135193</v>
       </c>
       <c r="T30">
-        <v>0.8181015316420741</v>
+        <v>0.827249381324525</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.477271966004322</v>
+        <v>6.253917760280035</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06935365273005986</v>
+        <v>0.06921587210964644</v>
       </c>
       <c r="C31">
-        <v>34287.95407910941</v>
+        <v>33887.67464121385</v>
       </c>
       <c r="D31">
-        <v>48397.48607910941</v>
+        <v>48504.21464121385</v>
       </c>
       <c r="E31">
-        <v>-19283.968</v>
+        <v>-18776.96</v>
       </c>
       <c r="F31">
-        <v>14703.232</v>
+        <v>15210.24</v>
       </c>
       <c r="G31">
         <v>593.7</v>
@@ -3835,28 +3835,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M31">
-        <v>786.6229119999999</v>
+        <v>813.7478399999999</v>
       </c>
       <c r="N31">
-        <v>4132.852087999999</v>
+        <v>4105.727159999999</v>
       </c>
       <c r="O31">
-        <v>1095.20580332</v>
+        <v>1088.0176974</v>
       </c>
       <c r="P31">
-        <v>3037.646284679999</v>
+        <v>3017.709462599999</v>
       </c>
       <c r="Q31">
-        <v>6453.046284679999</v>
+        <v>6433.109462599999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08161989821135193</v>
+        <v>0.08202731729949492</v>
       </c>
       <c r="T31">
-        <v>0.827249381324525</v>
+        <v>0.83665859814076</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.253917760280035</v>
+        <v>6.045453834937367</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06921587210964644</v>
+        <v>0.069078091489233</v>
       </c>
       <c r="C32">
-        <v>33887.67464121385</v>
+        <v>33487.86697003122</v>
       </c>
       <c r="D32">
-        <v>48504.21464121385</v>
+        <v>48611.41497003122</v>
       </c>
       <c r="E32">
-        <v>-18776.96</v>
+        <v>-18269.952</v>
       </c>
       <c r="F32">
-        <v>15210.24</v>
+        <v>15717.248</v>
       </c>
       <c r="G32">
         <v>593.7</v>
@@ -3917,28 +3917,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M32">
-        <v>813.7478399999999</v>
+        <v>840.8727679999998</v>
       </c>
       <c r="N32">
-        <v>4105.727159999999</v>
+        <v>4078.602231999999</v>
       </c>
       <c r="O32">
-        <v>1088.0176974</v>
+        <v>1080.82959148</v>
       </c>
       <c r="P32">
-        <v>3017.709462599999</v>
+        <v>2997.772640519999</v>
       </c>
       <c r="Q32">
-        <v>6433.109462599999</v>
+        <v>6413.172640519999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08202731729949492</v>
+        <v>0.08244654563656957</v>
       </c>
       <c r="T32">
-        <v>0.83665859814076</v>
+        <v>0.8463405458792049</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.045453834937367</v>
+        <v>5.850439195100678</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.069078091489233</v>
+        <v>0.06894031086881958</v>
       </c>
       <c r="C33">
-        <v>33487.86697003122</v>
+        <v>33088.53420047883</v>
       </c>
       <c r="D33">
-        <v>48611.41497003122</v>
+        <v>48719.09020047884</v>
       </c>
       <c r="E33">
-        <v>-18269.952</v>
+        <v>-17762.944</v>
       </c>
       <c r="F33">
-        <v>15717.248</v>
+        <v>16224.256</v>
       </c>
       <c r="G33">
         <v>593.7</v>
@@ -3999,28 +3999,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M33">
-        <v>840.8727679999998</v>
+        <v>867.9976959999999</v>
       </c>
       <c r="N33">
-        <v>4078.602231999999</v>
+        <v>4051.477303999999</v>
       </c>
       <c r="O33">
-        <v>1080.82959148</v>
+        <v>1073.64148556</v>
       </c>
       <c r="P33">
-        <v>2997.772640519999</v>
+        <v>2977.835818439999</v>
       </c>
       <c r="Q33">
-        <v>6413.172640519999</v>
+        <v>6393.235818439999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08244654563656957</v>
+        <v>0.08287810421885232</v>
       </c>
       <c r="T33">
-        <v>0.8463405458792049</v>
+        <v>0.8563072567864277</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.850439195100678</v>
+        <v>5.667612970253781</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06894031086881958</v>
+        <v>0.06899657024840614</v>
       </c>
       <c r="C34">
-        <v>33088.53420047883</v>
+        <v>32537.50205859626</v>
       </c>
       <c r="D34">
-        <v>48719.09020047884</v>
+        <v>48675.06605859626</v>
       </c>
       <c r="E34">
-        <v>-17762.944</v>
+        <v>-17255.936</v>
       </c>
       <c r="F34">
-        <v>16224.256</v>
+        <v>16731.264</v>
       </c>
       <c r="G34">
         <v>593.7</v>
@@ -4081,45 +4081,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M34">
-        <v>867.9976959999999</v>
+        <v>908.5076352</v>
       </c>
       <c r="N34">
-        <v>4051.477303999999</v>
+        <v>4010.967364799998</v>
       </c>
       <c r="O34">
-        <v>1073.64148556</v>
+        <v>1062.906351672</v>
       </c>
       <c r="P34">
-        <v>2977.835818439999</v>
+        <v>2948.061013127999</v>
       </c>
       <c r="Q34">
-        <v>6393.235818439999</v>
+        <v>6363.461013127999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08287810421885232</v>
+        <v>0.08332254514687484</v>
       </c>
       <c r="T34">
-        <v>0.8563072567864277</v>
+        <v>0.866571481452075</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.265</v>
       </c>
       <c r="W34">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.667612970253781</v>
+        <v>5.414896704656774</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06899657024840614</v>
+        <v>0.0688646696279927</v>
       </c>
       <c r="C35">
-        <v>32537.50205859626</v>
+        <v>32133.83472082702</v>
       </c>
       <c r="D35">
-        <v>48675.06605859626</v>
+        <v>48778.40672082702</v>
       </c>
       <c r="E35">
-        <v>-17255.936</v>
+        <v>-16748.928</v>
       </c>
       <c r="F35">
-        <v>16731.264</v>
+        <v>17238.272</v>
       </c>
       <c r="G35">
         <v>593.7</v>
@@ -4163,28 +4163,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M35">
-        <v>908.5076352</v>
+        <v>936.0381696000001</v>
       </c>
       <c r="N35">
-        <v>4010.967364799998</v>
+        <v>3983.436830399999</v>
       </c>
       <c r="O35">
-        <v>1062.906351672</v>
+        <v>1055.610760056</v>
       </c>
       <c r="P35">
-        <v>2948.061013127999</v>
+        <v>2927.826070343999</v>
       </c>
       <c r="Q35">
-        <v>6363.461013127999</v>
+        <v>6343.226070343999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08332254514687484</v>
+        <v>0.08378045398180714</v>
       </c>
       <c r="T35">
-        <v>0.866571481452075</v>
+        <v>0.8771467432288024</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.414896704656774</v>
+        <v>5.255635036872751</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0688646696279927</v>
+        <v>0.06873276900757928</v>
       </c>
       <c r="C36">
-        <v>32133.83472082702</v>
+        <v>31730.60711594282</v>
       </c>
       <c r="D36">
-        <v>48778.40672082702</v>
+        <v>48882.18711594282</v>
       </c>
       <c r="E36">
-        <v>-16748.928</v>
+        <v>-16241.92</v>
       </c>
       <c r="F36">
-        <v>17238.272</v>
+        <v>17745.28</v>
       </c>
       <c r="G36">
         <v>593.7</v>
@@ -4245,28 +4245,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M36">
-        <v>936.0381696000001</v>
+        <v>963.5687039999999</v>
       </c>
       <c r="N36">
-        <v>3983.436830399999</v>
+        <v>3955.906295999999</v>
       </c>
       <c r="O36">
-        <v>1055.610760056</v>
+        <v>1048.31516844</v>
       </c>
       <c r="P36">
-        <v>2927.826070343999</v>
+        <v>2907.591127559999</v>
       </c>
       <c r="Q36">
-        <v>6343.226070343999</v>
+        <v>6322.991127559999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08378045398180714</v>
+        <v>0.08425245231935274</v>
       </c>
       <c r="T36">
-        <v>0.8771467432288024</v>
+        <v>0.8880473976755831</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.255635036872751</v>
+        <v>5.105474035819245</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06873276900757928</v>
+        <v>0.06860086838716585</v>
       </c>
       <c r="C37">
-        <v>31730.60711594282</v>
+        <v>31327.82205664031</v>
       </c>
       <c r="D37">
-        <v>48882.18711594282</v>
+        <v>48986.41005664031</v>
       </c>
       <c r="E37">
-        <v>-16241.92</v>
+        <v>-15734.912</v>
       </c>
       <c r="F37">
-        <v>17745.28</v>
+        <v>18252.288</v>
       </c>
       <c r="G37">
         <v>593.7</v>
@@ -4327,28 +4327,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M37">
-        <v>963.5687039999999</v>
+        <v>991.0992384</v>
       </c>
       <c r="N37">
-        <v>3955.906295999999</v>
+        <v>3928.375761599998</v>
       </c>
       <c r="O37">
-        <v>1048.31516844</v>
+        <v>1041.019576824</v>
       </c>
       <c r="P37">
-        <v>2907.591127559999</v>
+        <v>2887.356184775999</v>
       </c>
       <c r="Q37">
-        <v>6322.991127559999</v>
+        <v>6302.756184775999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08425245231935274</v>
+        <v>0.08473920060494665</v>
       </c>
       <c r="T37">
-        <v>0.8880473976755831</v>
+        <v>0.8992886975738257</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.105474035819245</v>
+        <v>4.963655312602043</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06860086838716585</v>
+        <v>0.06846896776675242</v>
       </c>
       <c r="C38">
-        <v>31327.82205664031</v>
+        <v>30925.48237965547</v>
       </c>
       <c r="D38">
-        <v>48986.41005664031</v>
+        <v>49091.07837965548</v>
       </c>
       <c r="E38">
-        <v>-15734.912</v>
+        <v>-15227.904</v>
       </c>
       <c r="F38">
-        <v>18252.288</v>
+        <v>18759.296</v>
       </c>
       <c r="G38">
         <v>593.7</v>
@@ -4409,28 +4409,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M38">
-        <v>991.0992383999999</v>
+        <v>1018.6297728</v>
       </c>
       <c r="N38">
-        <v>3928.375761599998</v>
+        <v>3900.845227199999</v>
       </c>
       <c r="O38">
-        <v>1041.019576824</v>
+        <v>1033.723985208</v>
       </c>
       <c r="P38">
-        <v>2887.356184775999</v>
+        <v>2867.121241991999</v>
       </c>
       <c r="Q38">
-        <v>6302.756184775999</v>
+        <v>6282.521241991999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08473920060494665</v>
+        <v>0.08524140121706733</v>
       </c>
       <c r="T38">
-        <v>0.8992886975738257</v>
+        <v>0.9108868641355043</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.963655312602043</v>
+        <v>4.829502466315502</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06846896776675242</v>
+        <v>0.068337067146339</v>
       </c>
       <c r="C39">
-        <v>30925.48237965547</v>
+        <v>30523.59094602098</v>
       </c>
       <c r="D39">
-        <v>49091.07837965548</v>
+        <v>49196.19494602098</v>
       </c>
       <c r="E39">
-        <v>-15227.904</v>
+        <v>-14720.896</v>
       </c>
       <c r="F39">
-        <v>18759.296</v>
+        <v>19266.304</v>
       </c>
       <c r="G39">
         <v>593.7</v>
@@ -4491,28 +4491,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M39">
-        <v>1018.6297728</v>
+        <v>1046.1603072</v>
       </c>
       <c r="N39">
-        <v>3900.845227199999</v>
+        <v>3873.314692799999</v>
       </c>
       <c r="O39">
-        <v>1033.723985208</v>
+        <v>1026.428393592</v>
       </c>
       <c r="P39">
-        <v>2867.121241991999</v>
+        <v>2846.886299207999</v>
       </c>
       <c r="Q39">
-        <v>6282.521241991999</v>
+        <v>6262.286299207999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08524140121706733</v>
+        <v>0.08575980184893386</v>
       </c>
       <c r="T39">
-        <v>0.9108868641355043</v>
+        <v>0.9228591651023985</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.829502466315502</v>
+        <v>4.702410296149304</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.068337067146339</v>
+        <v>0.06820516652592556</v>
       </c>
       <c r="C40">
-        <v>30523.59094602098</v>
+        <v>30122.15064132692</v>
       </c>
       <c r="D40">
-        <v>49196.19494602098</v>
+        <v>49301.76264132692</v>
       </c>
       <c r="E40">
-        <v>-14720.896</v>
+        <v>-14213.888</v>
       </c>
       <c r="F40">
-        <v>19266.304</v>
+        <v>19773.312</v>
       </c>
       <c r="G40">
         <v>593.7</v>
@@ -4573,28 +4573,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M40">
-        <v>1046.1603072</v>
+        <v>1073.6908416</v>
       </c>
       <c r="N40">
-        <v>3873.314692799999</v>
+        <v>3845.784158399999</v>
       </c>
       <c r="O40">
-        <v>1026.428393592</v>
+        <v>1019.132801976</v>
       </c>
       <c r="P40">
-        <v>2846.886299207999</v>
+        <v>2826.651356423999</v>
       </c>
       <c r="Q40">
-        <v>6262.286299207999</v>
+        <v>6242.051356423999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08575980184893386</v>
+        <v>0.08629519922282879</v>
       </c>
       <c r="T40">
-        <v>0.9228591651023985</v>
+        <v>0.9352240005272238</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.702410296149304</v>
+        <v>4.581835673171117</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06820516652592556</v>
+        <v>0.06807326590551213</v>
       </c>
       <c r="C41">
-        <v>30122.15064132692</v>
+        <v>29721.16437598482</v>
       </c>
       <c r="D41">
-        <v>49301.76264132692</v>
+        <v>49407.78437598483</v>
       </c>
       <c r="E41">
-        <v>-14213.888</v>
+        <v>-13706.88</v>
       </c>
       <c r="F41">
-        <v>19773.312</v>
+        <v>20280.32</v>
       </c>
       <c r="G41">
         <v>593.7</v>
@@ -4655,28 +4655,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M41">
-        <v>1073.6908416</v>
+        <v>1101.221376</v>
       </c>
       <c r="N41">
-        <v>3845.784158399999</v>
+        <v>3818.253623999999</v>
       </c>
       <c r="O41">
-        <v>1019.132801976</v>
+        <v>1011.83721036</v>
       </c>
       <c r="P41">
-        <v>2826.651356423999</v>
+        <v>2806.416413639999</v>
       </c>
       <c r="Q41">
-        <v>6242.051356423999</v>
+        <v>6221.816413639999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08629519922282879</v>
+        <v>0.08684844317585355</v>
       </c>
       <c r="T41">
-        <v>0.9352240005272238</v>
+        <v>0.9480009971328764</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.581835673171117</v>
+        <v>4.467289781341838</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06807326590551213</v>
+        <v>0.0679413652850987</v>
       </c>
       <c r="C42">
-        <v>29721.16437598482</v>
+        <v>29320.63508549514</v>
       </c>
       <c r="D42">
-        <v>49407.78437598483</v>
+        <v>49514.26308549514</v>
       </c>
       <c r="E42">
-        <v>-13706.88</v>
+        <v>-13199.872</v>
       </c>
       <c r="F42">
-        <v>20280.32</v>
+        <v>20787.328</v>
       </c>
       <c r="G42">
         <v>593.7</v>
@@ -4737,28 +4737,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M42">
-        <v>1101.221376</v>
+        <v>1128.7519104</v>
       </c>
       <c r="N42">
-        <v>3818.253623999999</v>
+        <v>3790.723089599998</v>
       </c>
       <c r="O42">
-        <v>1011.83721036</v>
+        <v>1004.541618744</v>
       </c>
       <c r="P42">
-        <v>2806.416413639999</v>
+        <v>2786.181470855999</v>
       </c>
       <c r="Q42">
-        <v>6221.816413639999</v>
+        <v>6201.581470855999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08684844317585355</v>
+        <v>0.08742044116118423</v>
       </c>
       <c r="T42">
-        <v>0.9480009971328764</v>
+        <v>0.9612111122675343</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.467289781341838</v>
+        <v>4.358331493992037</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0679413652850987</v>
+        <v>0.06780946466468527</v>
       </c>
       <c r="C43">
-        <v>29320.63508549514</v>
+        <v>28920.56573071814</v>
       </c>
       <c r="D43">
-        <v>49514.26308549514</v>
+        <v>49621.20173071814</v>
       </c>
       <c r="E43">
-        <v>-13199.872</v>
+        <v>-12692.864</v>
       </c>
       <c r="F43">
-        <v>20787.328</v>
+        <v>21294.336</v>
       </c>
       <c r="G43">
         <v>593.7</v>
@@ -4819,28 +4819,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M43">
-        <v>1128.7519104</v>
+        <v>1156.2824448</v>
       </c>
       <c r="N43">
-        <v>3790.723089599998</v>
+        <v>3763.192555199998</v>
       </c>
       <c r="O43">
-        <v>1004.541618744</v>
+        <v>997.2460271279996</v>
       </c>
       <c r="P43">
-        <v>2786.181470855999</v>
+        <v>2765.946528071999</v>
       </c>
       <c r="Q43">
-        <v>6201.581470855999</v>
+        <v>6181.346528071999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08742044116118423</v>
+        <v>0.0880121632149746</v>
       </c>
       <c r="T43">
-        <v>0.9612111122675343</v>
+        <v>0.9748767486137322</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.358331493992037</v>
+        <v>4.254561696516037</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06780946466468527</v>
+        <v>0.06799361404427184</v>
       </c>
       <c r="C44">
-        <v>28920.56573071814</v>
+        <v>28264.38566358005</v>
       </c>
       <c r="D44">
-        <v>49621.20173071814</v>
+        <v>49472.02966358005</v>
       </c>
       <c r="E44">
-        <v>-12692.864</v>
+        <v>-12185.856</v>
       </c>
       <c r="F44">
-        <v>21294.336</v>
+        <v>21801.344</v>
       </c>
       <c r="G44">
         <v>593.7</v>
@@ -4901,45 +4901,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M44">
-        <v>1156.2824448</v>
+        <v>1205.6143232</v>
       </c>
       <c r="N44">
-        <v>3763.192555199998</v>
+        <v>3713.860676799999</v>
       </c>
       <c r="O44">
-        <v>997.2460271279996</v>
+        <v>984.1730793519997</v>
       </c>
       <c r="P44">
-        <v>2765.946528071999</v>
+        <v>2729.687597447999</v>
       </c>
       <c r="Q44">
-        <v>6181.346528071999</v>
+        <v>6145.087597447999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0880121632149746</v>
+        <v>0.08862464744609094</v>
       </c>
       <c r="T44">
-        <v>0.9748767486137322</v>
+        <v>0.9890218809720772</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.265</v>
       </c>
       <c r="W44">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.254561696516037</v>
+        <v>4.080471594715704</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06799361404427184</v>
+        <v>0.06786906342385841</v>
       </c>
       <c r="C45">
-        <v>28264.38566358005</v>
+        <v>27858.17278959253</v>
       </c>
       <c r="D45">
-        <v>49472.02966358005</v>
+        <v>49572.82478959253</v>
       </c>
       <c r="E45">
-        <v>-12185.856</v>
+        <v>-11678.848</v>
       </c>
       <c r="F45">
-        <v>21801.344</v>
+        <v>22308.352</v>
       </c>
       <c r="G45">
         <v>593.7</v>
@@ -4983,28 +4983,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M45">
-        <v>1205.6143232</v>
+        <v>1233.6518656</v>
       </c>
       <c r="N45">
-        <v>3713.860676799999</v>
+        <v>3685.823134399999</v>
       </c>
       <c r="O45">
-        <v>984.1730793519997</v>
+        <v>976.7431306159997</v>
       </c>
       <c r="P45">
-        <v>2729.687597447999</v>
+        <v>2709.080003783999</v>
       </c>
       <c r="Q45">
-        <v>6145.087597447999</v>
+        <v>6124.480003784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08862464744609094</v>
+        <v>0.08925900611403287</v>
       </c>
       <c r="T45">
-        <v>0.9890218809720772</v>
+        <v>1.003672196628935</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.080471594715704</v>
+        <v>3.987733603926711</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06786906342385841</v>
+        <v>0.06774451280344498</v>
       </c>
       <c r="C46">
-        <v>27858.17278959253</v>
+        <v>27452.37147741922</v>
       </c>
       <c r="D46">
-        <v>49572.82478959253</v>
+        <v>49674.03147741922</v>
       </c>
       <c r="E46">
-        <v>-11678.848</v>
+        <v>-11171.84</v>
       </c>
       <c r="F46">
-        <v>22308.352</v>
+        <v>22815.36</v>
       </c>
       <c r="G46">
         <v>593.7</v>
@@ -5065,28 +5065,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M46">
-        <v>1233.6518656</v>
+        <v>1261.689408</v>
       </c>
       <c r="N46">
-        <v>3685.823134399999</v>
+        <v>3657.785591999998</v>
       </c>
       <c r="O46">
-        <v>976.7431306159997</v>
+        <v>969.3131818799997</v>
       </c>
       <c r="P46">
-        <v>2709.080003783999</v>
+        <v>2688.472410119999</v>
       </c>
       <c r="Q46">
-        <v>6124.480003784</v>
+        <v>6103.872410119999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08925900611403287</v>
+        <v>0.08991643236989995</v>
       </c>
       <c r="T46">
-        <v>1.003672196628935</v>
+        <v>1.01885525103695</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.987733603926711</v>
+        <v>3.899117301617228</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06774451280344498</v>
+        <v>0.06761996218303154</v>
       </c>
       <c r="C47">
-        <v>27452.37147741922</v>
+        <v>27046.98425292098</v>
       </c>
       <c r="D47">
-        <v>49674.03147741922</v>
+        <v>49775.65225292098</v>
       </c>
       <c r="E47">
-        <v>-11171.84</v>
+        <v>-10664.832</v>
       </c>
       <c r="F47">
-        <v>22815.36</v>
+        <v>23322.368</v>
       </c>
       <c r="G47">
         <v>593.7</v>
@@ -5147,28 +5147,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M47">
-        <v>1261.689408</v>
+        <v>1289.7269504</v>
       </c>
       <c r="N47">
-        <v>3657.785591999998</v>
+        <v>3629.748049599998</v>
       </c>
       <c r="O47">
-        <v>969.3131818799997</v>
+        <v>961.8832331439996</v>
       </c>
       <c r="P47">
-        <v>2688.472410119999</v>
+        <v>2667.864816455999</v>
       </c>
       <c r="Q47">
-        <v>6103.872410119999</v>
+        <v>6083.264816456</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08991643236989995</v>
+        <v>0.09059820774635471</v>
       </c>
       <c r="T47">
-        <v>1.01885525103695</v>
+        <v>1.034600640793411</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.899117301617228</v>
+        <v>3.814353882016854</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06761996218303154</v>
+        <v>0.06749541156261812</v>
       </c>
       <c r="C48">
-        <v>27046.98425292098</v>
+        <v>26642.01366267018</v>
       </c>
       <c r="D48">
-        <v>49775.65225292098</v>
+        <v>49877.68966267018</v>
       </c>
       <c r="E48">
-        <v>-10664.832</v>
+        <v>-10157.824</v>
       </c>
       <c r="F48">
-        <v>23322.368</v>
+        <v>23829.376</v>
       </c>
       <c r="G48">
         <v>593.7</v>
@@ -5229,28 +5229,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M48">
-        <v>1289.7269504</v>
+        <v>1317.7644928</v>
       </c>
       <c r="N48">
-        <v>3629.748049599998</v>
+        <v>3601.710507199999</v>
       </c>
       <c r="O48">
-        <v>961.8832331439996</v>
+        <v>954.4532844079997</v>
       </c>
       <c r="P48">
-        <v>2667.864816455999</v>
+        <v>2647.257222791999</v>
       </c>
       <c r="Q48">
-        <v>6083.264816456</v>
+        <v>6062.657222791999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09059820774635471</v>
+        <v>0.09130571049550587</v>
       </c>
       <c r="T48">
-        <v>1.034600640793411</v>
+        <v>1.05094019620106</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.814353882016854</v>
+        <v>3.733197416442028</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06749541156261812</v>
+        <v>0.06737086094220468</v>
       </c>
       <c r="C49">
-        <v>26642.01366267018</v>
+        <v>26237.46227416347</v>
       </c>
       <c r="D49">
-        <v>49877.68966267018</v>
+        <v>49980.14627416347</v>
       </c>
       <c r="E49">
-        <v>-10157.824</v>
+        <v>-9650.815999999999</v>
       </c>
       <c r="F49">
-        <v>23829.376</v>
+        <v>24336.384</v>
       </c>
       <c r="G49">
         <v>593.7</v>
@@ -5311,28 +5311,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M49">
-        <v>1317.7644928</v>
+        <v>1345.8020352</v>
       </c>
       <c r="N49">
-        <v>3601.710507199999</v>
+        <v>3573.672964799999</v>
       </c>
       <c r="O49">
-        <v>954.4532844079997</v>
+        <v>947.0233356719997</v>
       </c>
       <c r="P49">
-        <v>2647.257222791999</v>
+        <v>2626.649629127999</v>
       </c>
       <c r="Q49">
-        <v>6062.657222791999</v>
+        <v>6042.049629128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09130571049550587</v>
+        <v>0.09204042488885517</v>
       </c>
       <c r="T49">
-        <v>1.05094019620106</v>
+        <v>1.067908196047463</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.733197416442028</v>
+        <v>3.655422470266152</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06737086094220468</v>
+        <v>0.06724631032179125</v>
       </c>
       <c r="C50">
-        <v>26237.46227416347</v>
+        <v>25833.33267603704</v>
       </c>
       <c r="D50">
-        <v>49980.14627416347</v>
+        <v>50083.02467603704</v>
       </c>
       <c r="E50">
-        <v>-9650.815999999999</v>
+        <v>-9143.808000000001</v>
       </c>
       <c r="F50">
-        <v>24336.384</v>
+        <v>24843.392</v>
       </c>
       <c r="G50">
         <v>593.7</v>
@@ -5393,28 +5393,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M50">
-        <v>1345.8020352</v>
+        <v>1373.8395776</v>
       </c>
       <c r="N50">
-        <v>3573.672964799999</v>
+        <v>3545.635422399999</v>
       </c>
       <c r="O50">
-        <v>947.0233356719997</v>
+        <v>939.5933869359998</v>
       </c>
       <c r="P50">
-        <v>2626.649629127999</v>
+        <v>2606.042035463999</v>
       </c>
       <c r="Q50">
-        <v>6042.049629128</v>
+        <v>6021.442035463999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09204042488885517</v>
+        <v>0.09280395161135539</v>
       </c>
       <c r="T50">
-        <v>1.067908196047463</v>
+        <v>1.085541607652549</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.655422470266152</v>
+        <v>3.580822011689292</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06724631032179125</v>
+        <v>0.06712175970137782</v>
       </c>
       <c r="C51">
-        <v>25833.33267603704</v>
+        <v>25429.62747828471</v>
       </c>
       <c r="D51">
-        <v>50083.02467603704</v>
+        <v>50186.32747828471</v>
       </c>
       <c r="E51">
-        <v>-9143.808000000001</v>
+        <v>-8636.799999999999</v>
       </c>
       <c r="F51">
-        <v>24843.392</v>
+        <v>25350.4</v>
       </c>
       <c r="G51">
         <v>593.7</v>
@@ -5475,28 +5475,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M51">
-        <v>1373.8395776</v>
+        <v>1401.87712</v>
       </c>
       <c r="N51">
-        <v>3545.635422399999</v>
+        <v>3517.597879999998</v>
       </c>
       <c r="O51">
-        <v>939.5933869359998</v>
+        <v>932.1634381999996</v>
       </c>
       <c r="P51">
-        <v>2606.042035463999</v>
+        <v>2585.434441799999</v>
       </c>
       <c r="Q51">
-        <v>6021.442035463999</v>
+        <v>6000.834441799999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09280395161135539</v>
+        <v>0.09359801940275564</v>
       </c>
       <c r="T51">
-        <v>1.085541607652549</v>
+        <v>1.103880355721839</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.580822011689292</v>
+        <v>3.509205571455506</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06712175970137782</v>
+        <v>0.0669972090809644</v>
       </c>
       <c r="C52">
-        <v>25429.62747828471</v>
+        <v>25026.34931247859</v>
       </c>
       <c r="D52">
-        <v>50186.32747828471</v>
+        <v>50290.0573124786</v>
       </c>
       <c r="E52">
-        <v>-8636.799999999999</v>
+        <v>-8129.791999999998</v>
       </c>
       <c r="F52">
-        <v>25350.4</v>
+        <v>25857.408</v>
       </c>
       <c r="G52">
         <v>593.7</v>
@@ -5557,28 +5557,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M52">
-        <v>1401.87712</v>
+        <v>1429.9146624</v>
       </c>
       <c r="N52">
-        <v>3517.597879999998</v>
+        <v>3489.560337599999</v>
       </c>
       <c r="O52">
-        <v>932.1634381999996</v>
+        <v>924.7334894639997</v>
       </c>
       <c r="P52">
-        <v>2585.434441799999</v>
+        <v>2564.826848135999</v>
       </c>
       <c r="Q52">
-        <v>6000.834441799999</v>
+        <v>5980.226848135999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09359801940275564</v>
+        <v>0.09442449812441714</v>
       </c>
       <c r="T52">
-        <v>1.103880355721839</v>
+        <v>1.122967624120488</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.509205571455506</v>
+        <v>3.440397619074025</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0669972090809644</v>
+        <v>0.06687265846055096</v>
       </c>
       <c r="C53">
-        <v>25026.34931247859</v>
+        <v>24623.50083199269</v>
       </c>
       <c r="D53">
-        <v>50290.0573124786</v>
+        <v>50394.21683199269</v>
       </c>
       <c r="E53">
-        <v>-8129.791999999998</v>
+        <v>-7622.784</v>
       </c>
       <c r="F53">
-        <v>25857.408</v>
+        <v>26364.416</v>
       </c>
       <c r="G53">
         <v>593.7</v>
@@ -5639,28 +5639,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M53">
-        <v>1429.9146624</v>
+        <v>1457.9522048</v>
       </c>
       <c r="N53">
-        <v>3489.560337599999</v>
+        <v>3461.522795199999</v>
       </c>
       <c r="O53">
-        <v>924.7334894639997</v>
+        <v>917.3035407279997</v>
       </c>
       <c r="P53">
-        <v>2564.826848135999</v>
+        <v>2544.219254471999</v>
       </c>
       <c r="Q53">
-        <v>5980.226848135999</v>
+        <v>5959.619254472</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09442449812441714</v>
+        <v>0.09528541345948116</v>
       </c>
       <c r="T53">
-        <v>1.122967624120488</v>
+        <v>1.14285019536908</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.440397619074025</v>
+        <v>3.374236126399525</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06687265846055096</v>
+        <v>0.06674810784013753</v>
       </c>
       <c r="C54">
-        <v>24623.50083199269</v>
+        <v>24221.08471222891</v>
       </c>
       <c r="D54">
-        <v>50394.21683199269</v>
+        <v>50498.80871222891</v>
       </c>
       <c r="E54">
-        <v>-7622.784</v>
+        <v>-7115.775999999998</v>
       </c>
       <c r="F54">
-        <v>26364.416</v>
+        <v>26871.424</v>
       </c>
       <c r="G54">
         <v>593.7</v>
@@ -5721,28 +5721,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M54">
-        <v>1457.9522048</v>
+        <v>1485.9897472</v>
       </c>
       <c r="N54">
-        <v>3461.522795199999</v>
+        <v>3433.485252799998</v>
       </c>
       <c r="O54">
-        <v>917.3035407279997</v>
+        <v>909.8735919919995</v>
       </c>
       <c r="P54">
-        <v>2544.219254471999</v>
+        <v>2523.611660807999</v>
       </c>
       <c r="Q54">
-        <v>5959.619254472</v>
+        <v>5939.011660807999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09528541345948116</v>
+        <v>0.09618296348965433</v>
       </c>
       <c r="T54">
-        <v>1.14285019536908</v>
+        <v>1.163578833479315</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.374236126399525</v>
+        <v>3.310571293825948</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06674810784013753</v>
+        <v>0.0666235572197241</v>
       </c>
       <c r="C55">
-        <v>24221.08471222891</v>
+        <v>23819.10365084631</v>
       </c>
       <c r="D55">
-        <v>50498.80871222891</v>
+        <v>50603.83565084632</v>
       </c>
       <c r="E55">
-        <v>-7115.775999999998</v>
+        <v>-6608.767999999996</v>
       </c>
       <c r="F55">
-        <v>26871.424</v>
+        <v>27378.432</v>
       </c>
       <c r="G55">
         <v>593.7</v>
@@ -5803,28 +5803,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M55">
-        <v>1485.9897472</v>
+        <v>1514.0272896</v>
       </c>
       <c r="N55">
-        <v>3433.485252799998</v>
+        <v>3405.447710399998</v>
       </c>
       <c r="O55">
-        <v>909.8735919919995</v>
+        <v>902.4436432559996</v>
       </c>
       <c r="P55">
-        <v>2523.611660807999</v>
+        <v>2503.004067143999</v>
       </c>
       <c r="Q55">
-        <v>5939.011660807999</v>
+        <v>5918.404067143999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09618296348965433</v>
+        <v>0.09711953743418283</v>
       </c>
       <c r="T55">
-        <v>1.163578833479315</v>
+        <v>1.185208716724777</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.310571293825948</v>
+        <v>3.249264418014357</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0666235572197241</v>
+        <v>0.06649900659931067</v>
       </c>
       <c r="C56">
-        <v>23819.10365084631</v>
+        <v>23417.56036799305</v>
       </c>
       <c r="D56">
-        <v>50603.83565084632</v>
+        <v>50709.30036799305</v>
       </c>
       <c r="E56">
-        <v>-6608.767999999996</v>
+        <v>-6101.759999999998</v>
       </c>
       <c r="F56">
-        <v>27378.432</v>
+        <v>27885.44</v>
       </c>
       <c r="G56">
         <v>593.7</v>
@@ -5885,28 +5885,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M56">
-        <v>1514.0272896</v>
+        <v>1542.064832</v>
       </c>
       <c r="N56">
-        <v>3405.447710399998</v>
+        <v>3377.410167999999</v>
       </c>
       <c r="O56">
-        <v>902.4436432559996</v>
+        <v>895.0136945199996</v>
       </c>
       <c r="P56">
-        <v>2503.004067143999</v>
+        <v>2482.396473479999</v>
       </c>
       <c r="Q56">
-        <v>5918.404067143999</v>
+        <v>5897.796473479999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09711953743418283</v>
+        <v>0.09809773688735704</v>
       </c>
       <c r="T56">
-        <v>1.185208716724777</v>
+        <v>1.207799928114481</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.249264418014357</v>
+        <v>3.190186883141369</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06649900659931067</v>
+        <v>0.06637445597889723</v>
       </c>
       <c r="C57">
-        <v>23417.56036799305</v>
+        <v>23016.45760654103</v>
       </c>
       <c r="D57">
-        <v>50709.30036799305</v>
+        <v>50815.20560654104</v>
       </c>
       <c r="E57">
-        <v>-6101.759999999998</v>
+        <v>-5594.751999999997</v>
       </c>
       <c r="F57">
-        <v>27885.44</v>
+        <v>28392.448</v>
       </c>
       <c r="G57">
         <v>593.7</v>
@@ -5967,28 +5967,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M57">
-        <v>1542.064832</v>
+        <v>1570.1023744</v>
       </c>
       <c r="N57">
-        <v>3377.410167999999</v>
+        <v>3349.372625599998</v>
       </c>
       <c r="O57">
-        <v>895.0136945199996</v>
+        <v>887.5837457839996</v>
       </c>
       <c r="P57">
-        <v>2482.396473479999</v>
+        <v>2461.788879815998</v>
       </c>
       <c r="Q57">
-        <v>5897.796473479999</v>
+        <v>5877.188879815998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09809773688735704</v>
+        <v>0.09912039995203917</v>
       </c>
       <c r="T57">
-        <v>1.207799928114481</v>
+        <v>1.231418012749173</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.190186883141369</v>
+        <v>3.13321926022813</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06637445597889723</v>
+        <v>0.06624990535848381</v>
       </c>
       <c r="C58">
-        <v>23016.45760654103</v>
+        <v>22615.79813232393</v>
       </c>
       <c r="D58">
-        <v>50815.20560654104</v>
+        <v>50921.55413232393</v>
       </c>
       <c r="E58">
-        <v>-5594.751999999997</v>
+        <v>-5087.743999999995</v>
       </c>
       <c r="F58">
-        <v>28392.448</v>
+        <v>28899.456</v>
       </c>
       <c r="G58">
         <v>593.7</v>
@@ -6049,28 +6049,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M58">
-        <v>1570.1023744</v>
+        <v>1598.1399168</v>
       </c>
       <c r="N58">
-        <v>3349.372625599998</v>
+        <v>3321.335083199998</v>
       </c>
       <c r="O58">
-        <v>887.5837457839996</v>
+        <v>880.1537970479995</v>
       </c>
       <c r="P58">
-        <v>2461.788879815998</v>
+        <v>2441.181286151999</v>
       </c>
       <c r="Q58">
-        <v>5877.188879815998</v>
+        <v>5856.581286151999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09912039995203917</v>
+        <v>0.10019062874066</v>
       </c>
       <c r="T58">
-        <v>1.231418012749173</v>
+        <v>1.256134612948268</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.13321926022813</v>
+        <v>3.078250501276759</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06624990535848381</v>
+        <v>0.06612535473807038</v>
       </c>
       <c r="C59">
-        <v>22615.79813232393</v>
+        <v>22215.58473437781</v>
       </c>
       <c r="D59">
-        <v>50921.55413232393</v>
+        <v>51028.34873437781</v>
       </c>
       <c r="E59">
-        <v>-5087.743999999995</v>
+        <v>-4580.735999999997</v>
       </c>
       <c r="F59">
-        <v>28899.456</v>
+        <v>29406.464</v>
       </c>
       <c r="G59">
         <v>593.7</v>
@@ -6131,28 +6131,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M59">
-        <v>1598.1399168</v>
+        <v>1626.1774592</v>
       </c>
       <c r="N59">
-        <v>3321.335083199998</v>
+        <v>3293.297540799998</v>
       </c>
       <c r="O59">
-        <v>880.1537970479995</v>
+        <v>872.7238483119996</v>
       </c>
       <c r="P59">
-        <v>2441.181286151999</v>
+        <v>2420.573692487999</v>
       </c>
       <c r="Q59">
-        <v>5856.581286151999</v>
+        <v>5835.973692487999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.10019062874066</v>
+        <v>0.1013118208049295</v>
       </c>
       <c r="T59">
-        <v>1.256134612948268</v>
+        <v>1.282028194109226</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.078250501276759</v>
+        <v>3.025177216771987</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06612535473807038</v>
+        <v>0.06708492911765694</v>
       </c>
       <c r="C60">
-        <v>22215.58473437781</v>
+        <v>20897.18460740894</v>
       </c>
       <c r="D60">
-        <v>51028.34873437781</v>
+        <v>50216.95660740894</v>
       </c>
       <c r="E60">
-        <v>-4580.736000000001</v>
+        <v>-4073.728000000003</v>
       </c>
       <c r="F60">
-        <v>29406.464</v>
+        <v>29913.47199999999</v>
       </c>
       <c r="G60">
         <v>593.7</v>
@@ -6213,45 +6213,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M60">
-        <v>1626.1774592</v>
+        <v>1728.9986816</v>
       </c>
       <c r="N60">
-        <v>3293.297540799998</v>
+        <v>3190.476318399998</v>
       </c>
       <c r="O60">
-        <v>872.7238483119996</v>
+        <v>845.4762243759997</v>
       </c>
       <c r="P60">
-        <v>2420.573692487999</v>
+        <v>2345.000094023999</v>
       </c>
       <c r="Q60">
-        <v>5835.973692487999</v>
+        <v>5760.400094023998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1013118208049295</v>
+        <v>0.1024877051650169</v>
       </c>
       <c r="T60">
-        <v>1.282028194109225</v>
+        <v>1.309184876790229</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.265</v>
       </c>
       <c r="W60">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.025177216771988</v>
+        <v>2.845274003012865</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06708492911765694</v>
+        <v>0.06697875349724353</v>
       </c>
       <c r="C61">
-        <v>20897.18460740894</v>
+        <v>20478.68421444348</v>
       </c>
       <c r="D61">
-        <v>50216.95660740894</v>
+        <v>50305.46421444348</v>
       </c>
       <c r="E61">
-        <v>-4073.728000000003</v>
+        <v>-3566.720000000001</v>
       </c>
       <c r="F61">
-        <v>29913.47199999999</v>
+        <v>30420.48</v>
       </c>
       <c r="G61">
         <v>593.7</v>
@@ -6295,28 +6295,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M61">
-        <v>1728.9986816</v>
+        <v>1758.303744</v>
       </c>
       <c r="N61">
-        <v>3190.476318399998</v>
+        <v>3161.171255999999</v>
       </c>
       <c r="O61">
-        <v>845.4762243759997</v>
+        <v>837.7103828399997</v>
       </c>
       <c r="P61">
-        <v>2345.000094023999</v>
+        <v>2323.460873159999</v>
       </c>
       <c r="Q61">
-        <v>5760.400094023998</v>
+        <v>5738.86087316</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1024877051650169</v>
+        <v>0.1037223837431088</v>
       </c>
       <c r="T61">
-        <v>1.309184876790229</v>
+        <v>1.337699393605284</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.845274003012865</v>
+        <v>2.797852769629318</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06697875349724353</v>
+        <v>0.06687257787683008</v>
       </c>
       <c r="C62">
-        <v>20478.68421444348</v>
+        <v>20060.49636242671</v>
       </c>
       <c r="D62">
-        <v>50305.46421444348</v>
+        <v>50394.28436242671</v>
       </c>
       <c r="E62">
-        <v>-3566.720000000001</v>
+        <v>-3059.712</v>
       </c>
       <c r="F62">
-        <v>30420.48</v>
+        <v>30927.488</v>
       </c>
       <c r="G62">
         <v>593.7</v>
@@ -6377,28 +6377,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M62">
-        <v>1758.303744</v>
+        <v>1787.6088064</v>
       </c>
       <c r="N62">
-        <v>3161.171255999999</v>
+        <v>3131.866193599998</v>
       </c>
       <c r="O62">
-        <v>837.7103828399997</v>
+        <v>829.9445413039997</v>
       </c>
       <c r="P62">
-        <v>2323.460873159999</v>
+        <v>2301.921652295999</v>
       </c>
       <c r="Q62">
-        <v>5738.86087316</v>
+        <v>5717.321652295999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1037223837431088</v>
+        <v>0.1050203791713592</v>
       </c>
       <c r="T62">
-        <v>1.337699393605284</v>
+        <v>1.367676193333931</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.797852769629318</v>
+        <v>2.751986330782935</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06687257787683008</v>
+        <v>0.06676640225641665</v>
       </c>
       <c r="C63">
-        <v>20060.49636242671</v>
+        <v>19642.62270976892</v>
       </c>
       <c r="D63">
-        <v>50394.28436242671</v>
+        <v>50483.41870976891</v>
       </c>
       <c r="E63">
-        <v>-3059.712</v>
+        <v>-2552.704000000002</v>
       </c>
       <c r="F63">
-        <v>30927.488</v>
+        <v>31434.496</v>
       </c>
       <c r="G63">
         <v>593.7</v>
@@ -6459,28 +6459,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M63">
-        <v>1787.6088064</v>
+        <v>1816.9138688</v>
       </c>
       <c r="N63">
-        <v>3131.866193599998</v>
+        <v>3102.561131199999</v>
       </c>
       <c r="O63">
-        <v>829.9445413039997</v>
+        <v>822.1786997679997</v>
       </c>
       <c r="P63">
-        <v>2301.921652295999</v>
+        <v>2280.382431431999</v>
       </c>
       <c r="Q63">
-        <v>5717.321652295999</v>
+        <v>5695.782431431999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1050203791713592</v>
+        <v>0.1063866901484649</v>
       </c>
       <c r="T63">
-        <v>1.367676193333931</v>
+        <v>1.399230719364085</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.751986330782935</v>
+        <v>2.707599454479985</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06676640225641665</v>
+        <v>0.06666022663600323</v>
       </c>
       <c r="C64">
-        <v>19642.62270976892</v>
+        <v>19225.06492663437</v>
       </c>
       <c r="D64">
-        <v>50483.41870976891</v>
+        <v>50572.86892663437</v>
       </c>
       <c r="E64">
-        <v>-2552.704000000002</v>
+        <v>-2045.696</v>
       </c>
       <c r="F64">
-        <v>31434.496</v>
+        <v>31941.504</v>
       </c>
       <c r="G64">
         <v>593.7</v>
@@ -6541,28 +6541,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M64">
-        <v>1816.9138688</v>
+        <v>1846.2189312</v>
       </c>
       <c r="N64">
-        <v>3102.561131199999</v>
+        <v>3073.256068799999</v>
       </c>
       <c r="O64">
-        <v>822.1786997679997</v>
+        <v>814.4128582319996</v>
       </c>
       <c r="P64">
-        <v>2280.382431431999</v>
+        <v>2258.843210567999</v>
       </c>
       <c r="Q64">
-        <v>5695.782431431999</v>
+        <v>5674.243210567999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1063866901484649</v>
+        <v>0.1078268557729817</v>
       </c>
       <c r="T64">
-        <v>1.399230719364085</v>
+        <v>1.432490895449923</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.707599454479985</v>
+        <v>2.664621685361255</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06666022663600323</v>
+        <v>0.0665540510155898</v>
       </c>
       <c r="C65">
-        <v>19225.06492663437</v>
+        <v>18807.82469504563</v>
       </c>
       <c r="D65">
-        <v>50572.86892663437</v>
+        <v>50662.63669504564</v>
       </c>
       <c r="E65">
-        <v>-2045.696</v>
+        <v>-1538.687999999998</v>
       </c>
       <c r="F65">
-        <v>31941.504</v>
+        <v>32448.512</v>
       </c>
       <c r="G65">
         <v>593.7</v>
@@ -6623,28 +6623,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M65">
-        <v>1846.2189312</v>
+        <v>1875.5239936</v>
       </c>
       <c r="N65">
-        <v>3073.256068799999</v>
+        <v>3043.951006399999</v>
       </c>
       <c r="O65">
-        <v>814.4128582319996</v>
+        <v>806.6470166959997</v>
       </c>
       <c r="P65">
-        <v>2258.843210567999</v>
+        <v>2237.303989703999</v>
       </c>
       <c r="Q65">
-        <v>5674.243210567999</v>
+        <v>5652.703989703999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1078268557729817</v>
+        <v>0.1093470305988605</v>
       </c>
       <c r="T65">
-        <v>1.432490895449923</v>
+        <v>1.467598859096086</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.664621685361255</v>
+        <v>2.622986971527485</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0665540510155898</v>
+        <v>0.06644787539517637</v>
       </c>
       <c r="C66">
-        <v>18807.82469504563</v>
+        <v>18390.903708989</v>
       </c>
       <c r="D66">
-        <v>50662.63669504564</v>
+        <v>50752.723708989</v>
       </c>
       <c r="E66">
-        <v>-1538.687999999998</v>
+        <v>-1031.68</v>
       </c>
       <c r="F66">
-        <v>32448.512</v>
+        <v>32955.52</v>
       </c>
       <c r="G66">
         <v>593.7</v>
@@ -6705,28 +6705,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M66">
-        <v>1875.5239936</v>
+        <v>1904.829056</v>
       </c>
       <c r="N66">
-        <v>3043.951006399999</v>
+        <v>3014.645943999999</v>
       </c>
       <c r="O66">
-        <v>806.6470166959997</v>
+        <v>798.8811751599997</v>
       </c>
       <c r="P66">
-        <v>2237.303989703999</v>
+        <v>2215.764768839999</v>
       </c>
       <c r="Q66">
-        <v>5652.703989703999</v>
+        <v>5631.164768839999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1093470305988605</v>
+        <v>0.1109540725576467</v>
       </c>
       <c r="T66">
-        <v>1.467598859096086</v>
+        <v>1.504712992093458</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.622986971527485</v>
+        <v>2.582633325811678</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06644787539517637</v>
+        <v>0.06634169977476292</v>
       </c>
       <c r="C67">
-        <v>18390.903708989</v>
+        <v>17974.30367452102</v>
       </c>
       <c r="D67">
-        <v>50752.723708989</v>
+        <v>50843.13167452102</v>
       </c>
       <c r="E67">
-        <v>-1031.68</v>
+        <v>-524.6719999999987</v>
       </c>
       <c r="F67">
-        <v>32955.52</v>
+        <v>33462.528</v>
       </c>
       <c r="G67">
         <v>593.7</v>
@@ -6787,28 +6787,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M67">
-        <v>1904.829056</v>
+        <v>1934.1341184</v>
       </c>
       <c r="N67">
-        <v>3014.645943999999</v>
+        <v>2985.340881599998</v>
       </c>
       <c r="O67">
-        <v>798.8811751599997</v>
+        <v>791.1153336239996</v>
       </c>
       <c r="P67">
-        <v>2215.764768839999</v>
+        <v>2194.225547975999</v>
       </c>
       <c r="Q67">
-        <v>5631.164768839999</v>
+        <v>5609.625547975998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1109540725576467</v>
+        <v>0.1126556463963616</v>
       </c>
       <c r="T67">
-        <v>1.504712992093458</v>
+        <v>1.544010309384793</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.582633325811678</v>
+        <v>2.543502517844834</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06634169977476292</v>
+        <v>0.0662355241543495</v>
       </c>
       <c r="C68">
-        <v>17974.30367452102</v>
+        <v>17558.02630987622</v>
       </c>
       <c r="D68">
-        <v>50843.13167452102</v>
+        <v>50933.86230987623</v>
       </c>
       <c r="E68">
-        <v>-524.6719999999987</v>
+        <v>-17.66399999999703</v>
       </c>
       <c r="F68">
-        <v>33462.528</v>
+        <v>33969.536</v>
       </c>
       <c r="G68">
         <v>593.7</v>
@@ -6869,28 +6869,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M68">
-        <v>1934.1341184</v>
+        <v>1963.4391808</v>
       </c>
       <c r="N68">
-        <v>2985.340881599998</v>
+        <v>2956.035819199999</v>
       </c>
       <c r="O68">
-        <v>791.1153336239996</v>
+        <v>783.3494920879997</v>
       </c>
       <c r="P68">
-        <v>2194.225547975999</v>
+        <v>2172.686327111999</v>
       </c>
       <c r="Q68">
-        <v>5609.625547975998</v>
+        <v>5588.086327111999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1126556463963616</v>
+        <v>0.1144603459222712</v>
       </c>
       <c r="T68">
-        <v>1.544010309384793</v>
+        <v>1.585689282269543</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.543502517844834</v>
+        <v>2.505539793697896</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0662355241543495</v>
+        <v>0.06787864853393608</v>
       </c>
       <c r="C69">
-        <v>17558.02630987622</v>
+        <v>15682.20925846937</v>
       </c>
       <c r="D69">
-        <v>50933.86230987623</v>
+        <v>49565.05325846937</v>
       </c>
       <c r="E69">
-        <v>-17.66399999999703</v>
+        <v>489.3440000000046</v>
       </c>
       <c r="F69">
-        <v>33969.536</v>
+        <v>34476.544</v>
       </c>
       <c r="G69">
         <v>593.7</v>
@@ -6951,45 +6951,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M69">
-        <v>1963.4391808</v>
+        <v>2113.4121472</v>
       </c>
       <c r="N69">
-        <v>2956.035819199999</v>
+        <v>2806.062852799998</v>
       </c>
       <c r="O69">
-        <v>783.3494920879997</v>
+        <v>743.6066559919996</v>
       </c>
       <c r="P69">
-        <v>2172.686327111999</v>
+        <v>2062.456196807999</v>
       </c>
       <c r="Q69">
-        <v>5588.086327111999</v>
+        <v>5477.856196807999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1144603459222712</v>
+        <v>0.1163778391685502</v>
       </c>
       <c r="T69">
-        <v>1.585689282269543</v>
+        <v>1.62997319095959</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.265</v>
       </c>
       <c r="W69">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.505539793697896</v>
+        <v>2.327740477179367</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06787864853393608</v>
+        <v>0.06779819791352264</v>
       </c>
       <c r="C70">
-        <v>15682.20925846937</v>
+        <v>15240.5056852517</v>
       </c>
       <c r="D70">
-        <v>49565.05325846937</v>
+        <v>49630.35768525171</v>
       </c>
       <c r="E70">
-        <v>489.3440000000046</v>
+        <v>996.3520000000062</v>
       </c>
       <c r="F70">
-        <v>34476.544</v>
+        <v>34983.552</v>
       </c>
       <c r="G70">
         <v>593.7</v>
@@ -7033,28 +7033,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M70">
-        <v>2113.4121472</v>
+        <v>2144.4917376</v>
       </c>
       <c r="N70">
-        <v>2806.062852799998</v>
+        <v>2774.983262399998</v>
       </c>
       <c r="O70">
-        <v>743.6066559919996</v>
+        <v>735.3705645359996</v>
       </c>
       <c r="P70">
-        <v>2062.456196807999</v>
+        <v>2039.612697863999</v>
       </c>
       <c r="Q70">
-        <v>5477.856196807999</v>
+        <v>5455.012697863998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1163778391685502</v>
+        <v>0.1184190416565246</v>
       </c>
       <c r="T70">
-        <v>1.62997319095959</v>
+        <v>1.677114126016736</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.327740477179367</v>
+        <v>2.294005107944883</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06779819791352264</v>
+        <v>0.0677177472931092</v>
       </c>
       <c r="C71">
-        <v>15240.5056852517</v>
+        <v>14798.97442273291</v>
       </c>
       <c r="D71">
-        <v>49630.35768525171</v>
+        <v>49695.83442273291</v>
       </c>
       <c r="E71">
-        <v>996.3520000000062</v>
+        <v>1503.360000000001</v>
       </c>
       <c r="F71">
-        <v>34983.552</v>
+        <v>35490.56</v>
       </c>
       <c r="G71">
         <v>593.7</v>
@@ -7115,28 +7115,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M71">
-        <v>2144.4917376</v>
+        <v>2175.571328</v>
       </c>
       <c r="N71">
-        <v>2774.983262399998</v>
+        <v>2743.903671999999</v>
       </c>
       <c r="O71">
-        <v>735.3705645359996</v>
+        <v>727.1344730799997</v>
       </c>
       <c r="P71">
-        <v>2039.612697863999</v>
+        <v>2016.769198919999</v>
       </c>
       <c r="Q71">
-        <v>5455.012697863998</v>
+        <v>5432.169198919999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1184190416565246</v>
+        <v>0.120596324310364</v>
       </c>
       <c r="T71">
-        <v>1.677114126016736</v>
+        <v>1.727397790077691</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.294005107944883</v>
+        <v>2.261233606402814</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0677177472931092</v>
+        <v>0.06909847667269578</v>
       </c>
       <c r="C72">
-        <v>14798.97442273291</v>
+        <v>13191.65640273778</v>
       </c>
       <c r="D72">
-        <v>49695.83442273291</v>
+        <v>48595.52440273778</v>
       </c>
       <c r="E72">
-        <v>1503.360000000001</v>
+        <v>2010.368000000002</v>
       </c>
       <c r="F72">
-        <v>35490.56</v>
+        <v>35997.568</v>
       </c>
       <c r="G72">
         <v>593.7</v>
@@ -7197,45 +7197,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M72">
-        <v>2175.571328</v>
+        <v>2307.4441088</v>
       </c>
       <c r="N72">
-        <v>2743.903671999999</v>
+        <v>2612.030891199998</v>
       </c>
       <c r="O72">
-        <v>727.1344730799997</v>
+        <v>692.1881861679996</v>
       </c>
       <c r="P72">
-        <v>2016.769198919999</v>
+        <v>1919.842705031999</v>
       </c>
       <c r="Q72">
-        <v>5432.169198919999</v>
+        <v>5335.242705031998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.120596324310364</v>
+        <v>0.1229237643886061</v>
       </c>
       <c r="T72">
-        <v>1.727397790077691</v>
+        <v>1.781149293039403</v>
       </c>
       <c r="U72">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.265</v>
       </c>
       <c r="W72">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.261233606402814</v>
+        <v>2.13200180287721</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06909847667269578</v>
+        <v>0.06903860605228235</v>
       </c>
       <c r="C73">
-        <v>13191.65640273778</v>
+        <v>12731.34806043953</v>
       </c>
       <c r="D73">
-        <v>48595.52440273778</v>
+        <v>48642.22406043953</v>
       </c>
       <c r="E73">
-        <v>2010.367999999995</v>
+        <v>2517.375999999997</v>
       </c>
       <c r="F73">
-        <v>35997.56799999999</v>
+        <v>36504.57599999999</v>
       </c>
       <c r="G73">
         <v>593.7</v>
@@ -7279,28 +7279,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M73">
-        <v>2307.4441088</v>
+        <v>2339.9433216</v>
       </c>
       <c r="N73">
-        <v>2612.030891199999</v>
+        <v>2579.531678399999</v>
       </c>
       <c r="O73">
-        <v>692.1881861679997</v>
+        <v>683.5758947759997</v>
       </c>
       <c r="P73">
-        <v>1919.842705031999</v>
+        <v>1895.955783623999</v>
       </c>
       <c r="Q73">
-        <v>5335.242705031999</v>
+        <v>5311.355783624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1229237643886061</v>
+        <v>0.1254174501867227</v>
       </c>
       <c r="T73">
-        <v>1.781149293039402</v>
+        <v>1.838740189069807</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.132001802877211</v>
+        <v>2.102390666726139</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06903860605228235</v>
+        <v>0.06897873543186891</v>
       </c>
       <c r="C74">
-        <v>12731.34806043953</v>
+        <v>12271.12955998773</v>
       </c>
       <c r="D74">
-        <v>48642.22406043953</v>
+        <v>48689.01355998773</v>
       </c>
       <c r="E74">
-        <v>2517.375999999997</v>
+        <v>3024.383999999998</v>
       </c>
       <c r="F74">
-        <v>36504.57599999999</v>
+        <v>37011.584</v>
       </c>
       <c r="G74">
         <v>593.7</v>
@@ -7361,28 +7361,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M74">
-        <v>2339.9433216</v>
+        <v>2372.4425344</v>
       </c>
       <c r="N74">
-        <v>2579.531678399999</v>
+        <v>2547.032465599999</v>
       </c>
       <c r="O74">
-        <v>683.5758947759997</v>
+        <v>674.9636033839997</v>
       </c>
       <c r="P74">
-        <v>1895.955783623999</v>
+        <v>1872.068862215999</v>
       </c>
       <c r="Q74">
-        <v>5311.355783624</v>
+        <v>5287.468862215999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1254174501867227</v>
+        <v>0.1280958534513663</v>
       </c>
       <c r="T74">
-        <v>1.838740189069807</v>
+        <v>1.900597077398761</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.102390666726139</v>
+        <v>2.073590794579205</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06897873543186891</v>
+        <v>0.06891886481145548</v>
       </c>
       <c r="C75">
-        <v>12271.12955998773</v>
+        <v>11811.00116089167</v>
       </c>
       <c r="D75">
-        <v>48689.01355998773</v>
+        <v>48735.89316089167</v>
       </c>
       <c r="E75">
-        <v>3024.383999999998</v>
+        <v>3531.392</v>
       </c>
       <c r="F75">
-        <v>37011.584</v>
+        <v>37518.592</v>
       </c>
       <c r="G75">
         <v>593.7</v>
@@ -7443,28 +7443,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M75">
-        <v>2372.4425344</v>
+        <v>2404.9417472</v>
       </c>
       <c r="N75">
-        <v>2547.032465599999</v>
+        <v>2514.533252799999</v>
       </c>
       <c r="O75">
-        <v>674.9636033839997</v>
+        <v>666.3513119919996</v>
       </c>
       <c r="P75">
-        <v>1872.068862215999</v>
+        <v>1848.181940807999</v>
       </c>
       <c r="Q75">
-        <v>5287.468862215999</v>
+        <v>5263.581940807999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1280958534513663</v>
+        <v>0.1309802877363672</v>
       </c>
       <c r="T75">
-        <v>1.900597077398761</v>
+        <v>1.967212187906865</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.073590794579205</v>
+        <v>2.045569297355161</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06891886481145548</v>
+        <v>0.06885899419104205</v>
       </c>
       <c r="C76">
-        <v>11811.00116089167</v>
+        <v>11350.96312366101</v>
       </c>
       <c r="D76">
-        <v>48735.89316089167</v>
+        <v>48782.86312366101</v>
       </c>
       <c r="E76">
-        <v>3531.392</v>
+        <v>4038.400000000001</v>
       </c>
       <c r="F76">
-        <v>37518.592</v>
+        <v>38025.6</v>
       </c>
       <c r="G76">
         <v>593.7</v>
@@ -7525,28 +7525,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M76">
-        <v>2404.9417472</v>
+        <v>2437.44096</v>
       </c>
       <c r="N76">
-        <v>2514.533252799999</v>
+        <v>2482.034039999999</v>
       </c>
       <c r="O76">
-        <v>666.3513119919996</v>
+        <v>657.7390205999997</v>
       </c>
       <c r="P76">
-        <v>1848.181940807999</v>
+        <v>1824.295019399999</v>
       </c>
       <c r="Q76">
-        <v>5263.581940807999</v>
+        <v>5239.695019399999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1309802877363672</v>
+        <v>0.1340954767641682</v>
       </c>
       <c r="T76">
-        <v>1.967212187906865</v>
+        <v>2.039156507255617</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.045569297355161</v>
+        <v>2.018295040057093</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06885899419104205</v>
+        <v>0.07315620357062863</v>
       </c>
       <c r="C77">
-        <v>11350.96312366101</v>
+        <v>7687.767118248048</v>
       </c>
       <c r="D77">
-        <v>48782.86312366101</v>
+        <v>45626.67511824805</v>
       </c>
       <c r="E77">
-        <v>4038.400000000001</v>
+        <v>4545.408000000003</v>
       </c>
       <c r="F77">
-        <v>38025.6</v>
+        <v>38532.608</v>
       </c>
       <c r="G77">
         <v>593.7</v>
@@ -7607,45 +7607,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M77">
-        <v>2437.44096</v>
+        <v>2770.4945152</v>
       </c>
       <c r="N77">
-        <v>2482.034039999999</v>
+        <v>2148.980484799999</v>
       </c>
       <c r="O77">
-        <v>657.7390205999997</v>
+        <v>569.4798284719997</v>
       </c>
       <c r="P77">
-        <v>1824.295019399999</v>
+        <v>1579.500656327999</v>
       </c>
       <c r="Q77">
-        <v>5239.695019399999</v>
+        <v>4994.900656327999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1340954767641682</v>
+        <v>0.1374702648776192</v>
       </c>
       <c r="T77">
-        <v>2.039156507255617</v>
+        <v>2.117096186550098</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.265</v>
       </c>
       <c r="W77">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.018295040057093</v>
+        <v>1.775666752996573</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07315620357062863</v>
+        <v>0.07315366295021519</v>
       </c>
       <c r="C78">
-        <v>7687.767118248048</v>
+        <v>7182.504475288901</v>
       </c>
       <c r="D78">
-        <v>45626.67511824805</v>
+        <v>45628.4204752889</v>
       </c>
       <c r="E78">
-        <v>4545.408000000003</v>
+        <v>5052.415999999997</v>
       </c>
       <c r="F78">
-        <v>38532.608</v>
+        <v>39039.61599999999</v>
       </c>
       <c r="G78">
         <v>593.7</v>
@@ -7689,28 +7689,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M78">
-        <v>2770.4945152</v>
+        <v>2806.9483904</v>
       </c>
       <c r="N78">
-        <v>2148.980484799999</v>
+        <v>2112.526609599999</v>
       </c>
       <c r="O78">
-        <v>569.4798284719997</v>
+        <v>559.8195515439996</v>
       </c>
       <c r="P78">
-        <v>1579.500656327999</v>
+        <v>1552.707058055999</v>
       </c>
       <c r="Q78">
-        <v>4994.900656327999</v>
+        <v>4968.107058055999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1374702648776192</v>
+        <v>0.1411385128270226</v>
       </c>
       <c r="T78">
-        <v>2.117096186550098</v>
+        <v>2.201813229261491</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.775666752996573</v>
+        <v>1.752606145814799</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07315366295021519</v>
+        <v>0.07538699232980176</v>
       </c>
       <c r="C79">
-        <v>7182.504475288901</v>
+        <v>5191.09847644619</v>
       </c>
       <c r="D79">
-        <v>45628.4204752889</v>
+        <v>44144.02247644619</v>
       </c>
       <c r="E79">
-        <v>5052.415999999997</v>
+        <v>5559.423999999999</v>
       </c>
       <c r="F79">
-        <v>39039.61599999999</v>
+        <v>39546.624</v>
       </c>
       <c r="G79">
         <v>593.7</v>
@@ -7771,45 +7771,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M79">
-        <v>2806.9483904</v>
+        <v>2997.6340992</v>
       </c>
       <c r="N79">
-        <v>2112.526609599999</v>
+        <v>1921.840900799999</v>
       </c>
       <c r="O79">
-        <v>559.8195515439996</v>
+        <v>509.2878387119997</v>
       </c>
       <c r="P79">
-        <v>1552.707058055999</v>
+        <v>1412.553062087999</v>
       </c>
       <c r="Q79">
-        <v>4968.107058055999</v>
+        <v>4827.953062087999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1411385128270226</v>
+        <v>0.1451402378627352</v>
       </c>
       <c r="T79">
-        <v>2.201813229261491</v>
+        <v>2.294231821310283</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.265</v>
       </c>
       <c r="W79">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.752606145814799</v>
+        <v>1.64111924177567</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07538699232980176</v>
+        <v>0.07541311670938833</v>
       </c>
       <c r="C80">
-        <v>5191.09847644619</v>
+        <v>4667.297998068039</v>
       </c>
       <c r="D80">
-        <v>44144.02247644619</v>
+        <v>44127.22999806804</v>
       </c>
       <c r="E80">
-        <v>5559.423999999999</v>
+        <v>6066.432000000001</v>
       </c>
       <c r="F80">
-        <v>39546.624</v>
+        <v>40053.632</v>
       </c>
       <c r="G80">
         <v>593.7</v>
@@ -7853,28 +7853,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M80">
-        <v>2997.6340992</v>
+        <v>3036.0653056</v>
       </c>
       <c r="N80">
-        <v>1921.840900799999</v>
+        <v>1883.409694399998</v>
       </c>
       <c r="O80">
-        <v>509.2878387119997</v>
+        <v>499.1035690159996</v>
       </c>
       <c r="P80">
-        <v>1412.553062087999</v>
+        <v>1384.306125383999</v>
       </c>
       <c r="Q80">
-        <v>4827.953062087999</v>
+        <v>4799.706125383998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1451402378627352</v>
+        <v>0.1495230795685159</v>
       </c>
       <c r="T80">
-        <v>2.294231821310283</v>
+        <v>2.39545218403039</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.64111924177567</v>
+        <v>1.620345580487371</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07541311670938833</v>
+        <v>0.0754392410889749</v>
       </c>
       <c r="C81">
-        <v>4667.297998068039</v>
+        <v>4143.510290619524</v>
       </c>
       <c r="D81">
-        <v>44127.22999806804</v>
+        <v>44110.45029061953</v>
       </c>
       <c r="E81">
-        <v>6066.432000000001</v>
+        <v>6573.440000000002</v>
       </c>
       <c r="F81">
-        <v>40053.632</v>
+        <v>40560.64</v>
       </c>
       <c r="G81">
         <v>593.7</v>
@@ -7935,28 +7935,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M81">
-        <v>3036.0653056</v>
+        <v>3074.496512</v>
       </c>
       <c r="N81">
-        <v>1883.409694399998</v>
+        <v>1844.978487999998</v>
       </c>
       <c r="O81">
-        <v>499.1035690159996</v>
+        <v>488.9192993199996</v>
       </c>
       <c r="P81">
-        <v>1384.306125383999</v>
+        <v>1356.059188679999</v>
       </c>
       <c r="Q81">
-        <v>4799.706125383998</v>
+        <v>4771.459188679999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1495230795685159</v>
+        <v>0.1543442054448745</v>
       </c>
       <c r="T81">
-        <v>2.39545218403039</v>
+        <v>2.506794583022506</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.620345580487371</v>
+        <v>1.600091260731278</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0754392410889749</v>
+        <v>0.07546536546856147</v>
       </c>
       <c r="C82">
-        <v>4143.510290619524</v>
+        <v>3619.735339537445</v>
       </c>
       <c r="D82">
-        <v>44110.45029061953</v>
+        <v>44093.68333953745</v>
       </c>
       <c r="E82">
-        <v>6573.440000000002</v>
+        <v>7080.448000000004</v>
       </c>
       <c r="F82">
-        <v>40560.64</v>
+        <v>41067.648</v>
       </c>
       <c r="G82">
         <v>593.7</v>
@@ -8017,28 +8017,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M82">
-        <v>3074.496512</v>
+        <v>3112.9277184</v>
       </c>
       <c r="N82">
-        <v>1844.978487999998</v>
+        <v>1806.547281599998</v>
       </c>
       <c r="O82">
-        <v>488.9192993199996</v>
+        <v>478.7350296239996</v>
       </c>
       <c r="P82">
-        <v>1356.059188679999</v>
+        <v>1327.812251975999</v>
       </c>
       <c r="Q82">
-        <v>4771.459188679999</v>
+        <v>4743.212251975999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1543442054448745</v>
+        <v>0.1596728182555867</v>
       </c>
       <c r="T82">
-        <v>2.506794583022506</v>
+        <v>2.629857234540108</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.600091260731278</v>
+        <v>1.58033704763583</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07546536546856147</v>
+        <v>0.07549148984814805</v>
       </c>
       <c r="C83">
-        <v>3619.735339537445</v>
+        <v>3095.97313028077</v>
       </c>
       <c r="D83">
-        <v>44093.68333953745</v>
+        <v>44076.92913028078</v>
       </c>
       <c r="E83">
-        <v>7080.448000000004</v>
+        <v>7587.456000000006</v>
       </c>
       <c r="F83">
-        <v>41067.648</v>
+        <v>41574.656</v>
       </c>
       <c r="G83">
         <v>593.7</v>
@@ -8099,28 +8099,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M83">
-        <v>3112.9277184</v>
+        <v>3151.3589248</v>
       </c>
       <c r="N83">
-        <v>1806.547281599998</v>
+        <v>1768.116075199998</v>
       </c>
       <c r="O83">
-        <v>478.7350296239996</v>
+        <v>468.5507599279995</v>
       </c>
       <c r="P83">
-        <v>1327.812251975999</v>
+        <v>1299.565315271999</v>
       </c>
       <c r="Q83">
-        <v>4743.212251975999</v>
+        <v>4714.965315271998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1596728182555867</v>
+        <v>0.165593499156378</v>
       </c>
       <c r="T83">
-        <v>2.629857234540108</v>
+        <v>2.766593514004111</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.58033704763583</v>
+        <v>1.561064644615881</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07549148984814805</v>
+        <v>0.07551761422773461</v>
       </c>
       <c r="C84">
-        <v>3095.97313028077</v>
+        <v>2572.223648330539</v>
       </c>
       <c r="D84">
-        <v>44076.92913028078</v>
+        <v>44060.18764833054</v>
       </c>
       <c r="E84">
-        <v>7587.456000000006</v>
+        <v>8094.464</v>
       </c>
       <c r="F84">
-        <v>41574.656</v>
+        <v>42081.664</v>
       </c>
       <c r="G84">
         <v>593.7</v>
@@ -8181,28 +8181,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M84">
-        <v>3151.3589248</v>
+        <v>3189.7901312</v>
       </c>
       <c r="N84">
-        <v>1768.116075199998</v>
+        <v>1729.684868799999</v>
       </c>
       <c r="O84">
-        <v>468.5507599279995</v>
+        <v>458.3664902319996</v>
       </c>
       <c r="P84">
-        <v>1299.565315271999</v>
+        <v>1271.318378567999</v>
       </c>
       <c r="Q84">
-        <v>4714.965315271998</v>
+        <v>4686.718378567999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.165593499156378</v>
+        <v>0.17221073075138</v>
       </c>
       <c r="T84">
-        <v>2.766593514004111</v>
+        <v>2.919416414581526</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.561064644615881</v>
+        <v>1.542256636849425</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07551761422773461</v>
+        <v>0.07554373860732118</v>
       </c>
       <c r="C85">
-        <v>2572.223648330539</v>
+        <v>2048.486879189819</v>
       </c>
       <c r="D85">
-        <v>44060.18764833054</v>
+        <v>44043.45887918982</v>
       </c>
       <c r="E85">
-        <v>8094.464</v>
+        <v>8601.472000000002</v>
       </c>
       <c r="F85">
-        <v>42081.664</v>
+        <v>42588.672</v>
       </c>
       <c r="G85">
         <v>593.7</v>
@@ -8263,28 +8263,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M85">
-        <v>3189.7901312</v>
+        <v>3228.2213376</v>
       </c>
       <c r="N85">
-        <v>1729.684868799999</v>
+        <v>1691.253662399999</v>
       </c>
       <c r="O85">
-        <v>458.3664902319996</v>
+        <v>448.1822205359996</v>
       </c>
       <c r="P85">
-        <v>1271.318378567999</v>
+        <v>1243.071441863999</v>
       </c>
       <c r="Q85">
-        <v>4686.718378567999</v>
+        <v>4658.471441863999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.17221073075138</v>
+        <v>0.1796551162957574</v>
       </c>
       <c r="T85">
-        <v>2.919416414581526</v>
+        <v>3.091342177731118</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.542256636849425</v>
+        <v>1.523896438791694</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07554373860732118</v>
+        <v>0.07556986298690775</v>
       </c>
       <c r="C86">
-        <v>2048.486879189826</v>
+        <v>1524.762808383733</v>
       </c>
       <c r="D86">
-        <v>44043.45887918982</v>
+        <v>44026.74280838373</v>
       </c>
       <c r="E86">
-        <v>8601.471999999994</v>
+        <v>9108.479999999996</v>
       </c>
       <c r="F86">
-        <v>42588.67199999999</v>
+        <v>43095.67999999999</v>
       </c>
       <c r="G86">
         <v>593.7</v>
@@ -8345,28 +8345,28 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M86">
-        <v>3228.2213376</v>
+        <v>3266.652544</v>
       </c>
       <c r="N86">
-        <v>1691.253662399999</v>
+        <v>1652.822455999999</v>
       </c>
       <c r="O86">
-        <v>448.1822205359998</v>
+        <v>437.9979508399998</v>
       </c>
       <c r="P86">
-        <v>1243.071441863999</v>
+        <v>1214.824505159999</v>
       </c>
       <c r="Q86">
-        <v>4658.471441864</v>
+        <v>4630.224505159999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1796551162957573</v>
+        <v>0.1880920865793849</v>
       </c>
       <c r="T86">
-        <v>3.091342177731116</v>
+        <v>3.28619137596732</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.523896438791694</v>
+        <v>1.505968245394145</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07556986298690775</v>
+        <v>0.08457180736649432</v>
       </c>
       <c r="C87">
-        <v>1524.762808383733</v>
+        <v>-4074.16264564501</v>
       </c>
       <c r="D87">
-        <v>44026.74280838373</v>
+        <v>38934.82535435499</v>
       </c>
       <c r="E87">
-        <v>9108.479999999996</v>
+        <v>9615.487999999998</v>
       </c>
       <c r="F87">
-        <v>43095.67999999999</v>
+        <v>43602.68799999999</v>
       </c>
       <c r="G87">
         <v>593.7</v>
@@ -8427,45 +8427,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M87">
-        <v>3266.652544</v>
+        <v>3924.241919999999</v>
       </c>
       <c r="N87">
-        <v>1652.822455999999</v>
+        <v>995.2330799999991</v>
       </c>
       <c r="O87">
-        <v>437.9979508399998</v>
+        <v>263.7367661999997</v>
       </c>
       <c r="P87">
-        <v>1214.824505159999</v>
+        <v>731.4963137999994</v>
       </c>
       <c r="Q87">
-        <v>4630.224505159999</v>
+        <v>4146.8963138</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1880920865793849</v>
+        <v>0.1977343383321022</v>
       </c>
       <c r="T87">
-        <v>3.28619137596732</v>
+        <v>3.508876173951553</v>
       </c>
       <c r="U87">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V87">
         <v>0.265</v>
       </c>
       <c r="W87">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.505968245394145</v>
+        <v>1.253611551043214</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08457180736649432</v>
+        <v>0.1049996974770162</v>
       </c>
       <c r="C88">
-        <v>-4074.16264564501</v>
+        <v>-12675.38880656925</v>
       </c>
       <c r="D88">
-        <v>38934.82535435499</v>
+        <v>30840.60719343074</v>
       </c>
       <c r="E88">
-        <v>9615.487999999998</v>
+        <v>10122.496</v>
       </c>
       <c r="F88">
-        <v>43602.68799999999</v>
+        <v>44109.696</v>
       </c>
       <c r="G88">
         <v>593.7</v>
@@ -8509,45 +8509,45 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M88">
-        <v>3924.241919999999</v>
+        <v>5231.4099456</v>
       </c>
       <c r="N88">
-        <v>995.2330799999991</v>
+        <v>-311.9349456000018</v>
       </c>
       <c r="O88">
-        <v>263.7367661999997</v>
+        <v>-82.66276058400048</v>
       </c>
       <c r="P88">
-        <v>731.4963137999994</v>
+        <v>-229.2721850160013</v>
       </c>
       <c r="Q88">
-        <v>4146.8963138</v>
+        <v>3186.127814983999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1977343383321022</v>
+        <v>0.2117732615420276</v>
       </c>
       <c r="T88">
-        <v>3.508876173951553</v>
+        <v>3.833100728453293</v>
       </c>
       <c r="U88">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V88">
-        <v>0.265</v>
+        <v>0.2491987606699556</v>
       </c>
       <c r="W88">
-        <v>0.06615</v>
+        <v>0.08904502698454328</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.253611551043214</v>
+        <v>0.9403726817734172</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1049996974770162</v>
+        <v>0.1057276974770162</v>
       </c>
       <c r="C89">
-        <v>-12675.38880656925</v>
+        <v>-13409.2065697776</v>
       </c>
       <c r="D89">
-        <v>30840.60719343074</v>
+        <v>30613.7974302224</v>
       </c>
       <c r="E89">
-        <v>10122.496</v>
+        <v>10629.504</v>
       </c>
       <c r="F89">
-        <v>44109.696</v>
+        <v>44616.704</v>
       </c>
       <c r="G89">
         <v>593.7</v>
@@ -8591,37 +8591,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M89">
-        <v>5231.4099456</v>
+        <v>5291.5410944</v>
       </c>
       <c r="N89">
-        <v>-311.9349456000018</v>
+        <v>-372.0660944000019</v>
       </c>
       <c r="O89">
-        <v>-82.66276058400048</v>
+        <v>-98.59751501600051</v>
       </c>
       <c r="P89">
-        <v>-229.2721850160013</v>
+        <v>-273.4685793840014</v>
       </c>
       <c r="Q89">
-        <v>3186.127814983999</v>
+        <v>3141.931420615999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2117732615420276</v>
+        <v>0.2256043666705299</v>
       </c>
       <c r="T89">
-        <v>3.833100728453293</v>
+        <v>4.152525789157735</v>
       </c>
       <c r="U89">
         <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.2491987606699556</v>
+        <v>0.2463669565714333</v>
       </c>
       <c r="W89">
-        <v>0.08904502698454328</v>
+        <v>0.08938087895062802</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9403726817734172</v>
+        <v>0.9296866285714465</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1057276974770162</v>
+        <v>0.1064556974770162</v>
       </c>
       <c r="C90">
-        <v>-13409.2065697776</v>
+        <v>-14139.71265317952</v>
       </c>
       <c r="D90">
-        <v>30613.7974302224</v>
+        <v>30390.29934682048</v>
       </c>
       <c r="E90">
-        <v>10629.504</v>
+        <v>11136.512</v>
       </c>
       <c r="F90">
-        <v>44616.704</v>
+        <v>45123.712</v>
       </c>
       <c r="G90">
         <v>593.7</v>
@@ -8673,37 +8673,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M90">
-        <v>5291.5410944</v>
+        <v>5351.672243200001</v>
       </c>
       <c r="N90">
-        <v>-372.0660944000019</v>
+        <v>-432.197243200002</v>
       </c>
       <c r="O90">
-        <v>-98.59751501600051</v>
+        <v>-114.5322694480005</v>
       </c>
       <c r="P90">
-        <v>-273.4685793840014</v>
+        <v>-317.6649737520015</v>
       </c>
       <c r="Q90">
-        <v>3141.931420615999</v>
+        <v>3097.735026247999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2256043666705299</v>
+        <v>0.2419502181860326</v>
       </c>
       <c r="T90">
-        <v>4.152525789157735</v>
+        <v>4.53002813362662</v>
       </c>
       <c r="U90">
         <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.2463669565714333</v>
+        <v>0.2435987885200689</v>
       </c>
       <c r="W90">
-        <v>0.08938087895062802</v>
+        <v>0.08970918368151984</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9296866285714465</v>
+        <v>0.9192407113964863</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1064556974770162</v>
+        <v>0.1071836974770162</v>
       </c>
       <c r="C91">
-        <v>-14139.71265317952</v>
+        <v>-14866.97906251454</v>
       </c>
       <c r="D91">
-        <v>30390.29934682048</v>
+        <v>30170.04093748546</v>
       </c>
       <c r="E91">
-        <v>11136.512</v>
+        <v>11643.52</v>
       </c>
       <c r="F91">
-        <v>45123.712</v>
+        <v>45630.71999999999</v>
       </c>
       <c r="G91">
         <v>593.7</v>
@@ -8755,37 +8755,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M91">
-        <v>5351.672243200001</v>
+        <v>5411.803392</v>
       </c>
       <c r="N91">
-        <v>-432.197243200002</v>
+        <v>-492.3283920000013</v>
       </c>
       <c r="O91">
-        <v>-114.5322694480005</v>
+        <v>-130.4670238800003</v>
       </c>
       <c r="P91">
-        <v>-317.6649737520015</v>
+        <v>-361.8613681200009</v>
       </c>
       <c r="Q91">
-        <v>3097.735026247999</v>
+        <v>3053.538631879999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2419502181860326</v>
+        <v>0.2615652400046359</v>
       </c>
       <c r="T91">
-        <v>4.53002813362662</v>
+        <v>4.983030946989282</v>
       </c>
       <c r="U91">
         <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.2435987885200689</v>
+        <v>0.2408921353142904</v>
       </c>
       <c r="W91">
-        <v>0.08970918368151984</v>
+        <v>0.09003019275172516</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9192407113964863</v>
+        <v>0.9090269257143033</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1071836974770162</v>
+        <v>0.1079116974770162</v>
       </c>
       <c r="C92">
-        <v>-14866.97906251454</v>
+        <v>-15591.07573105169</v>
       </c>
       <c r="D92">
-        <v>30170.04093748546</v>
+        <v>29952.95226894831</v>
       </c>
       <c r="E92">
-        <v>11643.52</v>
+        <v>12150.528</v>
       </c>
       <c r="F92">
-        <v>45630.71999999999</v>
+        <v>46137.728</v>
       </c>
       <c r="G92">
         <v>593.7</v>
@@ -8837,37 +8837,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M92">
-        <v>5411.803392</v>
+        <v>5471.9345408</v>
       </c>
       <c r="N92">
-        <v>-492.3283920000013</v>
+        <v>-552.4595408000014</v>
       </c>
       <c r="O92">
-        <v>-130.4670238800003</v>
+        <v>-146.4017783120004</v>
       </c>
       <c r="P92">
-        <v>-361.8613681200009</v>
+        <v>-406.057762488001</v>
       </c>
       <c r="Q92">
-        <v>3053.538631879999</v>
+        <v>3009.342237511999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2615652400046359</v>
+        <v>0.2855391555607066</v>
       </c>
       <c r="T92">
-        <v>4.983030946989282</v>
+        <v>5.536701052210314</v>
       </c>
       <c r="U92">
         <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.2408921353142904</v>
+        <v>0.2382449689921553</v>
       </c>
       <c r="W92">
-        <v>0.09003019275172516</v>
+        <v>0.09034414667753039</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9090269257143033</v>
+        <v>0.899037618838322</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1079116974770162</v>
+        <v>0.1086396974770162</v>
       </c>
       <c r="C93">
-        <v>-15591.07573105169</v>
+        <v>-16312.07059361911</v>
       </c>
       <c r="D93">
-        <v>29952.95226894831</v>
+        <v>29738.96540638088</v>
       </c>
       <c r="E93">
-        <v>12150.528</v>
+        <v>12657.536</v>
       </c>
       <c r="F93">
-        <v>46137.728</v>
+        <v>46644.736</v>
       </c>
       <c r="G93">
         <v>593.7</v>
@@ -8919,37 +8919,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M93">
-        <v>5471.9345408</v>
+        <v>5532.0656896</v>
       </c>
       <c r="N93">
-        <v>-552.4595408000014</v>
+        <v>-612.5906896000015</v>
       </c>
       <c r="O93">
-        <v>-146.4017783120004</v>
+        <v>-162.3365327440004</v>
       </c>
       <c r="P93">
-        <v>-406.057762488001</v>
+        <v>-450.2541568560011</v>
       </c>
       <c r="Q93">
-        <v>3009.342237511999</v>
+        <v>2965.145843143999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2855391555607066</v>
+        <v>0.315506550005795</v>
       </c>
       <c r="T93">
-        <v>5.536701052210314</v>
+        <v>6.228788683736605</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.2382449689921553</v>
+        <v>0.2356553497639797</v>
       </c>
       <c r="W93">
-        <v>0.09034414667753039</v>
+        <v>0.09065127551799201</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.899037618838322</v>
+        <v>0.8892654708074705</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1086396974770162</v>
+        <v>0.1093676974770162</v>
       </c>
       <c r="C94">
-        <v>-16312.07059361911</v>
+        <v>-17030.02965748308</v>
       </c>
       <c r="D94">
-        <v>29738.96540638088</v>
+        <v>29528.01434251692</v>
       </c>
       <c r="E94">
-        <v>12657.536</v>
+        <v>13164.544</v>
       </c>
       <c r="F94">
-        <v>46644.736</v>
+        <v>47151.744</v>
       </c>
       <c r="G94">
         <v>593.7</v>
@@ -9001,37 +9001,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M94">
-        <v>5532.0656896</v>
+        <v>5592.1968384</v>
       </c>
       <c r="N94">
-        <v>-612.5906896000015</v>
+        <v>-672.7218384000016</v>
       </c>
       <c r="O94">
-        <v>-162.3365327440004</v>
+        <v>-178.2712871760004</v>
       </c>
       <c r="P94">
-        <v>-450.2541568560011</v>
+        <v>-494.4505512240012</v>
       </c>
       <c r="Q94">
-        <v>2965.145843143999</v>
+        <v>2920.949448775999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.315506550005795</v>
+        <v>0.3540360571494801</v>
       </c>
       <c r="T94">
-        <v>6.228788683736605</v>
+        <v>7.118615638556121</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.2356553497639797</v>
+        <v>0.2331214212718939</v>
       </c>
       <c r="W94">
-        <v>0.09065127551799201</v>
+        <v>0.09095179943715338</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8892654708074705</v>
+        <v>0.8797034764977129</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1093676974770162</v>
+        <v>0.1100956974770163</v>
       </c>
       <c r="C95">
-        <v>-17030.02965748308</v>
+        <v>-17745.01707023145</v>
       </c>
       <c r="D95">
-        <v>29528.01434251692</v>
+        <v>29320.03492976855</v>
       </c>
       <c r="E95">
-        <v>13164.544</v>
+        <v>13671.552</v>
       </c>
       <c r="F95">
-        <v>47151.744</v>
+        <v>47658.752</v>
       </c>
       <c r="G95">
         <v>593.7</v>
@@ -9083,37 +9083,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M95">
-        <v>5592.1968384</v>
+        <v>5652.3279872</v>
       </c>
       <c r="N95">
-        <v>-672.7218384000016</v>
+        <v>-732.8529872000017</v>
       </c>
       <c r="O95">
-        <v>-178.2712871760004</v>
+        <v>-194.2060416080005</v>
       </c>
       <c r="P95">
-        <v>-494.4505512240012</v>
+        <v>-538.6469455920012</v>
       </c>
       <c r="Q95">
-        <v>2920.949448775999</v>
+        <v>2876.753054407999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3540360571494801</v>
+        <v>0.4054087333410601</v>
       </c>
       <c r="T95">
-        <v>7.118615638556121</v>
+        <v>8.305051578315476</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.2331214212718939</v>
+        <v>0.2306414061519801</v>
       </c>
       <c r="W95">
-        <v>0.09095179943715338</v>
+        <v>0.09124592923037517</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8797034764977129</v>
+        <v>0.8703449288753967</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1100956974770163</v>
+        <v>0.1108236974770162</v>
       </c>
       <c r="C96">
-        <v>-17745.01707023145</v>
+        <v>-18457.09518480851</v>
       </c>
       <c r="D96">
-        <v>29320.03492976855</v>
+        <v>29114.96481519149</v>
       </c>
       <c r="E96">
-        <v>13671.552</v>
+        <v>14178.56</v>
       </c>
       <c r="F96">
-        <v>47658.752</v>
+        <v>48165.76</v>
       </c>
       <c r="G96">
         <v>593.7</v>
@@ -9165,37 +9165,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M96">
-        <v>5652.3279872</v>
+        <v>5712.459136</v>
       </c>
       <c r="N96">
-        <v>-732.8529872000017</v>
+        <v>-792.9841360000019</v>
       </c>
       <c r="O96">
-        <v>-194.2060416080005</v>
+        <v>-210.1407960400005</v>
       </c>
       <c r="P96">
-        <v>-538.6469455920012</v>
+        <v>-582.8433399600013</v>
       </c>
       <c r="Q96">
-        <v>2876.753054407999</v>
+        <v>2832.556660039999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4054087333410601</v>
+        <v>0.4773304800092724</v>
       </c>
       <c r="T96">
-        <v>8.305051578315476</v>
+        <v>9.966061893978576</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.2306414061519801</v>
+        <v>0.2282136018766961</v>
       </c>
       <c r="W96">
-        <v>0.09124592923037517</v>
+        <v>0.09153386681742384</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8703449288753967</v>
+        <v>0.8611834033082872</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1108236974770162</v>
+        <v>0.1115516974770162</v>
       </c>
       <c r="C97">
-        <v>-18457.09518480851</v>
+        <v>-19166.32462183949</v>
       </c>
       <c r="D97">
-        <v>29114.96481519149</v>
+        <v>28912.74337816051</v>
       </c>
       <c r="E97">
-        <v>14178.56</v>
+        <v>14685.568</v>
       </c>
       <c r="F97">
-        <v>48165.76</v>
+        <v>48672.768</v>
       </c>
       <c r="G97">
         <v>593.7</v>
@@ -9247,37 +9247,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M97">
-        <v>5712.459136</v>
+        <v>5772.590284800001</v>
       </c>
       <c r="N97">
-        <v>-792.9841360000019</v>
+        <v>-853.115284800002</v>
       </c>
       <c r="O97">
-        <v>-210.1407960400005</v>
+        <v>-226.0755504720005</v>
       </c>
       <c r="P97">
-        <v>-582.8433399600013</v>
+        <v>-627.0397343280015</v>
       </c>
       <c r="Q97">
-        <v>2832.556660039999</v>
+        <v>2788.360265671999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4773304800092724</v>
+        <v>0.5852131000115907</v>
       </c>
       <c r="T97">
-        <v>9.966061893978576</v>
+        <v>12.45757736747323</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.2282136018766961</v>
+        <v>0.2258363768571472</v>
       </c>
       <c r="W97">
-        <v>0.09153386681742384</v>
+        <v>0.09181580570474235</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8611834033082872</v>
+        <v>0.8522127428571593</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1115516974770162</v>
+        <v>0.1122796974770162</v>
       </c>
       <c r="C98">
-        <v>-19166.32462183949</v>
+        <v>-19872.76432937577</v>
       </c>
       <c r="D98">
-        <v>28912.74337816051</v>
+        <v>28713.31167062423</v>
       </c>
       <c r="E98">
-        <v>14685.568</v>
+        <v>15192.576</v>
       </c>
       <c r="F98">
-        <v>48672.768</v>
+        <v>49179.776</v>
       </c>
       <c r="G98">
         <v>593.7</v>
@@ -9329,37 +9329,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M98">
-        <v>5772.590284800001</v>
+        <v>5832.721433600001</v>
       </c>
       <c r="N98">
-        <v>-853.115284800002</v>
+        <v>-913.2464336000021</v>
       </c>
       <c r="O98">
-        <v>-226.0755504720005</v>
+        <v>-242.0103049040006</v>
       </c>
       <c r="P98">
-        <v>-627.0397343280015</v>
+        <v>-671.2361286960015</v>
       </c>
       <c r="Q98">
-        <v>2788.360265671999</v>
+        <v>2744.163871303998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5852131000115892</v>
+        <v>0.7650174666821191</v>
       </c>
       <c r="T98">
-        <v>12.45757736747319</v>
+        <v>16.61010315663093</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.2258363768571472</v>
+        <v>0.223508166786455</v>
       </c>
       <c r="W98">
-        <v>0.09181580570474235</v>
+        <v>0.09209193141912646</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8522127428571593</v>
+        <v>0.8434270444771885</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1122796974770162</v>
+        <v>0.1130076974770162</v>
       </c>
       <c r="C99">
-        <v>-19872.76432937577</v>
+        <v>-20576.4716401843</v>
       </c>
       <c r="D99">
-        <v>28713.31167062423</v>
+        <v>28516.6123598157</v>
       </c>
       <c r="E99">
-        <v>15192.576</v>
+        <v>15699.584</v>
       </c>
       <c r="F99">
-        <v>49179.776</v>
+        <v>49686.78399999999</v>
       </c>
       <c r="G99">
         <v>593.7</v>
@@ -9411,37 +9411,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M99">
-        <v>5832.721433600001</v>
+        <v>5892.8525824</v>
       </c>
       <c r="N99">
-        <v>-913.2464336000021</v>
+        <v>-973.3775824000013</v>
       </c>
       <c r="O99">
-        <v>-242.0103049040006</v>
+        <v>-257.9450593360004</v>
       </c>
       <c r="P99">
-        <v>-671.2361286960015</v>
+        <v>-715.4325230640009</v>
       </c>
       <c r="Q99">
-        <v>2744.163871303998</v>
+        <v>2699.967476935999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7650174666821191</v>
+        <v>1.124626200023179</v>
       </c>
       <c r="T99">
-        <v>16.61010315663093</v>
+        <v>24.91515473494639</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.223508166786455</v>
+        <v>0.2212274712070014</v>
       </c>
       <c r="W99">
-        <v>0.09209193141912646</v>
+        <v>0.09236242191484964</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8434270444771885</v>
+        <v>0.8348206460641561</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1130076974770162</v>
+        <v>0.1137356974770162</v>
       </c>
       <c r="C100">
-        <v>-20576.4716401843</v>
+        <v>-21277.5023266984</v>
       </c>
       <c r="D100">
-        <v>28516.6123598157</v>
+        <v>28322.5896733016</v>
       </c>
       <c r="E100">
-        <v>15699.584</v>
+        <v>16206.592</v>
       </c>
       <c r="F100">
-        <v>49686.78399999999</v>
+        <v>50193.79199999999</v>
       </c>
       <c r="G100">
         <v>593.7</v>
@@ -9493,37 +9493,37 @@
         <v>4919.474999999999</v>
       </c>
       <c r="M100">
-        <v>5892.8525824</v>
+        <v>5952.9837312</v>
       </c>
       <c r="N100">
-        <v>-973.3775824000013</v>
+        <v>-1033.508731200001</v>
       </c>
       <c r="O100">
-        <v>-257.9450593360004</v>
+        <v>-273.8798137680004</v>
       </c>
       <c r="P100">
-        <v>-715.4325230640009</v>
+        <v>-759.628917432001</v>
       </c>
       <c r="Q100">
-        <v>2699.967476935999</v>
+        <v>2655.771082567999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.124626200023179</v>
+        <v>2.203452400046356</v>
       </c>
       <c r="T100">
-        <v>24.91515473494639</v>
+        <v>49.83030946989276</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.2212274712070014</v>
+        <v>0.2189928502857185</v>
       </c>
       <c r="W100">
-        <v>0.09236242191484964</v>
+        <v>0.09262744795611379</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8348206460641561</v>
+        <v>0.8263881142857302</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1137356974770162</v>
-      </c>
-      <c r="C101">
-        <v>-21277.5023266984</v>
-      </c>
-      <c r="D101">
-        <v>28322.5896733016</v>
-      </c>
-      <c r="E101">
-        <v>16206.592</v>
-      </c>
-      <c r="F101">
-        <v>50193.79199999999</v>
-      </c>
-      <c r="G101">
-        <v>593.7</v>
-      </c>
-      <c r="H101">
-        <v>16713.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8334.874999999998</v>
-      </c>
-      <c r="K101">
-        <v>3415.4</v>
-      </c>
-      <c r="L101">
-        <v>4919.474999999999</v>
-      </c>
-      <c r="M101">
-        <v>5952.9837312</v>
-      </c>
-      <c r="N101">
-        <v>-1033.508731200001</v>
-      </c>
-      <c r="O101">
-        <v>-273.8798137680004</v>
-      </c>
-      <c r="P101">
-        <v>-759.628917432001</v>
-      </c>
-      <c r="Q101">
-        <v>2655.771082567999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.203452400046356</v>
-      </c>
-      <c r="T101">
-        <v>49.83030946989276</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.2189928502857185</v>
-      </c>
-      <c r="W101">
-        <v>0.09262744795611379</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8263881142857302</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
